--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN96"/>
+  <dimension ref="A1:BN107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21655,15 +21655,11 @@
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -21697,173 +21693,109 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q95" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>18</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>7</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
+        <v>4</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1</v>
+      </c>
+      <c r="X95" t="n">
+        <v>7</v>
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="AA95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>5</v>
       </c>
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="AG95" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>13</v>
       </c>
       <c r="AK95" t="inlineStr"/>
       <c r="AL95" t="inlineStr"/>
       <c r="AM95" t="inlineStr"/>
       <c r="AN95" t="inlineStr"/>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AV95" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BA95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BB95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BC95" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BD95" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AO95" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>665</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>253</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>589</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>93</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>126</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>106</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>6</v>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -21931,15 +21863,11 @@
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -21973,181 +21901,113 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q96" t="n">
+        <v>18</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="n">
+        <v>3</v>
+      </c>
+      <c r="U96" t="n">
+        <v>4</v>
+      </c>
+      <c r="V96" t="n">
+        <v>2</v>
+      </c>
+      <c r="W96" t="n">
+        <v>9</v>
+      </c>
+      <c r="X96" t="n">
+        <v>2</v>
       </c>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA96" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
       </c>
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="AG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>15</v>
       </c>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="AP96" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="AV96" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BA96" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BB96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BC96" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BD96" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>759</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>315</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>652</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>231</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>228</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>99</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>125</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>52</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>6</v>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -22185,6 +22045,3078 @@
       </c>
       <c r="BM96" t="inlineStr"/>
       <c r="BN96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
+      <c r="AQ97" t="inlineStr"/>
+      <c r="AR97" t="inlineStr"/>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr"/>
+      <c r="BA97" t="inlineStr"/>
+      <c r="BB97" t="inlineStr"/>
+      <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="BH97" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="BI97" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>551</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL97" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM97" t="inlineStr"/>
+      <c r="BN97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>54 392</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr"/>
+      <c r="BA98" t="inlineStr"/>
+      <c r="BB98" t="inlineStr"/>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="BH98" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="BI98" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>551</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL98" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM98" t="inlineStr"/>
+      <c r="BN98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+      <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="inlineStr"/>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr"/>
+      <c r="BA99" t="inlineStr"/>
+      <c r="BB99" t="inlineStr"/>
+      <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="BG99" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="BH99" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="BI99" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>551</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM99" t="inlineStr"/>
+      <c r="BN99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2yXIHV57</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>24.08.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Stade du Moustoir
+ (Lorient)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>16 787</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE100" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="BG100" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="BH100" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="BI100" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL100" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM100" t="inlineStr"/>
+      <c r="BN100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>GM5aU8kD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Parc des Sports
+ (Annecy)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>15 660</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BE101" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="BF101" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="BH101" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="BI101" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL101" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM101" t="inlineStr"/>
+      <c r="BN101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>r97iWUK0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="BI102" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL102" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM102" t="inlineStr"/>
+      <c r="BN102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>MaSQpUZg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Stade Francis Le Basser
+ (Laval)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="BI103" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL103" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM103" t="inlineStr"/>
+      <c r="BN103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>WUmnhCsK</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="BI104" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr"/>
+      <c r="BN104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>nsErYjjl</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Leleu M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Nouste Camp
+ (Pau)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>4 031</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="BI105" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL105" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM105" t="inlineStr"/>
+      <c r="BN105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>UsP4uZcE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Stade Paul-Lignon
+ (Rodez)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5 955</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="BH106" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="BI106" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL106" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM106" t="inlineStr"/>
+      <c r="BN106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>4rrRVcF7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="BH107" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="BI107" t="n">
+        <v>55</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>555</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL107" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BM107" t="inlineStr"/>
+      <c r="BN107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN114"/>
+  <dimension ref="A1:BN122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25480,15 +25480,11 @@
           <t>63 841</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -25510,15 +25506,11 @@
           <t>Reims</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="M113" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.88</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -25530,137 +25522,85 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="Q113" t="n">
+        <v>16</v>
+      </c>
+      <c r="R113" t="n">
+        <v>12</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="n">
+        <v>3</v>
+      </c>
+      <c r="U113" t="n">
+        <v>4</v>
+      </c>
+      <c r="V113" t="n">
+        <v>7</v>
+      </c>
+      <c r="W113" t="n">
+        <v>2</v>
+      </c>
+      <c r="X113" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>13</v>
       </c>
       <c r="AK113" t="inlineStr"/>
       <c r="AL113" t="inlineStr"/>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>41</v>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
@@ -25744,15 +25684,11 @@
           <t>4 560</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -25786,121 +25722,77 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q114" t="n">
+        <v>5</v>
+      </c>
+      <c r="R114" t="n">
+        <v>19</v>
+      </c>
+      <c r="S114" t="n">
+        <v>2</v>
+      </c>
+      <c r="T114" t="n">
+        <v>2</v>
+      </c>
+      <c r="U114" t="n">
+        <v>2</v>
+      </c>
+      <c r="V114" t="n">
+        <v>10</v>
+      </c>
+      <c r="W114" t="n">
+        <v>1</v>
+      </c>
+      <c r="X114" t="n">
+        <v>7</v>
       </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="AA114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>5</v>
       </c>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="AG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>15</v>
       </c>
       <c r="AK114" t="inlineStr"/>
       <c r="AL114" t="inlineStr"/>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AP114" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>118</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>65</v>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
@@ -25936,68 +25828,2300 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA114" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="BB114" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="BC114" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="BD114" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="BE114" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BF114" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BG114" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BH114" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BI114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ114" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK114" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BL114" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BA114" t="n">
+        <v>400</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>552</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>319</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>477</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>31</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>8</v>
       </c>
       <c r="BM114" t="inlineStr"/>
       <c r="BN114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AW115" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr"/>
+      <c r="BB115" t="inlineStr"/>
+      <c r="BC115" t="inlineStr"/>
+      <c r="BD115" t="inlineStr"/>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr"/>
+      <c r="BG115" t="inlineStr"/>
+      <c r="BH115" t="inlineStr"/>
+      <c r="BI115" t="inlineStr"/>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
+      <c r="BM115" t="inlineStr"/>
+      <c r="BN115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>WlzDg17E</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Petit A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AW116" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BJ116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BM116" t="inlineStr"/>
+      <c r="BN116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AW117" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK117" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL117" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BM117" t="inlineStr"/>
+      <c r="BN117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AW118" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL118" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BM118" t="inlineStr"/>
+      <c r="BN118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AW119" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ119" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL119" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BM119" t="inlineStr"/>
+      <c r="BN119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AW120" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK120" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL120" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BM120" t="inlineStr"/>
+      <c r="BN120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AW121" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI121" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BJ121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BL121" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BM121" t="inlineStr"/>
+      <c r="BN121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AW122" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK122" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM122" t="inlineStr"/>
+      <c r="BN122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN122"/>
+  <dimension ref="A1:BN126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25896,15 +25896,11 @@
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -25926,15 +25922,11 @@
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
+      <c r="M115" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N115" t="n">
+        <v>2.24</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -25946,137 +25938,85 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q115" t="n">
+        <v>22</v>
+      </c>
+      <c r="R115" t="n">
+        <v>14</v>
+      </c>
+      <c r="S115" t="n">
+        <v>13</v>
+      </c>
+      <c r="T115" t="n">
+        <v>7</v>
+      </c>
+      <c r="U115" t="n">
+        <v>2</v>
+      </c>
+      <c r="V115" t="n">
+        <v>2</v>
+      </c>
+      <c r="W115" t="n">
+        <v>7</v>
+      </c>
+      <c r="X115" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>6</v>
       </c>
       <c r="AK115" t="inlineStr"/>
       <c r="AL115" t="inlineStr"/>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AP115" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>86</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>30</v>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
@@ -26156,15 +26096,11 @@
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -26198,129 +26134,81 @@
           <t>28%</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q116" t="n">
+        <v>23</v>
+      </c>
+      <c r="R116" t="n">
+        <v>8</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="n">
+        <v>4</v>
+      </c>
+      <c r="U116" t="n">
+        <v>10</v>
+      </c>
+      <c r="V116" t="n">
+        <v>1</v>
+      </c>
+      <c r="W116" t="n">
+        <v>8</v>
+      </c>
+      <c r="X116" t="n">
+        <v>3</v>
       </c>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA116" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
       </c>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AP116" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="AG116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>138</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>99</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>27</v>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
@@ -26356,65 +26244,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA116" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="BB116" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="BC116" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="BD116" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="BE116" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BF116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BG116" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BI116" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BJ116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK116" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL116" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BA116" t="n">
+        <v>519</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>222</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>403</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>109</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>18</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>12</v>
       </c>
       <c r="BM116" t="inlineStr"/>
       <c r="BN116" t="inlineStr"/>
@@ -26448,15 +26312,11 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -26490,121 +26350,77 @@
           <t>23%</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q117" t="n">
+        <v>12</v>
+      </c>
+      <c r="R117" t="n">
+        <v>8</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" t="n">
+        <v>4</v>
+      </c>
+      <c r="U117" t="n">
+        <v>8</v>
+      </c>
+      <c r="V117" t="n">
+        <v>3</v>
+      </c>
+      <c r="W117" t="n">
+        <v>3</v>
+      </c>
+      <c r="X117" t="n">
+        <v>1</v>
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
       </c>
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="AG117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>20</v>
       </c>
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr"/>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="AP117" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>153</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>95</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>39</v>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
@@ -26640,65 +26456,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA117" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="BB117" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="BC117" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="BD117" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="BE117" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF117" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BG117" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH117" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BI117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK117" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL117" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BA117" t="n">
+        <v>734</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>254</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>612</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>148</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>15</v>
       </c>
       <c r="BM117" t="inlineStr"/>
       <c r="BN117" t="inlineStr"/>
@@ -26732,15 +26524,11 @@
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -26774,129 +26562,81 @@
           <t>63%</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q118" t="n">
+        <v>6</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6</v>
+      </c>
+      <c r="S118" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" t="n">
+        <v>3</v>
+      </c>
+      <c r="U118" t="n">
+        <v>3</v>
+      </c>
+      <c r="V118" t="n">
+        <v>2</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1</v>
       </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>1</v>
       </c>
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AP118" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="AG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>124</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>56</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>41</v>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
@@ -26932,65 +26672,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA118" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="BB118" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="BC118" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="BD118" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="BE118" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF118" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BG118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH118" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BI118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK118" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL118" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BA118" t="n">
+        <v>420</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>696</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>357</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>577</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>17</v>
       </c>
       <c r="BM118" t="inlineStr"/>
       <c r="BN118" t="inlineStr"/>
@@ -27024,15 +26740,11 @@
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -27066,121 +26778,77 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q119" t="n">
+        <v>13</v>
+      </c>
+      <c r="R119" t="n">
+        <v>13</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>8</v>
+      </c>
+      <c r="V119" t="n">
+        <v>5</v>
+      </c>
+      <c r="W119" t="n">
+        <v>2</v>
+      </c>
+      <c r="X119" t="n">
+        <v>7</v>
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="AA119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>8</v>
       </c>
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="AG119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>14</v>
       </c>
       <c r="AK119" t="inlineStr"/>
       <c r="AL119" t="inlineStr"/>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>139</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>109</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>60</v>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
@@ -27216,65 +26884,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BF119" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BG119" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BH119" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BI119" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ119" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK119" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL119" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="BA119" t="n">
+        <v>463</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>413</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>331</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>298</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>21</v>
       </c>
       <c r="BM119" t="inlineStr"/>
       <c r="BN119" t="inlineStr"/>
@@ -27308,15 +26952,11 @@
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -27350,113 +26990,73 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q120" t="n">
+        <v>7</v>
+      </c>
+      <c r="R120" t="n">
+        <v>12</v>
+      </c>
+      <c r="S120" t="n">
+        <v>4</v>
+      </c>
+      <c r="T120" t="n">
+        <v>5</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3</v>
+      </c>
+      <c r="V120" t="n">
+        <v>7</v>
       </c>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>3</v>
       </c>
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="AG120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>11</v>
       </c>
       <c r="AK120" t="inlineStr"/>
       <c r="AL120" t="inlineStr"/>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AP120" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>110</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>55</v>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
@@ -27492,65 +27092,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA120" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="BB120" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="BC120" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="BD120" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="BE120" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BF120" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BG120" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BH120" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI120" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ120" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BK120" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL120" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BA120" t="n">
+        <v>455</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>436</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>363</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>343</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>17</v>
       </c>
       <c r="BM120" t="inlineStr"/>
       <c r="BN120" t="inlineStr"/>
@@ -27584,15 +27160,11 @@
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -27626,121 +27198,77 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q121" t="n">
+        <v>21</v>
+      </c>
+      <c r="R121" t="n">
+        <v>18</v>
+      </c>
+      <c r="S121" t="n">
+        <v>7</v>
+      </c>
+      <c r="T121" t="n">
+        <v>7</v>
+      </c>
+      <c r="U121" t="n">
+        <v>8</v>
+      </c>
+      <c r="V121" t="n">
+        <v>6</v>
+      </c>
+      <c r="W121" t="n">
+        <v>6</v>
+      </c>
+      <c r="X121" t="n">
+        <v>5</v>
       </c>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA121" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>1</v>
       </c>
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AG121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>10</v>
       </c>
       <c r="AK121" t="inlineStr"/>
       <c r="AL121" t="inlineStr"/>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AP121" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>85</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>71</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>44</v>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
@@ -27776,65 +27304,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA121" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="BB121" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="BC121" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="BD121" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="BE121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BF121" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BG121" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BH121" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BI121" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BJ121" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BL121" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BA121" t="n">
+        <v>586</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>414</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>493</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>337</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>12</v>
       </c>
       <c r="BM121" t="inlineStr"/>
       <c r="BN121" t="inlineStr"/>
@@ -27868,15 +27372,11 @@
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -27910,121 +27410,77 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q122" t="n">
+        <v>13</v>
+      </c>
+      <c r="R122" t="n">
+        <v>9</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4</v>
+      </c>
+      <c r="U122" t="n">
+        <v>7</v>
+      </c>
+      <c r="V122" t="n">
+        <v>5</v>
+      </c>
+      <c r="W122" t="n">
+        <v>5</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA122" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
       </c>
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="AG122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>16</v>
       </c>
       <c r="AK122" t="inlineStr"/>
       <c r="AL122" t="inlineStr"/>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>103</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>34</v>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
@@ -28060,68 +27516,1132 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA122" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="BB122" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="BC122" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="BD122" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="BE122" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF122" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BG122" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BH122" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BI122" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ122" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK122" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL122" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BA122" t="n">
+        <v>319</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>397</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>219</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>282</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>10</v>
       </c>
       <c r="BM122" t="inlineStr"/>
       <c r="BN122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AW123" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr"/>
+      <c r="BB123" t="inlineStr"/>
+      <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
+      <c r="BI123" t="inlineStr"/>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
+      <c r="BM123" t="inlineStr"/>
+      <c r="BN123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>31.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr"/>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AW124" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr"/>
+      <c r="BB124" t="inlineStr"/>
+      <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
+      <c r="BM124" t="inlineStr"/>
+      <c r="BN124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>zoZtwwYp</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>31.08.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>5 460</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AW125" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BH125" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK125" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL125" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BM125" t="inlineStr"/>
+      <c r="BN125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>8lUzaKf4</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>31.08.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>18 369</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr"/>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AW126" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>555</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG126" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BH126" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BI126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BJ126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BM126" t="inlineStr"/>
+      <c r="BN126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN126"/>
+  <dimension ref="A1:BN132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27584,15 +27584,11 @@
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -27614,15 +27610,11 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="M123" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1.7</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -27634,137 +27626,85 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="Q123" t="n">
+        <v>11</v>
+      </c>
+      <c r="R123" t="n">
+        <v>10</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="n">
+        <v>5</v>
+      </c>
+      <c r="U123" t="n">
+        <v>5</v>
+      </c>
+      <c r="V123" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>13</v>
       </c>
       <c r="AK123" t="inlineStr"/>
       <c r="AL123" t="inlineStr"/>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AP123" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>55</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>86</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>44</v>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
@@ -27844,15 +27784,11 @@
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G124" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -27874,15 +27810,11 @@
           <t>St Etienne</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
+      <c r="M124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.31</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -27894,137 +27826,85 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q124" t="n">
+        <v>17</v>
+      </c>
+      <c r="R124" t="n">
+        <v>3</v>
+      </c>
+      <c r="S124" t="n">
+        <v>7</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>6</v>
+      </c>
+      <c r="V124" t="n">
+        <v>2</v>
+      </c>
+      <c r="W124" t="n">
+        <v>4</v>
+      </c>
+      <c r="X124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>14</v>
       </c>
       <c r="AK124" t="inlineStr"/>
       <c r="AL124" t="inlineStr"/>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AP124" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>105</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>111</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>54</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>42</v>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
@@ -28108,15 +27988,11 @@
           <t>5 460</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -28150,113 +28026,73 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q125" t="n">
+        <v>14</v>
+      </c>
+      <c r="R125" t="n">
+        <v>19</v>
+      </c>
+      <c r="S125" t="n">
+        <v>7</v>
+      </c>
+      <c r="T125" t="n">
+        <v>9</v>
+      </c>
+      <c r="U125" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" t="n">
+        <v>5</v>
+      </c>
+      <c r="W125" t="n">
+        <v>4</v>
+      </c>
+      <c r="X125" t="n">
+        <v>5</v>
       </c>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1</v>
       </c>
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="AG125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>13</v>
       </c>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="inlineStr"/>
       <c r="AN125" t="inlineStr"/>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="AO125" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>159</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>82</v>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
@@ -28292,65 +28128,41 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA125" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="BB125" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="BC125" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="BD125" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="BE125" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BF125" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BG125" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BH125" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BI125" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK125" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL125" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="BA125" t="n">
+        <v>291</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>561</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>219</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>503</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>16</v>
       </c>
       <c r="BM125" t="inlineStr"/>
       <c r="BN125" t="inlineStr"/>
@@ -28388,15 +28200,11 @@
           <t>18 369</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -28430,121 +28238,77 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q126" t="n">
+        <v>20</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3</v>
+      </c>
+      <c r="T126" t="n">
+        <v>4</v>
+      </c>
+      <c r="U126" t="n">
+        <v>15</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>2</v>
+      </c>
+      <c r="X126" t="n">
+        <v>3</v>
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>1</v>
       </c>
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="AG126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>19</v>
       </c>
       <c r="AK126" t="inlineStr"/>
       <c r="AL126" t="inlineStr"/>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>182</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>74</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>31</v>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
@@ -28580,68 +28344,1648 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BA126" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="BB126" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="BC126" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="BD126" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="BE126" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BG126" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH126" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BI126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BJ126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK126" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BA126" t="n">
+        <v>608</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>272</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>553</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>187</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>9</v>
       </c>
       <c r="BM126" t="inlineStr"/>
       <c r="BN126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>45 434</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr"/>
+      <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AW127" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr"/>
+      <c r="BB127" t="inlineStr"/>
+      <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
+      <c r="BM127" t="inlineStr"/>
+      <c r="BN127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>9 168</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN128" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AW128" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr"/>
+      <c r="BB128" t="inlineStr"/>
+      <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
+      <c r="BM128" t="inlineStr"/>
+      <c r="BN128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>19 715</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AT129" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AW129" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr"/>
+      <c r="BB129" t="inlineStr"/>
+      <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
+      <c r="BM129" t="inlineStr"/>
+      <c r="BN129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr"/>
+      <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AW130" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr"/>
+      <c r="BB130" t="inlineStr"/>
+      <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
+      <c r="BM130" t="inlineStr"/>
+      <c r="BN130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>9 030</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr"/>
+      <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AW131" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr"/>
+      <c r="BB131" t="inlineStr"/>
+      <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
+      <c r="BM131" t="inlineStr"/>
+      <c r="BN131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>19 178</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AW132" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>551</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr"/>
+      <c r="BB132" t="inlineStr"/>
+      <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="inlineStr"/>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
+      <c r="BM132" t="inlineStr"/>
+      <c r="BN132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN143"/>
+  <dimension ref="A1:BN150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29700,15 +29700,11 @@
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -29730,15 +29726,11 @@
           <t>Monaco</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
+      <c r="M133" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2.93</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -29750,135 +29742,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="Q133" t="n">
+        <v>10</v>
+      </c>
+      <c r="R133" t="n">
+        <v>14</v>
+      </c>
+      <c r="S133" t="n">
+        <v>2</v>
+      </c>
+      <c r="T133" t="n">
+        <v>7</v>
+      </c>
+      <c r="U133" t="n">
+        <v>5</v>
+      </c>
+      <c r="V133" t="n">
+        <v>4</v>
+      </c>
+      <c r="W133" t="n">
+        <v>3</v>
+      </c>
+      <c r="X133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>46</v>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
@@ -29964,15 +29904,11 @@
           <t>65 803</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -29994,15 +29930,11 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
+      <c r="M134" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1.93</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -30014,135 +29946,83 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="Q134" t="n">
+        <v>10</v>
+      </c>
+      <c r="R134" t="n">
+        <v>11</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
+      </c>
+      <c r="U134" t="n">
+        <v>3</v>
+      </c>
+      <c r="V134" t="n">
+        <v>4</v>
+      </c>
+      <c r="W134" t="n">
+        <v>2</v>
+      </c>
+      <c r="X134" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>91</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>43</v>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
@@ -30178,15 +30058,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
       </c>
       <c r="BA134" t="inlineStr"/>
       <c r="BB134" t="inlineStr"/>
@@ -30236,15 +30112,11 @@
           <t>22 144</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -30266,15 +30138,11 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
+      <c r="M135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.11</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -30286,135 +30154,83 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="Q135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>17</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>4</v>
+      </c>
+      <c r="U135" t="n">
+        <v>5</v>
+      </c>
+      <c r="V135" t="n">
+        <v>11</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>92</v>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
@@ -30496,15 +30312,11 @@
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -30538,119 +30350,75 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q136" t="n">
+        <v>13</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" t="n">
+        <v>3</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1</v>
       </c>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>3</v>
       </c>
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="AG136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>115</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>92</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>51</v>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
@@ -30688,65 +30456,41 @@
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr"/>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="BE136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BF136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH136" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BI136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK136" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL136" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="BA136" t="n">
+        <v>698</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>372</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>608</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>161</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>16</v>
       </c>
       <c r="BM136" t="inlineStr"/>
       <c r="BN136" t="inlineStr"/>
@@ -30784,15 +30528,11 @@
           <t>5 478</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -30826,119 +30566,75 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q137" t="n">
+        <v>9</v>
+      </c>
+      <c r="R137" t="n">
+        <v>12</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="n">
+        <v>4</v>
+      </c>
+      <c r="U137" t="n">
+        <v>4</v>
+      </c>
+      <c r="V137" t="n">
+        <v>6</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>2</v>
       </c>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AA137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>6</v>
       </c>
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="AG137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>56</v>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
@@ -30976,65 +30672,41 @@
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr"/>
-      <c r="BA137" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="BB137" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="BC137" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="BD137" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="BE137" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BF137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BG137" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BH137" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BA137" t="n">
+        <v>342</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>536</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>238</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>441</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>9</v>
       </c>
       <c r="BM137" t="inlineStr"/>
       <c r="BN137" t="inlineStr"/>
@@ -31072,15 +30744,11 @@
           <t>10 567</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -31114,119 +30782,75 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q138" t="n">
+        <v>12</v>
+      </c>
+      <c r="R138" t="n">
+        <v>8</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3</v>
+      </c>
+      <c r="T138" t="n">
+        <v>2</v>
+      </c>
+      <c r="U138" t="n">
+        <v>3</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1</v>
+      </c>
+      <c r="W138" t="n">
+        <v>6</v>
+      </c>
+      <c r="X138" t="n">
+        <v>5</v>
       </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1</v>
       </c>
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="AG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>139</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>40</v>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
@@ -31264,65 +30888,41 @@
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr"/>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="BB138" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="BC138" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="BD138" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="BE138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BG138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH138" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BI138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BL138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BA138" t="n">
+        <v>450</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>278</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>382</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>201</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>7</v>
       </c>
       <c r="BM138" t="inlineStr"/>
       <c r="BN138" t="inlineStr"/>
@@ -31360,15 +30960,11 @@
           <t>4 275</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -31402,119 +30998,75 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q139" t="n">
+        <v>6</v>
+      </c>
+      <c r="R139" t="n">
+        <v>8</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
+        <v>4</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2</v>
+      </c>
+      <c r="V139" t="n">
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>3</v>
+      </c>
+      <c r="X139" t="n">
+        <v>2</v>
       </c>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
       </c>
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="AG139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>111</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>47</v>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
@@ -31552,65 +31104,41 @@
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr"/>
-      <c r="BA139" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="BB139" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="BC139" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="BD139" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="BE139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF139" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BH139" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BI139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK139" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL139" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BA139" t="n">
+        <v>476</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>394</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>387</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>311</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>13</v>
       </c>
       <c r="BM139" t="inlineStr"/>
       <c r="BN139" t="inlineStr"/>
@@ -31648,15 +31176,11 @@
           <t>5 748</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -31690,119 +31214,75 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
+        <v>2</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>3</v>
       </c>
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="AG140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>142</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>142</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>79</v>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
@@ -31840,65 +31320,41 @@
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr"/>
-      <c r="BA140" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="BB140" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="BC140" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="BD140" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="BE140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BG140" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BI140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BL140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BA140" t="n">
+        <v>201</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>209</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>158</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>169</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>4</v>
       </c>
       <c r="BM140" t="inlineStr"/>
       <c r="BN140" t="inlineStr"/>
@@ -31936,15 +31392,11 @@
           <t>10 017</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -31978,119 +31430,75 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q141" t="n">
+        <v>14</v>
+      </c>
+      <c r="R141" t="n">
+        <v>5</v>
+      </c>
+      <c r="S141" t="n">
+        <v>7</v>
+      </c>
+      <c r="T141" t="n">
+        <v>3</v>
+      </c>
+      <c r="U141" t="n">
+        <v>5</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>2</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
       </c>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA141" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
       </c>
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="AG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>43</v>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
@@ -32126,75 +31534,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA141" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="BB141" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="BC141" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="BD141" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="BE141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BF141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BG141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BI141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>468</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>384</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>379</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>321</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>2</v>
       </c>
       <c r="BM141" t="inlineStr"/>
       <c r="BN141" t="inlineStr"/>
@@ -32232,15 +31612,11 @@
           <t>2 741</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -32274,119 +31650,75 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q142" t="n">
+        <v>19</v>
+      </c>
+      <c r="R142" t="n">
+        <v>8</v>
+      </c>
+      <c r="S142" t="n">
+        <v>9</v>
+      </c>
+      <c r="T142" t="n">
+        <v>3</v>
+      </c>
+      <c r="U142" t="n">
+        <v>8</v>
+      </c>
+      <c r="V142" t="n">
+        <v>5</v>
+      </c>
+      <c r="W142" t="n">
+        <v>2</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
       </c>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
       </c>
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="AG142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>76</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>36</v>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
@@ -32424,65 +31756,41 @@
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr"/>
-      <c r="BA142" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="BB142" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="BC142" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="BD142" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="BE142" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BF142" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BG142" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH142" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BI142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK142" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL142" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="BA142" t="n">
+        <v>470</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>410</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>368</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>296</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>29</v>
       </c>
       <c r="BM142" t="inlineStr"/>
       <c r="BN142" t="inlineStr"/>
@@ -32520,15 +31828,11 @@
           <t>3 991</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -32562,119 +31866,75 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>3</v>
+      </c>
+      <c r="S143" t="n">
+        <v>2</v>
+      </c>
+      <c r="T143" t="n">
+        <v>3</v>
+      </c>
+      <c r="U143" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
       </c>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>3</v>
       </c>
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="AG143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>109</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>72</v>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
@@ -32712,68 +31972,1956 @@
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr"/>
-      <c r="BA143" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BB143" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="BC143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="BD143" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="BE143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BF143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BG143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH143" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BI143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BL143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BA143" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>111</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>72</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>98</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2</v>
       </c>
       <c r="BM143" t="inlineStr"/>
       <c r="BN143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>15.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>38 116</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AU144" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr"/>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
+      <c r="BI144" t="inlineStr"/>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="inlineStr"/>
+      <c r="BM144" t="inlineStr"/>
+      <c r="BN144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>29 811</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AU145" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr"/>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr"/>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="inlineStr"/>
+      <c r="BM145" t="inlineStr"/>
+      <c r="BN145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>19 135</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AU146" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr"/>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
+      <c r="BI146" t="inlineStr"/>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="inlineStr"/>
+      <c r="BM146" t="inlineStr"/>
+      <c r="BN146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>30 097</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN147" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AU147" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr"/>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
+      <c r="BI147" t="inlineStr"/>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="inlineStr"/>
+      <c r="BM147" t="inlineStr"/>
+      <c r="BN147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>27 451</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN148" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AU148" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr"/>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr"/>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
+      <c r="BI148" t="inlineStr"/>
+      <c r="BJ148" t="inlineStr"/>
+      <c r="BK148" t="inlineStr"/>
+      <c r="BL148" t="inlineStr"/>
+      <c r="BM148" t="inlineStr"/>
+      <c r="BN148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>14.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Turpin C.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>47 628</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AN149" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AU149" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr"/>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr"/>
+      <c r="BI149" t="inlineStr"/>
+      <c r="BJ149" t="inlineStr"/>
+      <c r="BK149" t="inlineStr"/>
+      <c r="BL149" t="inlineStr"/>
+      <c r="BM149" t="inlineStr"/>
+      <c r="BN149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>4GNqcbPG</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>16.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>4 079</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr"/>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AN150" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AU150" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr"/>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN143"/>
+  <dimension ref="A1:BN168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29700,15 +29700,11 @@
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>3</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -29730,15 +29726,11 @@
           <t>Monaco</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
+      <c r="M133" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2.93</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -29750,135 +29742,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="Q133" t="n">
+        <v>10</v>
+      </c>
+      <c r="R133" t="n">
+        <v>14</v>
+      </c>
+      <c r="S133" t="n">
+        <v>2</v>
+      </c>
+      <c r="T133" t="n">
+        <v>7</v>
+      </c>
+      <c r="U133" t="n">
+        <v>5</v>
+      </c>
+      <c r="V133" t="n">
+        <v>4</v>
+      </c>
+      <c r="W133" t="n">
+        <v>3</v>
+      </c>
+      <c r="X133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>46</v>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
@@ -29964,15 +29904,11 @@
           <t>65 803</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -29994,15 +29930,11 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
+      <c r="M134" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1.93</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -30014,135 +29946,83 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="Q134" t="n">
+        <v>10</v>
+      </c>
+      <c r="R134" t="n">
+        <v>11</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4</v>
+      </c>
+      <c r="U134" t="n">
+        <v>3</v>
+      </c>
+      <c r="V134" t="n">
+        <v>4</v>
+      </c>
+      <c r="W134" t="n">
+        <v>2</v>
+      </c>
+      <c r="X134" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>91</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>43</v>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
@@ -30178,15 +30058,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
       </c>
       <c r="BA134" t="inlineStr"/>
       <c r="BB134" t="inlineStr"/>
@@ -30236,15 +30112,11 @@
           <t>22 144</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -30266,15 +30138,11 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
+      <c r="M135" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.11</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -30286,135 +30154,83 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="Q135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>17</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>4</v>
+      </c>
+      <c r="U135" t="n">
+        <v>5</v>
+      </c>
+      <c r="V135" t="n">
+        <v>11</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>92</v>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
@@ -30496,15 +30312,11 @@
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -30538,119 +30350,75 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q136" t="n">
+        <v>13</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" t="n">
+        <v>3</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1</v>
       </c>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>3</v>
       </c>
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="AG136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>115</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>92</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>51</v>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
@@ -30688,65 +30456,41 @@
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr"/>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="BE136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BF136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH136" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BI136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK136" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL136" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="BA136" t="n">
+        <v>698</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>372</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>608</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>161</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>16</v>
       </c>
       <c r="BM136" t="inlineStr"/>
       <c r="BN136" t="inlineStr"/>
@@ -30784,15 +30528,11 @@
           <t>5 478</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -30826,119 +30566,75 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q137" t="n">
+        <v>9</v>
+      </c>
+      <c r="R137" t="n">
+        <v>12</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="n">
+        <v>4</v>
+      </c>
+      <c r="U137" t="n">
+        <v>4</v>
+      </c>
+      <c r="V137" t="n">
+        <v>6</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>2</v>
       </c>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AA137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>6</v>
       </c>
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="AG137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>56</v>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
@@ -30976,65 +30672,41 @@
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr"/>
-      <c r="BA137" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="BB137" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="BC137" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="BD137" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="BE137" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BF137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BG137" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BH137" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL137" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BA137" t="n">
+        <v>342</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>536</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>238</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>441</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>9</v>
       </c>
       <c r="BM137" t="inlineStr"/>
       <c r="BN137" t="inlineStr"/>
@@ -31072,15 +30744,11 @@
           <t>10 567</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -31114,119 +30782,75 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q138" t="n">
+        <v>12</v>
+      </c>
+      <c r="R138" t="n">
+        <v>8</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3</v>
+      </c>
+      <c r="T138" t="n">
+        <v>2</v>
+      </c>
+      <c r="U138" t="n">
+        <v>3</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1</v>
+      </c>
+      <c r="W138" t="n">
+        <v>6</v>
+      </c>
+      <c r="X138" t="n">
+        <v>5</v>
       </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1</v>
       </c>
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="AG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>139</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>40</v>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
@@ -31264,65 +30888,41 @@
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr"/>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="BB138" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="BC138" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="BD138" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="BE138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BG138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH138" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BI138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BL138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BA138" t="n">
+        <v>450</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>278</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>382</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>201</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>7</v>
       </c>
       <c r="BM138" t="inlineStr"/>
       <c r="BN138" t="inlineStr"/>
@@ -31360,15 +30960,11 @@
           <t>4 275</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -31402,119 +30998,75 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q139" t="n">
+        <v>6</v>
+      </c>
+      <c r="R139" t="n">
+        <v>8</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
+        <v>4</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2</v>
+      </c>
+      <c r="V139" t="n">
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>3</v>
+      </c>
+      <c r="X139" t="n">
+        <v>2</v>
       </c>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
       </c>
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP139" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="AG139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>111</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>47</v>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
@@ -31552,65 +31104,41 @@
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr"/>
-      <c r="BA139" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="BB139" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="BC139" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="BD139" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="BE139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF139" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BH139" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BI139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ139" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK139" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL139" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BA139" t="n">
+        <v>476</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>394</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>387</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>311</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>13</v>
       </c>
       <c r="BM139" t="inlineStr"/>
       <c r="BN139" t="inlineStr"/>
@@ -31648,15 +31176,11 @@
           <t>5 748</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -31690,119 +31214,75 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
+        <v>2</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>3</v>
       </c>
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AP140" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="AG140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>142</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>142</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>79</v>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
@@ -31840,65 +31320,41 @@
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr"/>
-      <c r="BA140" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="BB140" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="BC140" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="BD140" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="BE140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BG140" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BI140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BL140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BA140" t="n">
+        <v>201</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>209</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>158</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>169</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>4</v>
       </c>
       <c r="BM140" t="inlineStr"/>
       <c r="BN140" t="inlineStr"/>
@@ -31936,15 +31392,11 @@
           <t>10 017</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -31978,119 +31430,75 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q141" t="n">
+        <v>14</v>
+      </c>
+      <c r="R141" t="n">
+        <v>5</v>
+      </c>
+      <c r="S141" t="n">
+        <v>7</v>
+      </c>
+      <c r="T141" t="n">
+        <v>3</v>
+      </c>
+      <c r="U141" t="n">
+        <v>5</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>2</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
       </c>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA141" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
       </c>
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="AG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>43</v>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
@@ -32126,75 +31534,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA141" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="BB141" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="BC141" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="BD141" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="BE141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BF141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BG141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH141" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BI141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>468</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>384</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>379</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>321</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>2</v>
       </c>
       <c r="BM141" t="inlineStr"/>
       <c r="BN141" t="inlineStr"/>
@@ -32232,15 +31612,11 @@
           <t>2 741</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -32274,119 +31650,75 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q142" t="n">
+        <v>19</v>
+      </c>
+      <c r="R142" t="n">
+        <v>8</v>
+      </c>
+      <c r="S142" t="n">
+        <v>9</v>
+      </c>
+      <c r="T142" t="n">
+        <v>3</v>
+      </c>
+      <c r="U142" t="n">
+        <v>8</v>
+      </c>
+      <c r="V142" t="n">
+        <v>5</v>
+      </c>
+      <c r="W142" t="n">
+        <v>2</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
       </c>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
       </c>
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="AG142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>76</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>36</v>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
@@ -32424,65 +31756,41 @@
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr"/>
-      <c r="BA142" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="BB142" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="BC142" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="BD142" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="BE142" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BF142" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BG142" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH142" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BI142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ142" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK142" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL142" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="BA142" t="n">
+        <v>470</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>410</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>368</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>296</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>29</v>
       </c>
       <c r="BM142" t="inlineStr"/>
       <c r="BN142" t="inlineStr"/>
@@ -32520,15 +31828,11 @@
           <t>3 991</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -32562,119 +31866,75 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>3</v>
+      </c>
+      <c r="S143" t="n">
+        <v>2</v>
+      </c>
+      <c r="T143" t="n">
+        <v>3</v>
+      </c>
+      <c r="U143" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
       </c>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>3</v>
       </c>
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="AG143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>109</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>72</v>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
@@ -32712,68 +31972,6712 @@
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr"/>
-      <c r="BA143" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BB143" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="BC143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="BD143" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="BE143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BF143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BG143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH143" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BI143" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK143" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BL143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BA143" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>111</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>72</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>98</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2</v>
       </c>
       <c r="BM143" t="inlineStr"/>
       <c r="BN143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>22.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="inlineStr"/>
+      <c r="AP144" t="inlineStr"/>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AU144" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr"/>
+      <c r="BB144" t="inlineStr"/>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
+      <c r="BI144" t="inlineStr"/>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="inlineStr"/>
+      <c r="BM144" t="inlineStr"/>
+      <c r="BN144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr"/>
+      <c r="AP145" t="inlineStr"/>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AU145" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr"/>
+      <c r="BA145" t="inlineStr"/>
+      <c r="BB145" t="inlineStr"/>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr"/>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="inlineStr"/>
+      <c r="BM145" t="inlineStr"/>
+      <c r="BN145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="inlineStr"/>
+      <c r="AP146" t="inlineStr"/>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AU146" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr"/>
+      <c r="BA146" t="inlineStr"/>
+      <c r="BB146" t="inlineStr"/>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
+      <c r="BI146" t="inlineStr"/>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="inlineStr"/>
+      <c r="BM146" t="inlineStr"/>
+      <c r="BN146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr"/>
+      <c r="AP147" t="inlineStr"/>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AU147" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr"/>
+      <c r="BA147" t="inlineStr"/>
+      <c r="BB147" t="inlineStr"/>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
+      <c r="BI147" t="inlineStr"/>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="inlineStr"/>
+      <c r="BM147" t="inlineStr"/>
+      <c r="BN147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr"/>
+      <c r="AO148" t="inlineStr"/>
+      <c r="AP148" t="inlineStr"/>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AU148" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr"/>
+      <c r="BA148" t="inlineStr"/>
+      <c r="BB148" t="inlineStr"/>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr"/>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
+      <c r="BI148" t="inlineStr"/>
+      <c r="BJ148" t="inlineStr"/>
+      <c r="BK148" t="inlineStr"/>
+      <c r="BL148" t="inlineStr"/>
+      <c r="BM148" t="inlineStr"/>
+      <c r="BN148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>21.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20 220</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr"/>
+      <c r="AO149" t="inlineStr"/>
+      <c r="AP149" t="inlineStr"/>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AT149" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AU149" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr"/>
+      <c r="BA149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr"/>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr"/>
+      <c r="BI149" t="inlineStr"/>
+      <c r="BJ149" t="inlineStr"/>
+      <c r="BK149" t="inlineStr"/>
+      <c r="BL149" t="inlineStr"/>
+      <c r="BM149" t="inlineStr"/>
+      <c r="BN149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>21.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>28 500</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="inlineStr"/>
+      <c r="AP150" t="inlineStr"/>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AT150" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AU150" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr"/>
+      <c r="BA150" t="inlineStr"/>
+      <c r="BB150" t="inlineStr"/>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr"/>
+      <c r="BI150" t="inlineStr"/>
+      <c r="BJ150" t="inlineStr"/>
+      <c r="BK150" t="inlineStr"/>
+      <c r="BL150" t="inlineStr"/>
+      <c r="BM150" t="inlineStr"/>
+      <c r="BN150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>21.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>39 516</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="inlineStr"/>
+      <c r="AP151" t="inlineStr"/>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AT151" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AU151" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr"/>
+      <c r="BA151" t="inlineStr"/>
+      <c r="BB151" t="inlineStr"/>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
+      <c r="BI151" t="inlineStr"/>
+      <c r="BJ151" t="inlineStr"/>
+      <c r="BK151" t="inlineStr"/>
+      <c r="BL151" t="inlineStr"/>
+      <c r="BM151" t="inlineStr"/>
+      <c r="BN151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>23 106</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr"/>
+      <c r="AO152" t="inlineStr"/>
+      <c r="AP152" t="inlineStr"/>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AU152" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr"/>
+      <c r="BA152" t="inlineStr"/>
+      <c r="BB152" t="inlineStr"/>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
+      <c r="BI152" t="inlineStr"/>
+      <c r="BJ152" t="inlineStr"/>
+      <c r="BK152" t="inlineStr"/>
+      <c r="BL152" t="inlineStr"/>
+      <c r="BM152" t="inlineStr"/>
+      <c r="BN152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>15.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>38 116</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr"/>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="AN153" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AT153" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AU153" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr"/>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
+      <c r="BI153" t="inlineStr"/>
+      <c r="BJ153" t="inlineStr"/>
+      <c r="BK153" t="inlineStr"/>
+      <c r="BL153" t="inlineStr"/>
+      <c r="BM153" t="inlineStr"/>
+      <c r="BN153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>29 811</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AN154" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AT154" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AU154" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr"/>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
+      <c r="BI154" t="inlineStr"/>
+      <c r="BJ154" t="inlineStr"/>
+      <c r="BK154" t="inlineStr"/>
+      <c r="BL154" t="inlineStr"/>
+      <c r="BM154" t="inlineStr"/>
+      <c r="BN154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>19 135</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AN155" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AT155" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AU155" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr"/>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
+      <c r="BI155" t="inlineStr"/>
+      <c r="BJ155" t="inlineStr"/>
+      <c r="BK155" t="inlineStr"/>
+      <c r="BL155" t="inlineStr"/>
+      <c r="BM155" t="inlineStr"/>
+      <c r="BN155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>30 097</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN156" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AT156" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AU156" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr"/>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr"/>
+      <c r="BD156" t="inlineStr"/>
+      <c r="BE156" t="inlineStr"/>
+      <c r="BF156" t="inlineStr"/>
+      <c r="BG156" t="inlineStr"/>
+      <c r="BH156" t="inlineStr"/>
+      <c r="BI156" t="inlineStr"/>
+      <c r="BJ156" t="inlineStr"/>
+      <c r="BK156" t="inlineStr"/>
+      <c r="BL156" t="inlineStr"/>
+      <c r="BM156" t="inlineStr"/>
+      <c r="BN156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>hCffxjZi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>27 451</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AU157" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr"/>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr"/>
+      <c r="BD157" t="inlineStr"/>
+      <c r="BE157" t="inlineStr"/>
+      <c r="BF157" t="inlineStr"/>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr"/>
+      <c r="BI157" t="inlineStr"/>
+      <c r="BJ157" t="inlineStr"/>
+      <c r="BK157" t="inlineStr"/>
+      <c r="BL157" t="inlineStr"/>
+      <c r="BM157" t="inlineStr"/>
+      <c r="BN157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>8MPiooIM</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>14.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Turpin C.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>47 628</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AN158" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AU158" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr"/>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr"/>
+      <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="inlineStr"/>
+      <c r="BI158" t="inlineStr"/>
+      <c r="BJ158" t="inlineStr"/>
+      <c r="BK158" t="inlineStr"/>
+      <c r="BL158" t="inlineStr"/>
+      <c r="BM158" t="inlineStr"/>
+      <c r="BN158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>WQczyE7L</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>21.09.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>17 970</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN159" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AT159" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AU159" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr"/>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BH159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK159" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BM159" t="inlineStr"/>
+      <c r="BN159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>d8sFTVae</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>5 405</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AN160" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AU160" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr"/>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BH160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BI160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK160" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM160" t="inlineStr"/>
+      <c r="BN160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>tM09MEhS</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>10 642</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr"/>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AN161" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AT161" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AU161" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="BD161" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BH161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BI161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK161" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BM161" t="inlineStr"/>
+      <c r="BN161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>ULuNR9U7</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>13 650</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AT162" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AU162" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr"/>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="BD162" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="BE162" t="inlineStr"/>
+      <c r="BF162" t="inlineStr"/>
+      <c r="BG162" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH162" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BI162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK162" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL162" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BM162" t="inlineStr"/>
+      <c r="BN162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>r5HuFWp2</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>3 121</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AN163" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AU163" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr"/>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="BD163" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="BE163" t="inlineStr"/>
+      <c r="BF163" t="inlineStr"/>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BH163" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BI163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ163" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK163" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL163" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM163" t="inlineStr"/>
+      <c r="BN163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>xhnuHhGk</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>6 464</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AN164" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AU164" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr"/>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="BD164" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="BH164" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BI164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ164" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK164" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL164" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BM164" t="inlineStr"/>
+      <c r="BN164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>pf70OzOF</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Paradis G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1 359</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN165" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AT165" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AU165" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH165" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BI165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BL165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM165" t="inlineStr"/>
+      <c r="BN165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>AB9Rxzw9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>4 560</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="AN166" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AU166" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr"/>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BH166" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BI166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK166" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BM166" t="inlineStr"/>
+      <c r="BN166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>OnFinJal</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>4 311</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AU167" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr"/>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BH167" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BI167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ167" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BL167" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM167" t="inlineStr"/>
+      <c r="BN167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>4GNqcbPG</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>16.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>4 079</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AU168" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr"/>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr"/>
+      <c r="BN168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN168"/>
+  <dimension ref="A1:BN177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32040,15 +32040,11 @@
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G144" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -32070,15 +32066,11 @@
           <t>Marseille</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
+      <c r="M144" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.98</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -32090,115 +32082,71 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q144" t="n">
+        <v>18</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6</v>
+      </c>
+      <c r="S144" t="n">
+        <v>9</v>
+      </c>
+      <c r="T144" t="n">
+        <v>5</v>
+      </c>
+      <c r="U144" t="n">
+        <v>6</v>
+      </c>
+      <c r="V144" t="n">
+        <v>1</v>
+      </c>
+      <c r="W144" t="n">
+        <v>3</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>3</v>
       </c>
       <c r="AM144" t="inlineStr"/>
       <c r="AN144" t="inlineStr"/>
@@ -32238,15 +32186,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>1</v>
       </c>
       <c r="BA144" t="inlineStr"/>
       <c r="BB144" t="inlineStr"/>
@@ -32292,15 +32236,11 @@
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -32322,15 +32262,11 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
+      <c r="M145" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.78</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -32342,115 +32278,71 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q145" t="n">
+        <v>4</v>
+      </c>
+      <c r="R145" t="n">
+        <v>9</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" t="n">
+        <v>3</v>
+      </c>
+      <c r="U145" t="n">
+        <v>2</v>
+      </c>
+      <c r="V145" t="n">
+        <v>2</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1</v>
+      </c>
+      <c r="X145" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>4</v>
       </c>
       <c r="AM145" t="inlineStr"/>
       <c r="AN145" t="inlineStr"/>
@@ -32536,15 +32428,11 @@
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -32566,15 +32454,11 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
+      <c r="M146" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2.08</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -32586,115 +32470,71 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q146" t="n">
+        <v>9</v>
+      </c>
+      <c r="R146" t="n">
+        <v>10</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2</v>
+      </c>
+      <c r="V146" t="n">
+        <v>8</v>
+      </c>
+      <c r="W146" t="n">
+        <v>2</v>
+      </c>
+      <c r="X146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1</v>
       </c>
       <c r="AM146" t="inlineStr"/>
       <c r="AN146" t="inlineStr"/>
@@ -32780,15 +32620,11 @@
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -32810,15 +32646,11 @@
           <t>Auxerre</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
+      <c r="M147" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1.36</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -32830,115 +32662,71 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q147" t="n">
+        <v>14</v>
+      </c>
+      <c r="R147" t="n">
+        <v>11</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="n">
+        <v>6</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3</v>
+      </c>
+      <c r="W147" t="n">
+        <v>3</v>
+      </c>
+      <c r="X147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>4</v>
       </c>
       <c r="AM147" t="inlineStr"/>
       <c r="AN147" t="inlineStr"/>
@@ -33024,15 +32812,11 @@
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G148" t="n">
+        <v>3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -33054,15 +32838,11 @@
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
+      <c r="M148" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0.38</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -33074,115 +32854,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q148" t="n">
+        <v>14</v>
+      </c>
+      <c r="R148" t="n">
+        <v>9</v>
+      </c>
+      <c r="S148" t="n">
+        <v>4</v>
+      </c>
+      <c r="T148" t="n">
+        <v>2</v>
+      </c>
+      <c r="U148" t="n">
+        <v>8</v>
+      </c>
+      <c r="V148" t="n">
+        <v>6</v>
+      </c>
+      <c r="W148" t="n">
+        <v>2</v>
+      </c>
+      <c r="X148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>3</v>
       </c>
       <c r="AM148" t="inlineStr"/>
       <c r="AN148" t="inlineStr"/>
@@ -33272,15 +33008,11 @@
           <t>20 220</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -33302,15 +33034,11 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
+      <c r="M149" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.98</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -33322,115 +33050,71 @@
           <t>78%</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q149" t="n">
+        <v>8</v>
+      </c>
+      <c r="R149" t="n">
+        <v>11</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" t="n">
+        <v>4</v>
+      </c>
+      <c r="U149" t="n">
+        <v>3</v>
+      </c>
+      <c r="V149" t="n">
+        <v>4</v>
+      </c>
+      <c r="W149" t="n">
+        <v>4</v>
+      </c>
+      <c r="X149" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1</v>
       </c>
       <c r="AM149" t="inlineStr"/>
       <c r="AN149" t="inlineStr"/>
@@ -33520,15 +33204,11 @@
           <t>28 500</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -33550,15 +33230,11 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
+      <c r="M150" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.88</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -33570,115 +33246,71 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q150" t="n">
+        <v>11</v>
+      </c>
+      <c r="R150" t="n">
+        <v>10</v>
+      </c>
+      <c r="S150" t="n">
+        <v>6</v>
+      </c>
+      <c r="T150" t="n">
+        <v>2</v>
+      </c>
+      <c r="U150" t="n">
+        <v>3</v>
+      </c>
+      <c r="V150" t="n">
+        <v>3</v>
+      </c>
+      <c r="W150" t="n">
+        <v>2</v>
+      </c>
+      <c r="X150" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>4</v>
       </c>
       <c r="AM150" t="inlineStr"/>
       <c r="AN150" t="inlineStr"/>
@@ -33768,15 +33400,11 @@
           <t>39 516</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G151" t="n">
+        <v>3</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -33798,15 +33426,11 @@
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
+      <c r="M151" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2.93</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -33818,115 +33442,71 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q151" t="n">
+        <v>15</v>
+      </c>
+      <c r="R151" t="n">
+        <v>12</v>
+      </c>
+      <c r="S151" t="n">
+        <v>7</v>
+      </c>
+      <c r="T151" t="n">
+        <v>9</v>
+      </c>
+      <c r="U151" t="n">
+        <v>6</v>
+      </c>
+      <c r="V151" t="n">
+        <v>1</v>
+      </c>
+      <c r="W151" t="n">
+        <v>2</v>
+      </c>
+      <c r="X151" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>2</v>
       </c>
       <c r="AM151" t="inlineStr"/>
       <c r="AN151" t="inlineStr"/>
@@ -34016,15 +33596,11 @@
           <t>23 106</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G152" t="n">
+        <v>8</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -34046,15 +33622,11 @@
           <t>St Etienne</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
+      <c r="M152" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0.19</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -34066,115 +33638,71 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q152" t="n">
+        <v>18</v>
+      </c>
+      <c r="R152" t="n">
+        <v>8</v>
+      </c>
+      <c r="S152" t="n">
+        <v>12</v>
+      </c>
+      <c r="T152" t="n">
+        <v>2</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2</v>
+      </c>
+      <c r="V152" t="n">
+        <v>4</v>
+      </c>
+      <c r="W152" t="n">
+        <v>4</v>
+      </c>
+      <c r="X152" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1</v>
       </c>
       <c r="AM152" t="inlineStr"/>
       <c r="AN152" t="inlineStr"/>
@@ -34264,15 +33792,11 @@
           <t>38 116</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -34294,15 +33818,11 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+      <c r="M153" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0.43</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -34314,127 +33834,79 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="Q153" t="n">
+        <v>12</v>
+      </c>
+      <c r="R153" t="n">
+        <v>8</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="n">
+        <v>3</v>
+      </c>
+      <c r="U153" t="n">
+        <v>5</v>
+      </c>
+      <c r="V153" t="n">
+        <v>2</v>
+      </c>
+      <c r="W153" t="n">
+        <v>2</v>
+      </c>
+      <c r="X153" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>11</v>
       </c>
       <c r="AK153" t="inlineStr"/>
       <c r="AL153" t="inlineStr"/>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AP153" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="AM153" t="n">
+        <v>147</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>124</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>53</v>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
@@ -34472,15 +33944,11 @@
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr"/>
-      <c r="BA153" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="BB153" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="BA153" t="n">
+        <v>492</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>421</v>
       </c>
       <c r="BC153" t="inlineStr"/>
       <c r="BD153" t="inlineStr"/>
@@ -34528,15 +33996,11 @@
           <t>29 811</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -34558,15 +34022,11 @@
           <t>Reims</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+      <c r="M154" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.53</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -34578,135 +34038,83 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="Q154" t="n">
+        <v>18</v>
+      </c>
+      <c r="R154" t="n">
+        <v>11</v>
+      </c>
+      <c r="S154" t="n">
+        <v>6</v>
+      </c>
+      <c r="T154" t="n">
+        <v>4</v>
+      </c>
+      <c r="U154" t="n">
+        <v>5</v>
+      </c>
+      <c r="V154" t="n">
+        <v>5</v>
+      </c>
+      <c r="W154" t="n">
+        <v>7</v>
+      </c>
+      <c r="X154" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>51</v>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
@@ -34744,15 +34152,11 @@
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr"/>
-      <c r="BA154" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="BB154" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
+      <c r="BA154" t="n">
+        <v>456</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>582</v>
       </c>
       <c r="BC154" t="inlineStr"/>
       <c r="BD154" t="inlineStr"/>
@@ -34800,15 +34204,11 @@
           <t>19 135</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -34830,15 +34230,11 @@
           <t>Angers</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="M155" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0.75</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -34850,135 +34246,83 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AP155" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="Q155" t="n">
+        <v>10</v>
+      </c>
+      <c r="R155" t="n">
+        <v>12</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="n">
+        <v>2</v>
+      </c>
+      <c r="U155" t="n">
+        <v>4</v>
+      </c>
+      <c r="V155" t="n">
+        <v>5</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>82</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>52</v>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
@@ -35016,15 +34360,11 @@
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr"/>
-      <c r="BA155" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="BB155" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
+      <c r="BA155" t="n">
+        <v>469</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>432</v>
       </c>
       <c r="BC155" t="inlineStr"/>
       <c r="BD155" t="inlineStr"/>
@@ -35072,15 +34412,11 @@
           <t>30 097</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -35102,15 +34438,11 @@
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+      <c r="M156" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0.54</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -35122,135 +34454,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="Q156" t="n">
+        <v>15</v>
+      </c>
+      <c r="R156" t="n">
+        <v>5</v>
+      </c>
+      <c r="S156" t="n">
+        <v>7</v>
+      </c>
+      <c r="T156" t="n">
+        <v>3</v>
+      </c>
+      <c r="U156" t="n">
+        <v>4</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2</v>
+      </c>
+      <c r="W156" t="n">
+        <v>4</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>33</v>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
@@ -35288,15 +34568,11 @@
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr"/>
-      <c r="BA156" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="BB156" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
+      <c r="BA156" t="n">
+        <v>520</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>438</v>
       </c>
       <c r="BC156" t="inlineStr"/>
       <c r="BD156" t="inlineStr"/>
@@ -35344,15 +34620,11 @@
           <t>27 451</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G157" t="n">
+        <v>3</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -35374,15 +34646,11 @@
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
+      <c r="M157" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0.31</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -35394,135 +34662,83 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="Q157" t="n">
+        <v>11</v>
+      </c>
+      <c r="R157" t="n">
+        <v>12</v>
+      </c>
+      <c r="S157" t="n">
+        <v>6</v>
+      </c>
+      <c r="T157" t="n">
+        <v>4</v>
+      </c>
+      <c r="U157" t="n">
+        <v>4</v>
+      </c>
+      <c r="V157" t="n">
+        <v>6</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1</v>
+      </c>
+      <c r="X157" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>99</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>59</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>38</v>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
@@ -35560,15 +34776,11 @@
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr"/>
-      <c r="BA157" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="BB157" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
+      <c r="BA157" t="n">
+        <v>452</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>444</v>
       </c>
       <c r="BC157" t="inlineStr"/>
       <c r="BD157" t="inlineStr"/>
@@ -35616,15 +34828,11 @@
           <t>47 628</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G158" t="n">
+        <v>3</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -35646,15 +34854,11 @@
           <t>Brest</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
+      <c r="M158" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0.93</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -35666,135 +34870,83 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Q158" t="n">
+        <v>22</v>
+      </c>
+      <c r="R158" t="n">
+        <v>5</v>
+      </c>
+      <c r="S158" t="n">
+        <v>9</v>
+      </c>
+      <c r="T158" t="n">
+        <v>3</v>
+      </c>
+      <c r="U158" t="n">
+        <v>7</v>
+      </c>
+      <c r="V158" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" t="n">
+        <v>6</v>
+      </c>
+      <c r="X158" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>133</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>22</v>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
@@ -35832,15 +34984,11 @@
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr"/>
-      <c r="BA158" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="BB158" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
+      <c r="BA158" t="n">
+        <v>679</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>333</v>
       </c>
       <c r="BC158" t="inlineStr"/>
       <c r="BD158" t="inlineStr"/>
@@ -35888,15 +35036,11 @@
           <t>17 970</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -35930,119 +35074,75 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q159" t="n">
+        <v>7</v>
+      </c>
+      <c r="R159" t="n">
+        <v>16</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" t="n">
+        <v>5</v>
+      </c>
+      <c r="U159" t="n">
+        <v>4</v>
+      </c>
+      <c r="V159" t="n">
+        <v>7</v>
+      </c>
+      <c r="W159" t="n">
+        <v>2</v>
+      </c>
+      <c r="X159" t="n">
+        <v>4</v>
       </c>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>1</v>
       </c>
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="AG159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>51</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>90</v>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
@@ -36080,65 +35180,41 @@
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr"/>
-      <c r="BA159" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="BB159" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="BC159" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="BD159" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="BE159" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BF159" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG159" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BH159" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK159" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL159" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BA159" t="n">
+        <v>438</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>537</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>355</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>454</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>14</v>
       </c>
       <c r="BM159" t="inlineStr"/>
       <c r="BN159" t="inlineStr"/>
@@ -36176,15 +35252,11 @@
           <t>5 405</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -36218,111 +35290,71 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q160" t="n">
+        <v>12</v>
+      </c>
+      <c r="R160" t="n">
+        <v>16</v>
+      </c>
+      <c r="S160" t="n">
+        <v>6</v>
+      </c>
+      <c r="T160" t="n">
+        <v>3</v>
+      </c>
+      <c r="U160" t="n">
+        <v>3</v>
+      </c>
+      <c r="V160" t="n">
+        <v>10</v>
+      </c>
+      <c r="W160" t="n">
+        <v>3</v>
+      </c>
+      <c r="X160" t="n">
+        <v>3</v>
       </c>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>2</v>
       </c>
       <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr"/>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="AG160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>16</v>
       </c>
       <c r="AK160" t="inlineStr"/>
       <c r="AL160" t="inlineStr"/>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="AM160" t="n">
+        <v>133</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>191</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>141</v>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
@@ -36360,57 +35392,37 @@
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr"/>
-      <c r="BA160" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="BB160" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="BC160" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="BD160" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
+      <c r="BA160" t="n">
+        <v>336</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>610</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>247</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>513</v>
       </c>
       <c r="BE160" t="inlineStr"/>
       <c r="BF160" t="inlineStr"/>
-      <c r="BG160" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BH160" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BI160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ160" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BK160" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL160" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BG160" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>6</v>
       </c>
       <c r="BM160" t="inlineStr"/>
       <c r="BN160" t="inlineStr"/>
@@ -36448,15 +35460,11 @@
           <t>10 642</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -36490,119 +35498,75 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q161" t="n">
+        <v>15</v>
+      </c>
+      <c r="R161" t="n">
+        <v>13</v>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="n">
+        <v>5</v>
+      </c>
+      <c r="U161" t="n">
+        <v>10</v>
+      </c>
+      <c r="V161" t="n">
+        <v>4</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>4</v>
       </c>
       <c r="Y161" t="inlineStr"/>
       <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>1</v>
       </c>
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr"/>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="AG161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>109</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>62</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>64</v>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
@@ -36638,67 +35602,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BA161" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="BB161" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="BC161" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="BD161" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="AY161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>307</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>586</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>233</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>506</v>
       </c>
       <c r="BE161" t="inlineStr"/>
       <c r="BF161" t="inlineStr"/>
-      <c r="BG161" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BH161" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BI161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ161" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK161" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BG161" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>5</v>
       </c>
       <c r="BM161" t="inlineStr"/>
       <c r="BN161" t="inlineStr"/>
@@ -36736,15 +35676,11 @@
           <t>13 650</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -36778,119 +35714,75 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q162" t="n">
+        <v>19</v>
+      </c>
+      <c r="R162" t="n">
+        <v>3</v>
+      </c>
+      <c r="S162" t="n">
+        <v>8</v>
+      </c>
+      <c r="T162" t="n">
+        <v>2</v>
+      </c>
+      <c r="U162" t="n">
+        <v>4</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>7</v>
+      </c>
+      <c r="X162" t="n">
+        <v>1</v>
       </c>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="AA162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>5</v>
       </c>
       <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr"/>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="AG162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>165</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>104</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>52</v>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
@@ -36928,57 +35820,37 @@
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr"/>
-      <c r="BA162" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="BB162" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="BC162" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="BD162" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="BA162" t="n">
+        <v>521</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>323</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>442</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>230</v>
       </c>
       <c r="BE162" t="inlineStr"/>
       <c r="BF162" t="inlineStr"/>
-      <c r="BG162" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH162" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BI162" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK162" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL162" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BG162" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>12</v>
       </c>
       <c r="BM162" t="inlineStr"/>
       <c r="BN162" t="inlineStr"/>
@@ -37016,15 +35888,11 @@
           <t>3 121</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G163" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -37058,119 +35926,75 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q163" t="n">
+        <v>14</v>
+      </c>
+      <c r="R163" t="n">
+        <v>16</v>
+      </c>
+      <c r="S163" t="n">
+        <v>6</v>
+      </c>
+      <c r="T163" t="n">
+        <v>4</v>
+      </c>
+      <c r="U163" t="n">
+        <v>5</v>
+      </c>
+      <c r="V163" t="n">
+        <v>9</v>
+      </c>
+      <c r="W163" t="n">
+        <v>3</v>
+      </c>
+      <c r="X163" t="n">
+        <v>3</v>
       </c>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="AA163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>8</v>
       </c>
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr"/>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="AG163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>66</v>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
@@ -37208,57 +36032,37 @@
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr"/>
-      <c r="BA163" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="BB163" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="BC163" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="BD163" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
+      <c r="BA163" t="n">
+        <v>427</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>387</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>324</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>306</v>
       </c>
       <c r="BE163" t="inlineStr"/>
       <c r="BF163" t="inlineStr"/>
-      <c r="BG163" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH163" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BI163" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ163" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BK163" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL163" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG163" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>7</v>
       </c>
       <c r="BM163" t="inlineStr"/>
       <c r="BN163" t="inlineStr"/>
@@ -37296,15 +36100,11 @@
           <t>6 464</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -37338,119 +36138,75 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q164" t="n">
+        <v>14</v>
+      </c>
+      <c r="R164" t="n">
+        <v>8</v>
+      </c>
+      <c r="S164" t="n">
+        <v>8</v>
+      </c>
+      <c r="T164" t="n">
+        <v>4</v>
+      </c>
+      <c r="U164" t="n">
+        <v>3</v>
+      </c>
+      <c r="V164" t="n">
+        <v>1</v>
+      </c>
+      <c r="W164" t="n">
+        <v>3</v>
+      </c>
+      <c r="X164" t="n">
+        <v>3</v>
       </c>
       <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="inlineStr"/>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA164" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
       </c>
       <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr"/>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="AG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>91</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>51</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>79</v>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
@@ -37488,57 +36244,37 @@
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr"/>
-      <c r="BA164" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="BB164" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="BC164" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="BD164" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+      <c r="BA164" t="n">
+        <v>485</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>317</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>366</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>209</v>
       </c>
       <c r="BE164" t="inlineStr"/>
       <c r="BF164" t="inlineStr"/>
-      <c r="BG164" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="BH164" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BI164" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK164" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL164" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BG164" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>11</v>
       </c>
       <c r="BM164" t="inlineStr"/>
       <c r="BN164" t="inlineStr"/>
@@ -37576,15 +36312,11 @@
           <t>1 359</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -37618,119 +36350,75 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q165" t="n">
+        <v>12</v>
+      </c>
+      <c r="R165" t="n">
+        <v>19</v>
+      </c>
+      <c r="S165" t="n">
+        <v>6</v>
+      </c>
+      <c r="T165" t="n">
+        <v>5</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2</v>
+      </c>
+      <c r="V165" t="n">
+        <v>7</v>
+      </c>
+      <c r="W165" t="n">
+        <v>4</v>
+      </c>
+      <c r="X165" t="n">
+        <v>7</v>
       </c>
       <c r="Y165" t="inlineStr"/>
       <c r="Z165" t="inlineStr"/>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>2</v>
       </c>
       <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr"/>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="AG165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>78</v>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
@@ -37766,67 +36454,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA165" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="BB165" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="BC165" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="BD165" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
+      <c r="AY165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>403</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>668</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>322</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>577</v>
       </c>
       <c r="BE165" t="inlineStr"/>
       <c r="BF165" t="inlineStr"/>
-      <c r="BG165" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH165" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BI165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ165" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK165" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL165" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG165" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>8</v>
       </c>
       <c r="BM165" t="inlineStr"/>
       <c r="BN165" t="inlineStr"/>
@@ -37864,15 +36528,11 @@
           <t>4 560</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -37906,119 +36566,75 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q166" t="n">
+        <v>12</v>
+      </c>
+      <c r="R166" t="n">
+        <v>14</v>
+      </c>
+      <c r="S166" t="n">
+        <v>2</v>
+      </c>
+      <c r="T166" t="n">
+        <v>5</v>
+      </c>
+      <c r="U166" t="n">
+        <v>8</v>
+      </c>
+      <c r="V166" t="n">
+        <v>4</v>
+      </c>
+      <c r="W166" t="n">
+        <v>2</v>
+      </c>
+      <c r="X166" t="n">
+        <v>5</v>
       </c>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="inlineStr"/>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>1</v>
       </c>
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr"/>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AP166" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="AG166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>176</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>64</v>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
@@ -38056,57 +36672,37 @@
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr"/>
-      <c r="BA166" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="BB166" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="BC166" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="BD166" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="BA166" t="n">
+        <v>660</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>327</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>572</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>226</v>
       </c>
       <c r="BE166" t="inlineStr"/>
       <c r="BF166" t="inlineStr"/>
-      <c r="BG166" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BH166" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BI166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK166" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL166" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BG166" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>14</v>
       </c>
       <c r="BM166" t="inlineStr"/>
       <c r="BN166" t="inlineStr"/>
@@ -38144,15 +36740,11 @@
           <t>4 311</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -38186,119 +36778,75 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q167" t="n">
+        <v>14</v>
+      </c>
+      <c r="R167" t="n">
+        <v>17</v>
+      </c>
+      <c r="S167" t="n">
+        <v>2</v>
+      </c>
+      <c r="T167" t="n">
+        <v>5</v>
+      </c>
+      <c r="U167" t="n">
+        <v>6</v>
+      </c>
+      <c r="V167" t="n">
+        <v>9</v>
+      </c>
+      <c r="W167" t="n">
+        <v>6</v>
+      </c>
+      <c r="X167" t="n">
+        <v>3</v>
       </c>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="inlineStr"/>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>2</v>
       </c>
       <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr"/>
-      <c r="AG167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="AG167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>103</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>60</v>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
@@ -38336,57 +36884,37 @@
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr"/>
-      <c r="BA167" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="BB167" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="BC167" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="BD167" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="BA167" t="n">
+        <v>540</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>416</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>433</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>320</v>
       </c>
       <c r="BE167" t="inlineStr"/>
       <c r="BF167" t="inlineStr"/>
-      <c r="BG167" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BH167" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BI167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ167" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK167" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL167" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG167" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>7</v>
       </c>
       <c r="BM167" t="inlineStr"/>
       <c r="BN167" t="inlineStr"/>
@@ -38424,15 +36952,11 @@
           <t>4 079</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G168" t="n">
+        <v>3</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -38466,119 +36990,75 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q168" t="n">
+        <v>12</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6</v>
+      </c>
+      <c r="S168" t="n">
+        <v>5</v>
+      </c>
+      <c r="T168" t="n">
+        <v>4</v>
+      </c>
+      <c r="U168" t="n">
+        <v>5</v>
+      </c>
+      <c r="V168" t="n">
+        <v>2</v>
+      </c>
+      <c r="W168" t="n">
+        <v>2</v>
+      </c>
+      <c r="X168" t="n">
+        <v>0</v>
       </c>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="inlineStr"/>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
       </c>
       <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr"/>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL168" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP168" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="AG168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>128</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>49</v>
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
@@ -38616,68 +37096,2644 @@
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr"/>
-      <c r="BA168" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="BB168" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="BC168" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="BD168" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="BE168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BF168" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BG168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH168" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BI168" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK168" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BL168" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BA168" t="n">
+        <v>370</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>329</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>306</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>267</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>7</v>
       </c>
       <c r="BM168" t="inlineStr"/>
       <c r="BN168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Aw6Go4Lt</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>3 000</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr"/>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AU169" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr"/>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BH169" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BL169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM169" t="inlineStr"/>
+      <c r="BN169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>rkVhpcU0</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Parc des Sports
+ (Annecy)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>15 660</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>4 005</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr"/>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AN170" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AU170" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr"/>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BH170" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BI170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ170" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BK170" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BL170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM170" t="inlineStr"/>
+      <c r="BN170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>pUN9kDME</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>14 204</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr"/>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AN171" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AU171" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr"/>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH171" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BI171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK171" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL171" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BM171" t="inlineStr"/>
+      <c r="BN171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>bDHWsMK5</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>4 556</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr"/>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AU172" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr"/>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BH172" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BI172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM172" t="inlineStr"/>
+      <c r="BN172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>65aPqrjg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Legat P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>3 636</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN173" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AU173" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr"/>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BH173" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BI173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL173" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BM173" t="inlineStr"/>
+      <c r="BN173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>CrvjVry0</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>16 675</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AU174" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr"/>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="BE174" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BF174" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BH174" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BI174" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK174" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM174" t="inlineStr"/>
+      <c r="BN174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>baxbTM5C</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Paradis G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Stade Charlety
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>6 448</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AU175" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr"/>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr"/>
+      <c r="BN175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>fRV6R0zP</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Petit A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nouste Camp
+ (Pau)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>4 031</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>3 054</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr"/>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AU176" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="BE176" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BF176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH176" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BI176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK176" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL176" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>KS5ut0kI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>24.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Leleu M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Stade Paul-Lignon
+ (Rodez)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>5 955</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>4 017</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AU177" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr"/>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BF177" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BH177" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BI177" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BJ177" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL177" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN177"/>
+  <dimension ref="A1:BN190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37168,15 +37168,11 @@
           <t>3 000</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -37210,119 +37206,75 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q169" t="n">
+        <v>12</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7</v>
+      </c>
+      <c r="S169" t="n">
+        <v>3</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3</v>
+      </c>
+      <c r="V169" t="n">
+        <v>5</v>
+      </c>
+      <c r="W169" t="n">
+        <v>6</v>
+      </c>
+      <c r="X169" t="n">
+        <v>1</v>
       </c>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA169" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>2</v>
       </c>
       <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr"/>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AP169" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="AG169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>73</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>52</v>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
@@ -37360,65 +37312,41 @@
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr"/>
-      <c r="BA169" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="BB169" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="BC169" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="BD169" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="BE169" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF169" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BG169" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BH169" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BI169" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK169" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BL169" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BA169" t="n">
+        <v>392</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>267</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>354</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>8</v>
       </c>
       <c r="BM169" t="inlineStr"/>
       <c r="BN169" t="inlineStr"/>
@@ -37456,15 +37384,11 @@
           <t>4 005</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -37498,119 +37422,75 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q170" t="n">
+        <v>9</v>
+      </c>
+      <c r="R170" t="n">
+        <v>18</v>
+      </c>
+      <c r="S170" t="n">
+        <v>2</v>
+      </c>
+      <c r="T170" t="n">
+        <v>3</v>
+      </c>
+      <c r="U170" t="n">
+        <v>6</v>
+      </c>
+      <c r="V170" t="n">
+        <v>8</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1</v>
+      </c>
+      <c r="X170" t="n">
+        <v>7</v>
       </c>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="inlineStr"/>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>3</v>
       </c>
       <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr"/>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="AG170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>92</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>149</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>51</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>109</v>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
@@ -37648,65 +37528,41 @@
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr"/>
-      <c r="BA170" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="BB170" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="BC170" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="BD170" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="BE170" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BF170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BG170" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="BH170" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BI170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ170" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BK170" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BL170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BA170" t="n">
+        <v>240</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>443</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>134</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>311</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>8</v>
       </c>
       <c r="BM170" t="inlineStr"/>
       <c r="BN170" t="inlineStr"/>
@@ -37744,15 +37600,11 @@
           <t>14 204</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -37786,119 +37638,75 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q171" t="n">
+        <v>15</v>
+      </c>
+      <c r="R171" t="n">
+        <v>7</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3</v>
+      </c>
+      <c r="T171" t="n">
+        <v>4</v>
+      </c>
+      <c r="U171" t="n">
+        <v>8</v>
+      </c>
+      <c r="V171" t="n">
+        <v>3</v>
+      </c>
+      <c r="W171" t="n">
+        <v>4</v>
+      </c>
+      <c r="X171" t="n">
+        <v>0</v>
       </c>
       <c r="Y171" t="inlineStr"/>
       <c r="Z171" t="inlineStr"/>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>2</v>
       </c>
       <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr"/>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="AG171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>102</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>108</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>55</v>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
@@ -37936,65 +37744,41 @@
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr"/>
-      <c r="BA171" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="BB171" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="BC171" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="BD171" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="BE171" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BF171" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BG171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH171" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BI171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK171" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL171" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BA171" t="n">
+        <v>564</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>407</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>506</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>335</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>37</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>14</v>
       </c>
       <c r="BM171" t="inlineStr"/>
       <c r="BN171" t="inlineStr"/>
@@ -38032,15 +37816,11 @@
           <t>4 556</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -38074,119 +37854,75 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q172" t="n">
+        <v>11</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6</v>
+      </c>
+      <c r="S172" t="n">
+        <v>4</v>
+      </c>
+      <c r="T172" t="n">
+        <v>3</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>3</v>
+      </c>
+      <c r="W172" t="n">
+        <v>4</v>
+      </c>
+      <c r="X172" t="n">
+        <v>0</v>
       </c>
       <c r="Y172" t="inlineStr"/>
       <c r="Z172" t="inlineStr"/>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>1</v>
       </c>
       <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr"/>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="AG172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>84</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>72</v>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
@@ -38224,65 +37960,41 @@
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr"/>
-      <c r="BA172" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="BB172" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="BC172" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="BD172" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="BE172" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF172" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BG172" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH172" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BI172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BL172" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BA172" t="n">
+        <v>456</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>439</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>358</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>357</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>6</v>
       </c>
       <c r="BM172" t="inlineStr"/>
       <c r="BN172" t="inlineStr"/>
@@ -38320,15 +38032,11 @@
           <t>3 636</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G173" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -38362,119 +38070,75 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q173" t="n">
+        <v>12</v>
+      </c>
+      <c r="R173" t="n">
+        <v>11</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3</v>
+      </c>
+      <c r="T173" t="n">
+        <v>4</v>
+      </c>
+      <c r="U173" t="n">
+        <v>4</v>
+      </c>
+      <c r="V173" t="n">
+        <v>6</v>
+      </c>
+      <c r="W173" t="n">
+        <v>5</v>
+      </c>
+      <c r="X173" t="n">
+        <v>1</v>
       </c>
       <c r="Y173" t="inlineStr"/>
       <c r="Z173" t="inlineStr"/>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AA173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>10</v>
       </c>
       <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr"/>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="AG173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>45</v>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
@@ -38512,65 +38176,41 @@
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr"/>
-      <c r="BA173" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="BB173" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="BC173" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="BD173" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="BE173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BF173" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BG173" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BH173" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BI173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL173" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BA173" t="n">
+        <v>446</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>377</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>343</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>278</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>13</v>
       </c>
       <c r="BM173" t="inlineStr"/>
       <c r="BN173" t="inlineStr"/>
@@ -38608,15 +38248,11 @@
           <t>16 675</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G174" t="n">
+        <v>6</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -38650,119 +38286,75 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q174" t="n">
+        <v>18</v>
+      </c>
+      <c r="R174" t="n">
+        <v>12</v>
+      </c>
+      <c r="S174" t="n">
+        <v>9</v>
+      </c>
+      <c r="T174" t="n">
+        <v>5</v>
+      </c>
+      <c r="U174" t="n">
+        <v>8</v>
+      </c>
+      <c r="V174" t="n">
+        <v>4</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1</v>
+      </c>
+      <c r="X174" t="n">
+        <v>3</v>
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="inlineStr"/>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>0</v>
       </c>
       <c r="AE174" t="inlineStr"/>
       <c r="AF174" t="inlineStr"/>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="AG174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>111</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>106</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>44</v>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
@@ -38800,65 +38392,41 @@
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr"/>
-      <c r="BA174" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="BB174" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="BC174" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="BD174" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="BE174" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BF174" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BG174" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH174" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BI174" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK174" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BA174" t="n">
+        <v>707</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>334</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>651</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>254</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>8</v>
       </c>
       <c r="BM174" t="inlineStr"/>
       <c r="BN174" t="inlineStr"/>
@@ -38896,15 +38464,11 @@
           <t>6 448</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G175" t="n">
+        <v>2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -38938,119 +38502,75 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q175" t="n">
+        <v>10</v>
+      </c>
+      <c r="R175" t="n">
+        <v>9</v>
+      </c>
+      <c r="S175" t="n">
+        <v>8</v>
+      </c>
+      <c r="T175" t="n">
+        <v>5</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>3</v>
+      </c>
+      <c r="W175" t="n">
+        <v>2</v>
+      </c>
+      <c r="X175" t="n">
+        <v>1</v>
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>2</v>
       </c>
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr"/>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="AG175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>48</v>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
@@ -39088,65 +38608,41 @@
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr"/>
-      <c r="BA175" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="BB175" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="BC175" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="BD175" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="BE175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BF175" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BG175" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BI175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL175" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BA175" t="n">
+        <v>550</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>473</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>475</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>407</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>17</v>
       </c>
       <c r="BM175" t="inlineStr"/>
       <c r="BN175" t="inlineStr"/>
@@ -39184,15 +38680,11 @@
           <t>3 054</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -39226,119 +38718,75 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q176" t="n">
+        <v>19</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6</v>
+      </c>
+      <c r="S176" t="n">
+        <v>7</v>
+      </c>
+      <c r="T176" t="n">
+        <v>2</v>
+      </c>
+      <c r="U176" t="n">
+        <v>5</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2</v>
+      </c>
+      <c r="W176" t="n">
+        <v>7</v>
+      </c>
+      <c r="X176" t="n">
+        <v>2</v>
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="inlineStr"/>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>2</v>
       </c>
       <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr"/>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="AG176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>25</v>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
@@ -39374,75 +38822,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA176" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="BB176" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="BC176" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="BD176" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="BE176" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BF176" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BG176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH176" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BI176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK176" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL176" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="AY176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>470</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>425</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>413</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>350</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>13</v>
       </c>
       <c r="BM176" t="inlineStr"/>
       <c r="BN176" t="inlineStr"/>
@@ -39480,15 +38900,11 @@
           <t>4 017</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -39522,119 +38938,75 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q177" t="n">
+        <v>14</v>
+      </c>
+      <c r="R177" t="n">
+        <v>10</v>
+      </c>
+      <c r="S177" t="n">
+        <v>2</v>
+      </c>
+      <c r="T177" t="n">
+        <v>6</v>
+      </c>
+      <c r="U177" t="n">
+        <v>8</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>4</v>
+      </c>
+      <c r="X177" t="n">
+        <v>4</v>
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>1</v>
       </c>
       <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr"/>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="AG177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>135</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>112</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>77</v>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
@@ -39672,68 +39044,3428 @@
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr"/>
-      <c r="BA177" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="BB177" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="BC177" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="BD177" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="BE177" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BF177" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BG177" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BH177" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BI177" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ177" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK177" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL177" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BA177" t="n">
+        <v>361</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>409</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>264</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>298</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>17</v>
       </c>
       <c r="BM177" t="inlineStr"/>
       <c r="BN177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>28.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr"/>
+      <c r="AP178" t="inlineStr"/>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AU178" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>28.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="inlineStr"/>
+      <c r="AO179" t="inlineStr"/>
+      <c r="AP179" t="inlineStr"/>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AU179" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr"/>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr"/>
+      <c r="BM179" t="inlineStr"/>
+      <c r="BN179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>28.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>37 301</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr"/>
+      <c r="AN180" t="inlineStr"/>
+      <c r="AO180" t="inlineStr"/>
+      <c r="AP180" t="inlineStr"/>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AU180" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="inlineStr"/>
+      <c r="BM180" t="inlineStr"/>
+      <c r="BN180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>27.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>47 000</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr"/>
+      <c r="AO181" t="inlineStr"/>
+      <c r="AP181" t="inlineStr"/>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AU181" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr"/>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="inlineStr"/>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr"/>
+      <c r="BM181" t="inlineStr"/>
+      <c r="BN181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>27.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>15 381</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr"/>
+      <c r="AN182" t="inlineStr"/>
+      <c r="AO182" t="inlineStr"/>
+      <c r="AP182" t="inlineStr"/>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AU182" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr"/>
+      <c r="BA182" t="inlineStr"/>
+      <c r="BB182" t="inlineStr"/>
+      <c r="BC182" t="inlineStr"/>
+      <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="inlineStr"/>
+      <c r="BN182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>jFY0ryaD</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>28.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="inlineStr"/>
+      <c r="AP183" t="inlineStr"/>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AU183" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr"/>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="BD183" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
+      <c r="BG183" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BH183" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BI183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK183" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BL183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM183" t="inlineStr"/>
+      <c r="BN183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>8SrDxn0N</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>28.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="inlineStr"/>
+      <c r="AO184" t="inlineStr"/>
+      <c r="AP184" t="inlineStr"/>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AU184" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr"/>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BH184" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI184" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>8nRerjWo</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>4 931</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr"/>
+      <c r="AO185" t="inlineStr"/>
+      <c r="AP185" t="inlineStr"/>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AU185" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
+      <c r="BG185" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BH185" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BI185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL185" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BM185" t="inlineStr"/>
+      <c r="BN185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>t0P3tU0b</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>10 578</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="inlineStr"/>
+      <c r="AO186" t="inlineStr"/>
+      <c r="AP186" t="inlineStr"/>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AU186" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr"/>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK186" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM186" t="inlineStr"/>
+      <c r="BN186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Sh9mvvKU</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>4 176</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr"/>
+      <c r="AO187" t="inlineStr"/>
+      <c r="AP187" t="inlineStr"/>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AU187" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BI187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL187" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BM187" t="inlineStr"/>
+      <c r="BN187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>h0KqXPNp</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Stade Francis Le Basser
+ (Laval)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>5 994</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr"/>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr"/>
+      <c r="AO188" t="inlineStr"/>
+      <c r="AP188" t="inlineStr"/>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AU188" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr"/>
+      <c r="BA188" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="BD188" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BH188" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BI188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL188" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>K6CVfTFi</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Stade du Moustoir
+ (Lorient)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>16 787</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>10 042</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr"/>
+      <c r="AO189" t="inlineStr"/>
+      <c r="AP189" t="inlineStr"/>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AU189" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="BD189" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BH189" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="BI189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>02u5v8VA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr"/>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr"/>
+      <c r="AO190" t="inlineStr"/>
+      <c r="AP190" t="inlineStr"/>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AU190" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>555</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="BH190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN190"/>
+  <dimension ref="A1:BN194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39112,15 +39112,11 @@
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -39142,15 +39138,11 @@
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+      <c r="M178" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0.79</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -39162,115 +39154,71 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q178" t="n">
+        <v>21</v>
+      </c>
+      <c r="R178" t="n">
+        <v>9</v>
+      </c>
+      <c r="S178" t="n">
+        <v>7</v>
+      </c>
+      <c r="T178" t="n">
+        <v>4</v>
+      </c>
+      <c r="U178" t="n">
+        <v>10</v>
+      </c>
+      <c r="V178" t="n">
+        <v>3</v>
+      </c>
+      <c r="W178" t="n">
+        <v>4</v>
+      </c>
+      <c r="X178" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>3</v>
       </c>
       <c r="AM178" t="inlineStr"/>
       <c r="AN178" t="inlineStr"/>
@@ -39310,15 +39258,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>1</v>
       </c>
       <c r="BA178" t="inlineStr"/>
       <c r="BB178" t="inlineStr"/>
@@ -39364,15 +39308,11 @@
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -39394,15 +39334,11 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
+      <c r="M179" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N179" t="n">
+        <v>4.14</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -39414,115 +39350,71 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q179" t="n">
+        <v>7</v>
+      </c>
+      <c r="R179" t="n">
+        <v>18</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4</v>
+      </c>
+      <c r="T179" t="n">
+        <v>10</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2</v>
+      </c>
+      <c r="V179" t="n">
+        <v>5</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1</v>
+      </c>
+      <c r="X179" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1</v>
       </c>
       <c r="AM179" t="inlineStr"/>
       <c r="AN179" t="inlineStr"/>
@@ -39612,15 +39504,11 @@
           <t>37 301</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -39642,15 +39530,11 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
+      <c r="M180" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0.8</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -39662,115 +39546,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q180" t="n">
+        <v>22</v>
+      </c>
+      <c r="R180" t="n">
+        <v>15</v>
+      </c>
+      <c r="S180" t="n">
+        <v>7</v>
+      </c>
+      <c r="T180" t="n">
+        <v>4</v>
+      </c>
+      <c r="U180" t="n">
+        <v>10</v>
+      </c>
+      <c r="V180" t="n">
+        <v>6</v>
+      </c>
+      <c r="W180" t="n">
+        <v>5</v>
+      </c>
+      <c r="X180" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>2</v>
       </c>
       <c r="AM180" t="inlineStr"/>
       <c r="AN180" t="inlineStr"/>
@@ -39810,15 +39650,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>0</v>
       </c>
       <c r="BA180" t="inlineStr"/>
       <c r="BB180" t="inlineStr"/>
@@ -39868,15 +39704,11 @@
           <t>47 000</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -39898,15 +39730,11 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
+      <c r="M181" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1.43</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -39918,115 +39746,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q181" t="n">
+        <v>24</v>
+      </c>
+      <c r="R181" t="n">
+        <v>12</v>
+      </c>
+      <c r="S181" t="n">
+        <v>8</v>
+      </c>
+      <c r="T181" t="n">
+        <v>5</v>
+      </c>
+      <c r="U181" t="n">
+        <v>10</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3</v>
+      </c>
+      <c r="W181" t="n">
+        <v>6</v>
+      </c>
+      <c r="X181" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>3</v>
       </c>
       <c r="AM181" t="inlineStr"/>
       <c r="AN181" t="inlineStr"/>
@@ -40116,15 +39900,11 @@
           <t>15 381</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -40146,15 +39926,11 @@
           <t>Brest</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
+      <c r="M182" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0.62</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -40166,115 +39942,71 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q182" t="n">
+        <v>15</v>
+      </c>
+      <c r="R182" t="n">
+        <v>8</v>
+      </c>
+      <c r="S182" t="n">
+        <v>4</v>
+      </c>
+      <c r="T182" t="n">
+        <v>4</v>
+      </c>
+      <c r="U182" t="n">
+        <v>6</v>
+      </c>
+      <c r="V182" t="n">
+        <v>4</v>
+      </c>
+      <c r="W182" t="n">
+        <v>5</v>
+      </c>
+      <c r="X182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>0</v>
       </c>
       <c r="AM182" t="inlineStr"/>
       <c r="AN182" t="inlineStr"/>
@@ -40360,15 +40092,11 @@
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -40402,99 +40130,63 @@
           <t>79%</t>
         </is>
       </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q183" t="n">
+        <v>6</v>
+      </c>
+      <c r="R183" t="n">
+        <v>12</v>
+      </c>
+      <c r="S183" t="n">
+        <v>5</v>
+      </c>
+      <c r="T183" t="n">
+        <v>2</v>
+      </c>
+      <c r="U183" t="n">
+        <v>1</v>
+      </c>
+      <c r="V183" t="n">
+        <v>7</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" t="n">
+        <v>3</v>
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="inlineStr"/>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>3</v>
       </c>
       <c r="AE183" t="inlineStr"/>
       <c r="AF183" t="inlineStr"/>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>2</v>
       </c>
       <c r="AM183" t="inlineStr"/>
       <c r="AN183" t="inlineStr"/>
@@ -40536,57 +40228,37 @@
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr"/>
-      <c r="BA183" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="BB183" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="BC183" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="BD183" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
+      <c r="BA183" t="n">
+        <v>224</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>807</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>138</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>734</v>
       </c>
       <c r="BE183" t="inlineStr"/>
       <c r="BF183" t="inlineStr"/>
-      <c r="BG183" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BH183" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BI183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK183" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BL183" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG183" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>19</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>8</v>
       </c>
       <c r="BM183" t="inlineStr"/>
       <c r="BN183" t="inlineStr"/>
@@ -40620,15 +40292,11 @@
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>3</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -40662,99 +40330,63 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q184" t="n">
+        <v>12</v>
+      </c>
+      <c r="R184" t="n">
+        <v>11</v>
+      </c>
+      <c r="S184" t="n">
+        <v>4</v>
+      </c>
+      <c r="T184" t="n">
+        <v>6</v>
+      </c>
+      <c r="U184" t="n">
+        <v>7</v>
+      </c>
+      <c r="V184" t="n">
+        <v>3</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1</v>
+      </c>
+      <c r="X184" t="n">
+        <v>2</v>
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="inlineStr"/>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA184" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>0</v>
       </c>
       <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr"/>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>2</v>
       </c>
       <c r="AM184" t="inlineStr"/>
       <c r="AN184" t="inlineStr"/>
@@ -40796,57 +40428,37 @@
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr"/>
-      <c r="BA184" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="BB184" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="BC184" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="BD184" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
+      <c r="BA184" t="n">
+        <v>461</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>503</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>402</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>432</v>
       </c>
       <c r="BE184" t="inlineStr"/>
       <c r="BF184" t="inlineStr"/>
-      <c r="BG184" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BH184" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BI184" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BG184" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>10</v>
       </c>
       <c r="BM184" t="inlineStr"/>
       <c r="BN184" t="inlineStr"/>
@@ -40884,15 +40496,11 @@
           <t>4 931</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -40926,99 +40534,63 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q185" t="n">
+        <v>20</v>
+      </c>
+      <c r="R185" t="n">
+        <v>12</v>
+      </c>
+      <c r="S185" t="n">
+        <v>11</v>
+      </c>
+      <c r="T185" t="n">
+        <v>3</v>
+      </c>
+      <c r="U185" t="n">
+        <v>3</v>
+      </c>
+      <c r="V185" t="n">
+        <v>6</v>
+      </c>
+      <c r="W185" t="n">
+        <v>6</v>
+      </c>
+      <c r="X185" t="n">
+        <v>3</v>
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="inlineStr"/>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>0</v>
       </c>
       <c r="AE185" t="inlineStr"/>
       <c r="AF185" t="inlineStr"/>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AG185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>4</v>
       </c>
       <c r="AM185" t="inlineStr"/>
       <c r="AN185" t="inlineStr"/>
@@ -41058,67 +40630,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA185" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="BB185" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="BC185" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="BD185" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="AY185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>503</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>307</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>407</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>224</v>
       </c>
       <c r="BE185" t="inlineStr"/>
       <c r="BF185" t="inlineStr"/>
-      <c r="BG185" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BH185" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BI185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BJ185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BK185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL185" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG185" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>15</v>
       </c>
       <c r="BM185" t="inlineStr"/>
       <c r="BN185" t="inlineStr"/>
@@ -41156,15 +40704,11 @@
           <t>10 578</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -41198,99 +40742,63 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q186" t="n">
+        <v>20</v>
+      </c>
+      <c r="R186" t="n">
+        <v>9</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="n">
+        <v>2</v>
+      </c>
+      <c r="U186" t="n">
+        <v>8</v>
+      </c>
+      <c r="V186" t="n">
+        <v>4</v>
+      </c>
+      <c r="W186" t="n">
+        <v>2</v>
+      </c>
+      <c r="X186" t="n">
+        <v>3</v>
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="inlineStr"/>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>2</v>
       </c>
       <c r="AE186" t="inlineStr"/>
       <c r="AF186" t="inlineStr"/>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AG186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>4</v>
       </c>
       <c r="AM186" t="inlineStr"/>
       <c r="AN186" t="inlineStr"/>
@@ -41332,57 +40840,37 @@
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr"/>
-      <c r="BA186" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="BB186" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="BC186" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="BD186" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="BA186" t="n">
+        <v>418</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>332</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>277</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>192</v>
       </c>
       <c r="BE186" t="inlineStr"/>
       <c r="BF186" t="inlineStr"/>
-      <c r="BG186" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="BH186" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BI186" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK186" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG186" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>8</v>
       </c>
       <c r="BM186" t="inlineStr"/>
       <c r="BN186" t="inlineStr"/>
@@ -41420,15 +40908,11 @@
           <t>4 176</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G187" t="n">
+        <v>3</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -41462,99 +40946,63 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q187" t="n">
+        <v>10</v>
+      </c>
+      <c r="R187" t="n">
+        <v>7</v>
+      </c>
+      <c r="S187" t="n">
+        <v>5</v>
+      </c>
+      <c r="T187" t="n">
+        <v>3</v>
+      </c>
+      <c r="U187" t="n">
+        <v>3</v>
+      </c>
+      <c r="V187" t="n">
+        <v>4</v>
+      </c>
+      <c r="W187" t="n">
+        <v>2</v>
+      </c>
+      <c r="X187" t="n">
+        <v>0</v>
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="inlineStr"/>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>1</v>
       </c>
       <c r="AE187" t="inlineStr"/>
       <c r="AF187" t="inlineStr"/>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1</v>
       </c>
       <c r="AM187" t="inlineStr"/>
       <c r="AN187" t="inlineStr"/>
@@ -41594,67 +41042,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA187" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="BB187" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="BC187" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="BD187" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+      <c r="AY187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>402</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>533</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>310</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>431</v>
       </c>
       <c r="BE187" t="inlineStr"/>
       <c r="BF187" t="inlineStr"/>
-      <c r="BG187" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="BH187" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BI187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK187" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL187" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG187" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>15</v>
       </c>
       <c r="BM187" t="inlineStr"/>
       <c r="BN187" t="inlineStr"/>
@@ -41692,15 +41116,11 @@
           <t>5 994</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -41734,99 +41154,63 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q188" t="n">
+        <v>7</v>
+      </c>
+      <c r="R188" t="n">
+        <v>7</v>
+      </c>
+      <c r="S188" t="n">
+        <v>5</v>
+      </c>
+      <c r="T188" t="n">
+        <v>2</v>
+      </c>
+      <c r="U188" t="n">
+        <v>1</v>
+      </c>
+      <c r="V188" t="n">
+        <v>3</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1</v>
+      </c>
+      <c r="X188" t="n">
+        <v>2</v>
       </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="inlineStr"/>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>1</v>
       </c>
       <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr"/>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL188" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AG188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>6</v>
       </c>
       <c r="AM188" t="inlineStr"/>
       <c r="AN188" t="inlineStr"/>
@@ -41868,57 +41252,37 @@
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr"/>
-      <c r="BA188" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="BB188" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="BC188" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="BD188" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
+      <c r="BA188" t="n">
+        <v>292</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>574</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>190</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>470</v>
       </c>
       <c r="BE188" t="inlineStr"/>
       <c r="BF188" t="inlineStr"/>
-      <c r="BG188" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BH188" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ188" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BK188" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL188" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BG188" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>9</v>
       </c>
       <c r="BM188" t="inlineStr"/>
       <c r="BN188" t="inlineStr"/>
@@ -41956,15 +41320,11 @@
           <t>10 042</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G189" t="n">
+        <v>3</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -41998,99 +41358,63 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q189" t="n">
+        <v>27</v>
+      </c>
+      <c r="R189" t="n">
+        <v>7</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="n">
+        <v>3</v>
+      </c>
+      <c r="U189" t="n">
+        <v>13</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2</v>
+      </c>
+      <c r="W189" t="n">
+        <v>4</v>
+      </c>
+      <c r="X189" t="n">
+        <v>2</v>
       </c>
       <c r="Y189" t="inlineStr"/>
       <c r="Z189" t="inlineStr"/>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA189" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>1</v>
       </c>
       <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr"/>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>2</v>
       </c>
       <c r="AM189" t="inlineStr"/>
       <c r="AN189" t="inlineStr"/>
@@ -42130,67 +41454,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA189" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="BB189" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="BC189" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="BD189" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="AY189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>510</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>275</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>449</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>189</v>
       </c>
       <c r="BE189" t="inlineStr"/>
       <c r="BF189" t="inlineStr"/>
-      <c r="BG189" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BH189" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="BI189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK189" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL189" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BG189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>35</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>5</v>
       </c>
       <c r="BM189" t="inlineStr"/>
       <c r="BN189" t="inlineStr"/>
@@ -42228,15 +41528,11 @@
           <t>500</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>1</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -42270,99 +41566,63 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q190" t="n">
+        <v>5</v>
+      </c>
+      <c r="R190" t="n">
+        <v>18</v>
+      </c>
+      <c r="S190" t="n">
+        <v>1</v>
+      </c>
+      <c r="T190" t="n">
+        <v>7</v>
+      </c>
+      <c r="U190" t="n">
+        <v>3</v>
+      </c>
+      <c r="V190" t="n">
+        <v>6</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1</v>
+      </c>
+      <c r="X190" t="n">
+        <v>5</v>
       </c>
       <c r="Y190" t="inlineStr"/>
       <c r="Z190" t="inlineStr"/>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA190" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>1</v>
       </c>
       <c r="AE190" t="inlineStr"/>
       <c r="AF190" t="inlineStr"/>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>3</v>
       </c>
       <c r="AM190" t="inlineStr"/>
       <c r="AN190" t="inlineStr"/>
@@ -42402,70 +41662,1046 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA190" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="BB190" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="BC190" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="BD190" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
+      <c r="AY190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>265</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>612</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>173</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>515</v>
       </c>
       <c r="BE190" t="inlineStr"/>
       <c r="BF190" t="inlineStr"/>
-      <c r="BG190" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="BH190" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BG190" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>3</v>
       </c>
       <c r="BM190" t="inlineStr"/>
       <c r="BN190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>19 790</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr"/>
+      <c r="AO191" t="inlineStr"/>
+      <c r="AP191" t="inlineStr"/>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AU191" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr"/>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="inlineStr"/>
+      <c r="BM191" t="inlineStr"/>
+      <c r="BN191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>8 526</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="inlineStr"/>
+      <c r="AO192" t="inlineStr"/>
+      <c r="AP192" t="inlineStr"/>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AU192" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr"/>
+      <c r="BA192" t="inlineStr"/>
+      <c r="BB192" t="inlineStr"/>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="inlineStr"/>
+      <c r="BM192" t="inlineStr"/>
+      <c r="BN192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>34 005</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr"/>
+      <c r="AO193" t="inlineStr"/>
+      <c r="AP193" t="inlineStr"/>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AT193" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AU193" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr"/>
+      <c r="BB193" t="inlineStr"/>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
+      <c r="BI193" t="inlineStr"/>
+      <c r="BJ193" t="inlineStr"/>
+      <c r="BK193" t="inlineStr"/>
+      <c r="BL193" t="inlineStr"/>
+      <c r="BM193" t="inlineStr"/>
+      <c r="BN193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>30 026</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr"/>
+      <c r="AO194" t="inlineStr"/>
+      <c r="AP194" t="inlineStr"/>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AU194" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>551</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="inlineStr"/>
+      <c r="BN194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN205"/>
+  <dimension ref="A1:BN212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42784,15 +42784,11 @@
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G196" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -42814,15 +42810,11 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="M196" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1.19</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -42834,115 +42826,71 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q196" t="n">
+        <v>11</v>
+      </c>
+      <c r="R196" t="n">
+        <v>8</v>
+      </c>
+      <c r="S196" t="n">
+        <v>4</v>
+      </c>
+      <c r="T196" t="n">
+        <v>2</v>
+      </c>
+      <c r="U196" t="n">
+        <v>4</v>
+      </c>
+      <c r="V196" t="n">
+        <v>5</v>
+      </c>
+      <c r="W196" t="n">
+        <v>3</v>
+      </c>
+      <c r="X196" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>2</v>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
@@ -43028,15 +42976,11 @@
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -43058,15 +43002,11 @@
           <t>Auxerre</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
+      <c r="M197" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0.82</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -43078,115 +43018,71 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q197" t="n">
+        <v>13</v>
+      </c>
+      <c r="R197" t="n">
+        <v>11</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="n">
+        <v>3</v>
+      </c>
+      <c r="U197" t="n">
+        <v>5</v>
+      </c>
+      <c r="V197" t="n">
+        <v>5</v>
+      </c>
+      <c r="W197" t="n">
+        <v>3</v>
+      </c>
+      <c r="X197" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1</v>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
@@ -43276,15 +43172,11 @@
           <t>54 568</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -43306,15 +43198,11 @@
           <t>Angers</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M198" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0.51</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -43326,115 +43214,71 @@
           <t>24%</t>
         </is>
       </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q198" t="n">
+        <v>16</v>
+      </c>
+      <c r="R198" t="n">
+        <v>10</v>
+      </c>
+      <c r="S198" t="n">
+        <v>4</v>
+      </c>
+      <c r="T198" t="n">
+        <v>3</v>
+      </c>
+      <c r="U198" t="n">
+        <v>8</v>
+      </c>
+      <c r="V198" t="n">
+        <v>5</v>
+      </c>
+      <c r="W198" t="n">
+        <v>4</v>
+      </c>
+      <c r="X198" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0</v>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
@@ -43470,15 +43314,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>1</v>
       </c>
       <c r="AW198" t="inlineStr"/>
       <c r="AX198" t="inlineStr"/>
@@ -43528,15 +43368,11 @@
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -43570,91 +43406,59 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q199" t="n">
+        <v>3</v>
+      </c>
+      <c r="R199" t="n">
+        <v>3</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2</v>
       </c>
       <c r="W199" t="inlineStr"/>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr"/>
       <c r="Z199" t="inlineStr"/>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>0</v>
       </c>
       <c r="AI199" t="inlineStr"/>
       <c r="AJ199" t="inlineStr"/>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>4</v>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
@@ -43690,15 +43494,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AV199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>0</v>
       </c>
       <c r="AW199" t="inlineStr"/>
       <c r="AX199" t="inlineStr"/>
@@ -43748,15 +43548,11 @@
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -43790,99 +43586,63 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q200" t="n">
+        <v>4</v>
+      </c>
+      <c r="R200" t="n">
+        <v>14</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1</v>
+      </c>
+      <c r="T200" t="n">
+        <v>5</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3</v>
+      </c>
+      <c r="V200" t="n">
+        <v>3</v>
+      </c>
+      <c r="W200" t="n">
+        <v>0</v>
+      </c>
+      <c r="X200" t="n">
+        <v>6</v>
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="inlineStr"/>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>1</v>
       </c>
       <c r="AE200" t="inlineStr"/>
       <c r="AF200" t="inlineStr"/>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AG200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0</v>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
@@ -43920,61 +43680,41 @@
       </c>
       <c r="AU200" t="inlineStr"/>
       <c r="AV200" t="inlineStr"/>
-      <c r="AW200" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AX200" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
+      <c r="AW200" t="n">
+        <v>414</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>528</v>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr"/>
       <c r="BA200" t="inlineStr"/>
       <c r="BB200" t="inlineStr"/>
-      <c r="BC200" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="BD200" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
+      <c r="BC200" t="n">
+        <v>346</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>459</v>
       </c>
       <c r="BE200" t="inlineStr"/>
       <c r="BF200" t="inlineStr"/>
-      <c r="BG200" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="BH200" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BI200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK200" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BG200" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>4</v>
       </c>
       <c r="BM200" t="inlineStr"/>
       <c r="BN200" t="inlineStr"/>
@@ -44008,15 +43748,11 @@
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G201" t="n">
+        <v>4</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -44050,99 +43786,63 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q201" t="n">
+        <v>9</v>
+      </c>
+      <c r="R201" t="n">
+        <v>23</v>
+      </c>
+      <c r="S201" t="n">
+        <v>6</v>
+      </c>
+      <c r="T201" t="n">
+        <v>7</v>
+      </c>
+      <c r="U201" t="n">
+        <v>3</v>
+      </c>
+      <c r="V201" t="n">
+        <v>12</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" t="n">
+        <v>4</v>
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="inlineStr"/>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>0</v>
       </c>
       <c r="AE201" t="inlineStr"/>
       <c r="AF201" t="inlineStr"/>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>3</v>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
@@ -44180,61 +43880,41 @@
       </c>
       <c r="AU201" t="inlineStr"/>
       <c r="AV201" t="inlineStr"/>
-      <c r="AW201" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="AX201" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
+      <c r="AW201" t="n">
+        <v>344</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>647</v>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr"/>
       <c r="BA201" t="inlineStr"/>
       <c r="BB201" t="inlineStr"/>
-      <c r="BC201" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="BD201" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
+      <c r="BC201" t="n">
+        <v>276</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>555</v>
       </c>
       <c r="BE201" t="inlineStr"/>
       <c r="BF201" t="inlineStr"/>
-      <c r="BG201" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BH201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BI201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ201" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BK201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL201" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BG201" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>14</v>
       </c>
       <c r="BM201" t="inlineStr"/>
       <c r="BN201" t="inlineStr"/>
@@ -44272,15 +43952,11 @@
           <t>5 181</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -44314,99 +43990,63 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q202" t="n">
+        <v>13</v>
+      </c>
+      <c r="R202" t="n">
+        <v>9</v>
+      </c>
+      <c r="S202" t="n">
+        <v>4</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="n">
+        <v>6</v>
+      </c>
+      <c r="V202" t="n">
+        <v>3</v>
+      </c>
+      <c r="W202" t="n">
+        <v>3</v>
+      </c>
+      <c r="X202" t="n">
+        <v>6</v>
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="inlineStr"/>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="AA202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>7</v>
       </c>
       <c r="AE202" t="inlineStr"/>
       <c r="AF202" t="inlineStr"/>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>2</v>
       </c>
       <c r="AM202" t="inlineStr">
         <is>
@@ -44444,61 +44084,41 @@
       </c>
       <c r="AU202" t="inlineStr"/>
       <c r="AV202" t="inlineStr"/>
-      <c r="AW202" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="AX202" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
+      <c r="AW202" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>453</v>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr"/>
       <c r="BA202" t="inlineStr"/>
       <c r="BB202" t="inlineStr"/>
-      <c r="BC202" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="BD202" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
+      <c r="BC202" t="n">
+        <v>194</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>296</v>
       </c>
       <c r="BE202" t="inlineStr"/>
       <c r="BF202" t="inlineStr"/>
-      <c r="BG202" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH202" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BI202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK202" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL202" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BG202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>11</v>
       </c>
       <c r="BM202" t="inlineStr"/>
       <c r="BN202" t="inlineStr"/>
@@ -44536,15 +44156,11 @@
           <t>3 817</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G203" t="n">
+        <v>2</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -44578,99 +44194,63 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q203" t="n">
+        <v>12</v>
+      </c>
+      <c r="R203" t="n">
+        <v>22</v>
+      </c>
+      <c r="S203" t="n">
+        <v>7</v>
+      </c>
+      <c r="T203" t="n">
+        <v>11</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2</v>
+      </c>
+      <c r="V203" t="n">
+        <v>4</v>
+      </c>
+      <c r="W203" t="n">
+        <v>3</v>
+      </c>
+      <c r="X203" t="n">
+        <v>7</v>
       </c>
       <c r="Y203" t="inlineStr"/>
       <c r="Z203" t="inlineStr"/>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AA203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>4</v>
       </c>
       <c r="AE203" t="inlineStr"/>
       <c r="AF203" t="inlineStr"/>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL203" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG203" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>3</v>
       </c>
       <c r="AM203" t="inlineStr">
         <is>
@@ -44706,71 +44286,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AW203" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AX203" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
+      <c r="AU203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>612</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>361</v>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr"/>
       <c r="BA203" t="inlineStr"/>
       <c r="BB203" t="inlineStr"/>
-      <c r="BC203" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="BD203" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
+      <c r="BC203" t="n">
+        <v>512</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>281</v>
       </c>
       <c r="BE203" t="inlineStr"/>
       <c r="BF203" t="inlineStr"/>
-      <c r="BG203" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BH203" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BI203" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ203" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK203" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BL203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BG203" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>10</v>
       </c>
       <c r="BM203" t="inlineStr"/>
       <c r="BN203" t="inlineStr"/>
@@ -44808,15 +44364,11 @@
           <t>5 062</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -44850,99 +44402,63 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q204" t="n">
+        <v>21</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6</v>
+      </c>
+      <c r="S204" t="n">
+        <v>8</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1</v>
+      </c>
+      <c r="U204" t="n">
+        <v>7</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2</v>
+      </c>
+      <c r="W204" t="n">
+        <v>6</v>
+      </c>
+      <c r="X204" t="n">
+        <v>3</v>
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="inlineStr"/>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA204" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>1</v>
       </c>
       <c r="AE204" t="inlineStr"/>
       <c r="AF204" t="inlineStr"/>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1</v>
       </c>
       <c r="AM204" t="inlineStr">
         <is>
@@ -44980,61 +44496,41 @@
       </c>
       <c r="AU204" t="inlineStr"/>
       <c r="AV204" t="inlineStr"/>
-      <c r="AW204" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="AX204" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
+      <c r="AW204" t="n">
+        <v>729</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>288</v>
       </c>
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr"/>
       <c r="BA204" t="inlineStr"/>
       <c r="BB204" t="inlineStr"/>
-      <c r="BC204" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="BD204" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+      <c r="BC204" t="n">
+        <v>647</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>212</v>
       </c>
       <c r="BE204" t="inlineStr"/>
       <c r="BF204" t="inlineStr"/>
-      <c r="BG204" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BH204" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="BI204" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BJ204" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK204" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BL204" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BG204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>35</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>12</v>
       </c>
       <c r="BM204" t="inlineStr"/>
       <c r="BN204" t="inlineStr"/>
@@ -45072,15 +44568,11 @@
           <t>4 049</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -45114,99 +44606,63 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q205" t="n">
+        <v>12</v>
+      </c>
+      <c r="R205" t="n">
+        <v>4</v>
+      </c>
+      <c r="S205" t="n">
+        <v>6</v>
+      </c>
+      <c r="T205" t="n">
+        <v>2</v>
+      </c>
+      <c r="U205" t="n">
+        <v>4</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2</v>
+      </c>
+      <c r="W205" t="n">
+        <v>2</v>
+      </c>
+      <c r="X205" t="n">
+        <v>0</v>
       </c>
       <c r="Y205" t="inlineStr"/>
       <c r="Z205" t="inlineStr"/>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>0</v>
       </c>
       <c r="AE205" t="inlineStr"/>
       <c r="AF205" t="inlineStr"/>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>3</v>
       </c>
       <c r="AM205" t="inlineStr">
         <is>
@@ -45244,64 +44700,1796 @@
       </c>
       <c r="AU205" t="inlineStr"/>
       <c r="AV205" t="inlineStr"/>
-      <c r="AW205" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AX205" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
+      <c r="AW205" t="n">
+        <v>388</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>685</v>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr"/>
       <c r="BA205" t="inlineStr"/>
       <c r="BB205" t="inlineStr"/>
-      <c r="BC205" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="BD205" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
+      <c r="BC205" t="n">
+        <v>304</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>587</v>
       </c>
       <c r="BE205" t="inlineStr"/>
       <c r="BF205" t="inlineStr"/>
-      <c r="BG205" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BH205" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="BI205" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK205" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL205" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG205" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>15</v>
       </c>
       <c r="BM205" t="inlineStr"/>
       <c r="BN205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>30 247</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AQ206" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr"/>
+      <c r="AV206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr"/>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr"/>
+      <c r="BA206" t="inlineStr"/>
+      <c r="BB206" t="inlineStr"/>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
+      <c r="BM206" t="inlineStr"/>
+      <c r="BN206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>14 572</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AQ207" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr"/>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr"/>
+      <c r="BA207" t="inlineStr"/>
+      <c r="BB207" t="inlineStr"/>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
+      <c r="BM207" t="inlineStr"/>
+      <c r="BN207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>14 903</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AQ208" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr"/>
+      <c r="AV208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr"/>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr"/>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>19 968</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AQ209" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr"/>
+      <c r="AV209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr"/>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr"/>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>51 888</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AQ210" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU210" t="inlineStr"/>
+      <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr"/>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr"/>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>05.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>26 533</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AQ211" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU211" t="inlineStr"/>
+      <c r="AV211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr"/>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr"/>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>fPQD76ac</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>05.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Paradis G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>18 279</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr"/>
+      <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AQ212" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU212" t="inlineStr"/>
+      <c r="AV212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr"/>
+      <c r="BA212" t="inlineStr"/>
+      <c r="BB212" t="inlineStr"/>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="BD212" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="BE212" t="inlineStr"/>
+      <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BH212" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BI212" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK212" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BL212" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BM212" t="inlineStr"/>
+      <c r="BN212" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN212"/>
+  <dimension ref="A1:BN222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44772,15 +44772,11 @@
           <t>30 247</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -44802,15 +44798,11 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="M206" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N206" t="n">
+        <v>1.17</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -44822,115 +44814,71 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL206" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q206" t="n">
+        <v>8</v>
+      </c>
+      <c r="R206" t="n">
+        <v>19</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3</v>
+      </c>
+      <c r="T206" t="n">
+        <v>9</v>
+      </c>
+      <c r="U206" t="n">
+        <v>3</v>
+      </c>
+      <c r="V206" t="n">
+        <v>5</v>
+      </c>
+      <c r="W206" t="n">
+        <v>2</v>
+      </c>
+      <c r="X206" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>2</v>
       </c>
       <c r="AM206" t="inlineStr">
         <is>
@@ -45020,15 +44968,11 @@
           <t>14 572</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -45050,15 +44994,11 @@
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
+      <c r="M207" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1.13</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -45070,115 +45010,71 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q207" t="n">
+        <v>8</v>
+      </c>
+      <c r="R207" t="n">
+        <v>14</v>
+      </c>
+      <c r="S207" t="n">
+        <v>3</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2</v>
+      </c>
+      <c r="V207" t="n">
+        <v>9</v>
+      </c>
+      <c r="W207" t="n">
+        <v>3</v>
+      </c>
+      <c r="X207" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
@@ -45214,15 +45110,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>1</v>
       </c>
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr"/>
@@ -45276,15 +45168,11 @@
           <t>14 903</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G208" t="n">
+        <v>4</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -45306,15 +45194,11 @@
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
+      <c r="M208" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0.42</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -45326,115 +45210,71 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL208" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q208" t="n">
+        <v>18</v>
+      </c>
+      <c r="R208" t="n">
+        <v>10</v>
+      </c>
+      <c r="S208" t="n">
+        <v>5</v>
+      </c>
+      <c r="T208" t="n">
+        <v>3</v>
+      </c>
+      <c r="U208" t="n">
+        <v>8</v>
+      </c>
+      <c r="V208" t="n">
+        <v>5</v>
+      </c>
+      <c r="W208" t="n">
+        <v>5</v>
+      </c>
+      <c r="X208" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>5</v>
       </c>
       <c r="AM208" t="inlineStr">
         <is>
@@ -45524,15 +45364,11 @@
           <t>19 968</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -45554,15 +45390,11 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
+      <c r="M209" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0.96</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -45574,115 +45406,71 @@
           <t>63%</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL209" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q209" t="n">
+        <v>8</v>
+      </c>
+      <c r="R209" t="n">
+        <v>12</v>
+      </c>
+      <c r="S209" t="n">
+        <v>5</v>
+      </c>
+      <c r="T209" t="n">
+        <v>5</v>
+      </c>
+      <c r="U209" t="n">
+        <v>3</v>
+      </c>
+      <c r="V209" t="n">
+        <v>3</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>4</v>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
@@ -45772,15 +45560,11 @@
           <t>51 888</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -45802,15 +45586,11 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="M210" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0.76</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -45822,115 +45602,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL210" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q210" t="n">
+        <v>17</v>
+      </c>
+      <c r="R210" t="n">
+        <v>11</v>
+      </c>
+      <c r="S210" t="n">
+        <v>6</v>
+      </c>
+      <c r="T210" t="n">
+        <v>6</v>
+      </c>
+      <c r="U210" t="n">
+        <v>8</v>
+      </c>
+      <c r="V210" t="n">
+        <v>4</v>
+      </c>
+      <c r="W210" t="n">
+        <v>3</v>
+      </c>
+      <c r="X210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>2</v>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
@@ -46020,15 +45756,11 @@
           <t>26 533</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>2</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -46050,15 +45782,11 @@
           <t>Monaco</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+      <c r="M211" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0.59</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -46070,115 +45798,71 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q211" t="n">
+        <v>14</v>
+      </c>
+      <c r="R211" t="n">
+        <v>5</v>
+      </c>
+      <c r="S211" t="n">
+        <v>3</v>
+      </c>
+      <c r="T211" t="n">
+        <v>2</v>
+      </c>
+      <c r="U211" t="n">
+        <v>5</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2</v>
+      </c>
+      <c r="W211" t="n">
+        <v>6</v>
+      </c>
+      <c r="X211" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>4</v>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
@@ -46268,15 +45952,11 @@
           <t>18 279</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -46310,89 +45990,57 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q212" t="n">
+        <v>15</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6</v>
+      </c>
+      <c r="S212" t="n">
+        <v>7</v>
+      </c>
+      <c r="T212" t="n">
+        <v>4</v>
+      </c>
+      <c r="U212" t="n">
+        <v>6</v>
+      </c>
+      <c r="V212" t="n">
+        <v>1</v>
+      </c>
+      <c r="W212" t="n">
+        <v>2</v>
+      </c>
+      <c r="X212" t="n">
+        <v>1</v>
       </c>
       <c r="Y212" t="inlineStr"/>
       <c r="Z212" t="inlineStr"/>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>1</v>
       </c>
       <c r="AE212" t="inlineStr"/>
       <c r="AF212" t="inlineStr"/>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AG212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>10</v>
       </c>
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr"/>
@@ -46432,64 +46080,2732 @@
       </c>
       <c r="AU212" t="inlineStr"/>
       <c r="AV212" t="inlineStr"/>
-      <c r="AW212" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="AX212" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
+      <c r="AW212" t="n">
+        <v>631</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>466</v>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr"/>
       <c r="BA212" t="inlineStr"/>
       <c r="BB212" t="inlineStr"/>
-      <c r="BC212" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="BD212" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="BC212" t="n">
+        <v>562</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>379</v>
       </c>
       <c r="BE212" t="inlineStr"/>
       <c r="BF212" t="inlineStr"/>
-      <c r="BG212" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH212" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ212" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK212" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BL212" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG212" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>15</v>
       </c>
       <c r="BM212" t="inlineStr"/>
       <c r="BN212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>19.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Lissorgue R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AN213" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AQ213" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU213" t="inlineStr"/>
+      <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr"/>
+      <c r="BA213" t="inlineStr"/>
+      <c r="BB213" t="inlineStr"/>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="BD213" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="BE213" t="inlineStr"/>
+      <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr"/>
+      <c r="BI213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK213" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BL213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BM213" t="inlineStr"/>
+      <c r="BN213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>19.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AN214" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AQ214" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU214" t="inlineStr"/>
+      <c r="AV214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr"/>
+      <c r="BA214" t="inlineStr"/>
+      <c r="BB214" t="inlineStr"/>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="BD214" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="BE214" t="inlineStr"/>
+      <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr"/>
+      <c r="BI214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK214" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL214" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BM214" t="inlineStr"/>
+      <c r="BN214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>7 246</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AQ215" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr"/>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
+      <c r="BI215" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK215" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL215" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>xlCidXdD</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>19.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>5 956</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AQ216" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU216" t="inlineStr"/>
+      <c r="AV216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr"/>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BH216" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BI216" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK216" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL216" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BM216" t="inlineStr"/>
+      <c r="BN216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>lbfDWDYP</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>9 967</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AQ217" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr"/>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BH217" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BI217" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BJ217" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK217" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BL217" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>d47R8AtJ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>5 916</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AQ218" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU218" t="inlineStr"/>
+      <c r="AV218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr"/>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="BH218" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BI218" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BK218" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL218" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BM218" t="inlineStr"/>
+      <c r="BN218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>4zEqbgS0</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>8 112</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr"/>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AQ219" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU219" t="inlineStr"/>
+      <c r="AV219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr"/>
+      <c r="BA219" t="inlineStr"/>
+      <c r="BB219" t="inlineStr"/>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="BD219" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="BE219" t="inlineStr"/>
+      <c r="BF219" t="inlineStr"/>
+      <c r="BG219" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BH219" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BI219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ219" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BK219" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL219" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM219" t="inlineStr"/>
+      <c r="BN219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>8UeBChsf</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Stade Francis Le Basser
+ (Laval)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>5 948</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr"/>
+      <c r="Z220" t="inlineStr"/>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr"/>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AQ220" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU220" t="inlineStr"/>
+      <c r="AV220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr"/>
+      <c r="BA220" t="inlineStr"/>
+      <c r="BB220" t="inlineStr"/>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="BD220" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="BE220" t="inlineStr"/>
+      <c r="BF220" t="inlineStr"/>
+      <c r="BG220" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BH220" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BI220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK220" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL220" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BM220" t="inlineStr"/>
+      <c r="BN220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>88Kz0Fcl</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Stade Francis Turcan
+ (Martigues)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr"/>
+      <c r="Z221" t="inlineStr"/>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr"/>
+      <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AQ221" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU221" t="inlineStr"/>
+      <c r="AV221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr"/>
+      <c r="BA221" t="inlineStr"/>
+      <c r="BB221" t="inlineStr"/>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="BD221" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="BE221" t="inlineStr"/>
+      <c r="BF221" t="inlineStr"/>
+      <c r="BG221" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BH221" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BI221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK221" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL221" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BM221" t="inlineStr"/>
+      <c r="BN221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>nF72EECs</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>4 643</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr"/>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr"/>
+      <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AN222" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AQ222" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU222" t="inlineStr"/>
+      <c r="AV222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr"/>
+      <c r="BA222" t="inlineStr"/>
+      <c r="BB222" t="inlineStr"/>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr"/>
+      <c r="BF222" t="inlineStr"/>
+      <c r="BG222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH222" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="BI222" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BJ222" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BK222" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL222" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BM222" t="inlineStr"/>
+      <c r="BN222" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN222"/>
+  <dimension ref="A1:BN230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46148,15 +46148,11 @@
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -46178,15 +46174,11 @@
           <t>Lens</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
+      <c r="M213" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1.29</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -46198,115 +46190,71 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q213" t="n">
+        <v>15</v>
+      </c>
+      <c r="R213" t="n">
+        <v>13</v>
+      </c>
+      <c r="S213" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" t="n">
+        <v>5</v>
+      </c>
+      <c r="U213" t="n">
+        <v>7</v>
+      </c>
+      <c r="V213" t="n">
+        <v>7</v>
+      </c>
+      <c r="W213" t="n">
+        <v>7</v>
+      </c>
+      <c r="X213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>2</v>
       </c>
       <c r="AM213" t="inlineStr">
         <is>
@@ -46344,53 +46292,37 @@
       </c>
       <c r="AU213" t="inlineStr"/>
       <c r="AV213" t="inlineStr"/>
-      <c r="AW213" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AX213" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
+      <c r="AW213" t="n">
+        <v>331</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>568</v>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr"/>
       <c r="BA213" t="inlineStr"/>
       <c r="BB213" t="inlineStr"/>
-      <c r="BC213" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="BD213" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="BC213" t="n">
+        <v>248</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>500</v>
       </c>
       <c r="BE213" t="inlineStr"/>
       <c r="BF213" t="inlineStr"/>
       <c r="BG213" t="inlineStr"/>
       <c r="BH213" t="inlineStr"/>
-      <c r="BI213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK213" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BL213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BI213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>4</v>
       </c>
       <c r="BM213" t="inlineStr"/>
       <c r="BN213" t="inlineStr"/>
@@ -46424,15 +46356,11 @@
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -46454,15 +46382,11 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="M214" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1.09</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -46474,115 +46398,71 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q214" t="n">
+        <v>12</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6</v>
+      </c>
+      <c r="S214" t="n">
+        <v>2</v>
+      </c>
+      <c r="T214" t="n">
+        <v>4</v>
+      </c>
+      <c r="U214" t="n">
+        <v>7</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2</v>
+      </c>
+      <c r="W214" t="n">
+        <v>3</v>
+      </c>
+      <c r="X214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>2</v>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
@@ -46620,53 +46500,37 @@
       </c>
       <c r="AU214" t="inlineStr"/>
       <c r="AV214" t="inlineStr"/>
-      <c r="AW214" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="AX214" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
+      <c r="AW214" t="n">
+        <v>459</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>365</v>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr"/>
       <c r="BA214" t="inlineStr"/>
       <c r="BB214" t="inlineStr"/>
-      <c r="BC214" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="BD214" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
+      <c r="BC214" t="n">
+        <v>353</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>292</v>
       </c>
       <c r="BE214" t="inlineStr"/>
       <c r="BF214" t="inlineStr"/>
       <c r="BG214" t="inlineStr"/>
       <c r="BH214" t="inlineStr"/>
-      <c r="BI214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK214" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL214" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BI214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>11</v>
       </c>
       <c r="BM214" t="inlineStr"/>
       <c r="BN214" t="inlineStr"/>
@@ -46704,15 +46568,11 @@
           <t>7 246</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -46734,15 +46594,11 @@
           <t>Lille</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="M215" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0.25</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -46754,115 +46610,71 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q215" t="n">
+        <v>14</v>
+      </c>
+      <c r="R215" t="n">
+        <v>3</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1</v>
+      </c>
+      <c r="U215" t="n">
+        <v>7</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2</v>
+      </c>
+      <c r="W215" t="n">
+        <v>3</v>
+      </c>
+      <c r="X215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>5</v>
       </c>
       <c r="AM215" t="inlineStr">
         <is>
@@ -46898,63 +46710,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW215" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="AX215" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
+      <c r="AU215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>458</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>444</v>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr"/>
       <c r="BA215" t="inlineStr"/>
       <c r="BB215" t="inlineStr"/>
-      <c r="BC215" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="BD215" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
+      <c r="BC215" t="n">
+        <v>385</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>358</v>
       </c>
       <c r="BE215" t="inlineStr"/>
       <c r="BF215" t="inlineStr"/>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
-      <c r="BI215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BK215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL215" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="BI215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>18</v>
       </c>
       <c r="BM215" t="inlineStr"/>
       <c r="BN215" t="inlineStr"/>
@@ -46992,15 +46784,11 @@
           <t>5 956</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G216" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -47034,99 +46822,63 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q216" t="n">
+        <v>15</v>
+      </c>
+      <c r="R216" t="n">
+        <v>14</v>
+      </c>
+      <c r="S216" t="n">
+        <v>9</v>
+      </c>
+      <c r="T216" t="n">
+        <v>4</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3</v>
+      </c>
+      <c r="V216" t="n">
+        <v>8</v>
+      </c>
+      <c r="W216" t="n">
+        <v>3</v>
+      </c>
+      <c r="X216" t="n">
+        <v>2</v>
       </c>
       <c r="Y216" t="inlineStr"/>
       <c r="Z216" t="inlineStr"/>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>0</v>
       </c>
       <c r="AE216" t="inlineStr"/>
       <c r="AF216" t="inlineStr"/>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>2</v>
       </c>
       <c r="AM216" t="inlineStr">
         <is>
@@ -47164,61 +46916,41 @@
       </c>
       <c r="AU216" t="inlineStr"/>
       <c r="AV216" t="inlineStr"/>
-      <c r="AW216" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="AX216" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="AW216" t="n">
+        <v>363</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>506</v>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr"/>
       <c r="BA216" t="inlineStr"/>
       <c r="BB216" t="inlineStr"/>
-      <c r="BC216" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="BD216" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+      <c r="BC216" t="n">
+        <v>274</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>409</v>
       </c>
       <c r="BE216" t="inlineStr"/>
       <c r="BF216" t="inlineStr"/>
-      <c r="BG216" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BH216" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI216" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ216" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK216" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL216" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="BG216" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>16</v>
       </c>
       <c r="BM216" t="inlineStr"/>
       <c r="BN216" t="inlineStr"/>
@@ -47256,15 +46988,11 @@
           <t>9 967</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -47298,91 +47026,59 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q217" t="n">
+        <v>20</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>2</v>
+      </c>
+      <c r="U217" t="n">
+        <v>10</v>
+      </c>
+      <c r="V217" t="n">
+        <v>1</v>
+      </c>
+      <c r="W217" t="n">
+        <v>6</v>
+      </c>
+      <c r="X217" t="n">
+        <v>3</v>
       </c>
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="AA217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>5</v>
       </c>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="inlineStr"/>
       <c r="AF217" t="inlineStr"/>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AG217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>4</v>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
@@ -47418,71 +47114,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AW217" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="AX217" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="AU217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>525</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>363</v>
       </c>
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr"/>
       <c r="BA217" t="inlineStr"/>
       <c r="BB217" t="inlineStr"/>
-      <c r="BC217" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="BD217" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="BC217" t="n">
+        <v>444</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>262</v>
       </c>
       <c r="BE217" t="inlineStr"/>
       <c r="BF217" t="inlineStr"/>
-      <c r="BG217" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BH217" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BI217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK217" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BL217" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BG217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>9</v>
       </c>
       <c r="BM217" t="inlineStr"/>
       <c r="BN217" t="inlineStr"/>
@@ -47520,15 +47192,11 @@
           <t>5 916</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G218" t="n">
+        <v>2</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -47562,99 +47230,63 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q218" t="n">
+        <v>13</v>
+      </c>
+      <c r="R218" t="n">
+        <v>13</v>
+      </c>
+      <c r="S218" t="n">
+        <v>5</v>
+      </c>
+      <c r="T218" t="n">
+        <v>7</v>
+      </c>
+      <c r="U218" t="n">
+        <v>6</v>
+      </c>
+      <c r="V218" t="n">
+        <v>5</v>
+      </c>
+      <c r="W218" t="n">
+        <v>2</v>
+      </c>
+      <c r="X218" t="n">
+        <v>1</v>
       </c>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="inlineStr"/>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>2</v>
       </c>
       <c r="AE218" t="inlineStr"/>
       <c r="AF218" t="inlineStr"/>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>2</v>
       </c>
       <c r="AM218" t="inlineStr">
         <is>
@@ -47692,61 +47324,41 @@
       </c>
       <c r="AU218" t="inlineStr"/>
       <c r="AV218" t="inlineStr"/>
-      <c r="AW218" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AX218" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
+      <c r="AW218" t="n">
+        <v>338</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>632</v>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr"/>
       <c r="BA218" t="inlineStr"/>
       <c r="BB218" t="inlineStr"/>
-      <c r="BC218" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="BD218" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
+      <c r="BC218" t="n">
+        <v>250</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>548</v>
       </c>
       <c r="BE218" t="inlineStr"/>
       <c r="BF218" t="inlineStr"/>
-      <c r="BG218" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="BH218" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BI218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BK218" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL218" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="BG218" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>18</v>
       </c>
       <c r="BM218" t="inlineStr"/>
       <c r="BN218" t="inlineStr"/>
@@ -47784,15 +47396,11 @@
           <t>8 112</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -47826,99 +47434,63 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T219" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q219" t="n">
+        <v>15</v>
+      </c>
+      <c r="R219" t="n">
+        <v>13</v>
+      </c>
+      <c r="S219" t="n">
+        <v>6</v>
+      </c>
+      <c r="T219" t="n">
+        <v>7</v>
+      </c>
+      <c r="U219" t="n">
+        <v>7</v>
+      </c>
+      <c r="V219" t="n">
+        <v>4</v>
+      </c>
+      <c r="W219" t="n">
+        <v>2</v>
+      </c>
+      <c r="X219" t="n">
+        <v>2</v>
       </c>
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="inlineStr"/>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>2</v>
       </c>
       <c r="AE219" t="inlineStr"/>
       <c r="AF219" t="inlineStr"/>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>3</v>
       </c>
       <c r="AM219" t="inlineStr">
         <is>
@@ -47956,61 +47528,41 @@
       </c>
       <c r="AU219" t="inlineStr"/>
       <c r="AV219" t="inlineStr"/>
-      <c r="AW219" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="AX219" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
+      <c r="AW219" t="n">
+        <v>638</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>361</v>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr"/>
       <c r="BA219" t="inlineStr"/>
       <c r="BB219" t="inlineStr"/>
-      <c r="BC219" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="BD219" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="BC219" t="n">
+        <v>546</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>256</v>
       </c>
       <c r="BE219" t="inlineStr"/>
       <c r="BF219" t="inlineStr"/>
-      <c r="BG219" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BH219" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BI219" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ219" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BK219" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL219" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG219" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>7</v>
       </c>
       <c r="BM219" t="inlineStr"/>
       <c r="BN219" t="inlineStr"/>
@@ -48048,15 +47600,11 @@
           <t>5 948</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G220" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -48090,99 +47638,63 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q220" t="n">
+        <v>3</v>
+      </c>
+      <c r="R220" t="n">
+        <v>14</v>
+      </c>
+      <c r="S220" t="n">
+        <v>3</v>
+      </c>
+      <c r="T220" t="n">
+        <v>7</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0</v>
+      </c>
+      <c r="V220" t="n">
+        <v>6</v>
+      </c>
+      <c r="W220" t="n">
+        <v>0</v>
+      </c>
+      <c r="X220" t="n">
+        <v>1</v>
       </c>
       <c r="Y220" t="inlineStr"/>
       <c r="Z220" t="inlineStr"/>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>1</v>
       </c>
       <c r="AE220" t="inlineStr"/>
       <c r="AF220" t="inlineStr"/>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL220" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>2</v>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
@@ -48220,61 +47732,41 @@
       </c>
       <c r="AU220" t="inlineStr"/>
       <c r="AV220" t="inlineStr"/>
-      <c r="AW220" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="AX220" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
+      <c r="AW220" t="n">
+        <v>287</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>663</v>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr"/>
       <c r="BA220" t="inlineStr"/>
       <c r="BB220" t="inlineStr"/>
-      <c r="BC220" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="BD220" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="BC220" t="n">
+        <v>191</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>550</v>
       </c>
       <c r="BE220" t="inlineStr"/>
       <c r="BF220" t="inlineStr"/>
-      <c r="BG220" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BH220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BI220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK220" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL220" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG220" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>15</v>
       </c>
       <c r="BM220" t="inlineStr"/>
       <c r="BN220" t="inlineStr"/>
@@ -48312,15 +47804,11 @@
           <t>409</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -48354,99 +47842,63 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q221" t="n">
+        <v>12</v>
+      </c>
+      <c r="R221" t="n">
+        <v>12</v>
+      </c>
+      <c r="S221" t="n">
+        <v>6</v>
+      </c>
+      <c r="T221" t="n">
+        <v>6</v>
+      </c>
+      <c r="U221" t="n">
+        <v>4</v>
+      </c>
+      <c r="V221" t="n">
+        <v>6</v>
+      </c>
+      <c r="W221" t="n">
+        <v>2</v>
+      </c>
+      <c r="X221" t="n">
+        <v>0</v>
       </c>
       <c r="Y221" t="inlineStr"/>
       <c r="Z221" t="inlineStr"/>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AA221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>6</v>
       </c>
       <c r="AE221" t="inlineStr"/>
       <c r="AF221" t="inlineStr"/>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1</v>
       </c>
       <c r="AM221" t="inlineStr">
         <is>
@@ -48484,61 +47936,41 @@
       </c>
       <c r="AU221" t="inlineStr"/>
       <c r="AV221" t="inlineStr"/>
-      <c r="AW221" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AX221" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
+      <c r="AW221" t="n">
+        <v>549</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>414</v>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr"/>
       <c r="BA221" t="inlineStr"/>
       <c r="BB221" t="inlineStr"/>
-      <c r="BC221" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="BD221" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
+      <c r="BC221" t="n">
+        <v>452</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>334</v>
       </c>
       <c r="BE221" t="inlineStr"/>
       <c r="BF221" t="inlineStr"/>
-      <c r="BG221" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH221" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BI221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK221" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL221" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="BG221" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>33</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>17</v>
       </c>
       <c r="BM221" t="inlineStr"/>
       <c r="BN221" t="inlineStr"/>
@@ -48576,15 +48008,11 @@
           <t>4 643</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -48618,99 +48046,63 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q222" t="n">
+        <v>17</v>
+      </c>
+      <c r="R222" t="n">
+        <v>10</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="n">
+        <v>2</v>
+      </c>
+      <c r="U222" t="n">
+        <v>5</v>
+      </c>
+      <c r="V222" t="n">
+        <v>3</v>
+      </c>
+      <c r="W222" t="n">
+        <v>2</v>
+      </c>
+      <c r="X222" t="n">
+        <v>5</v>
       </c>
       <c r="Y222" t="inlineStr"/>
       <c r="Z222" t="inlineStr"/>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA222" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>1</v>
       </c>
       <c r="AE222" t="inlineStr"/>
       <c r="AF222" t="inlineStr"/>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>1</v>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
@@ -48748,64 +48140,1784 @@
       </c>
       <c r="AU222" t="inlineStr"/>
       <c r="AV222" t="inlineStr"/>
-      <c r="AW222" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="AX222" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
+      <c r="AW222" t="n">
+        <v>504</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>410</v>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr"/>
       <c r="BA222" t="inlineStr"/>
       <c r="BB222" t="inlineStr"/>
-      <c r="BC222" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="BD222" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
+      <c r="BC222" t="n">
+        <v>430</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>336</v>
       </c>
       <c r="BE222" t="inlineStr"/>
       <c r="BF222" t="inlineStr"/>
-      <c r="BG222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH222" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="BI222" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BJ222" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BK222" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL222" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="BG222" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>35</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>14</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>19</v>
       </c>
       <c r="BM222" t="inlineStr"/>
       <c r="BN222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>20.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Turpin C.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>18 000</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>5</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N223" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>13</v>
+      </c>
+      <c r="R223" t="n">
+        <v>21</v>
+      </c>
+      <c r="S223" t="n">
+        <v>5</v>
+      </c>
+      <c r="T223" t="n">
+        <v>10</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3</v>
+      </c>
+      <c r="V223" t="n">
+        <v>9</v>
+      </c>
+      <c r="W223" t="n">
+        <v>5</v>
+      </c>
+      <c r="X223" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="AN223" t="inlineStr">
+        <is>
+          <t>der zakarian michel</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AQ223" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>293</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>562</v>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr"/>
+      <c r="BA223" t="inlineStr"/>
+      <c r="BB223" t="inlineStr"/>
+      <c r="BC223" t="n">
+        <v>238</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>513</v>
+      </c>
+      <c r="BE223" t="inlineStr"/>
+      <c r="BF223" t="inlineStr"/>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
+      <c r="BI223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM223" t="inlineStr"/>
+      <c r="BN223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>17 016</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>10</v>
+      </c>
+      <c r="R224" t="n">
+        <v>15</v>
+      </c>
+      <c r="S224" t="n">
+        <v>8</v>
+      </c>
+      <c r="T224" t="n">
+        <v>3</v>
+      </c>
+      <c r="U224" t="n">
+        <v>2</v>
+      </c>
+      <c r="V224" t="n">
+        <v>4</v>
+      </c>
+      <c r="W224" t="n">
+        <v>0</v>
+      </c>
+      <c r="X224" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AQ224" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU224" t="inlineStr"/>
+      <c r="AV224" t="inlineStr"/>
+      <c r="AW224" t="n">
+        <v>264</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>477</v>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr"/>
+      <c r="BA224" t="inlineStr"/>
+      <c r="BB224" t="inlineStr"/>
+      <c r="BC224" t="n">
+        <v>197</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>409</v>
+      </c>
+      <c r="BE224" t="inlineStr"/>
+      <c r="BF224" t="inlineStr"/>
+      <c r="BG224" t="inlineStr"/>
+      <c r="BH224" t="inlineStr"/>
+      <c r="BI224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM224" t="inlineStr"/>
+      <c r="BN224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>28 141</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>11</v>
+      </c>
+      <c r="R225" t="n">
+        <v>13</v>
+      </c>
+      <c r="S225" t="n">
+        <v>7</v>
+      </c>
+      <c r="T225" t="n">
+        <v>7</v>
+      </c>
+      <c r="U225" t="n">
+        <v>3</v>
+      </c>
+      <c r="V225" t="n">
+        <v>5</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1</v>
+      </c>
+      <c r="X225" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AN225" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AQ225" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU225" t="inlineStr"/>
+      <c r="AV225" t="inlineStr"/>
+      <c r="AW225" t="n">
+        <v>390</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>535</v>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr"/>
+      <c r="BA225" t="inlineStr"/>
+      <c r="BB225" t="inlineStr"/>
+      <c r="BC225" t="n">
+        <v>320</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>466</v>
+      </c>
+      <c r="BE225" t="inlineStr"/>
+      <c r="BF225" t="inlineStr"/>
+      <c r="BG225" t="inlineStr"/>
+      <c r="BH225" t="inlineStr"/>
+      <c r="BI225" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM225" t="inlineStr"/>
+      <c r="BN225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>24 107</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>18</v>
+      </c>
+      <c r="R226" t="n">
+        <v>8</v>
+      </c>
+      <c r="S226" t="n">
+        <v>6</v>
+      </c>
+      <c r="T226" t="n">
+        <v>4</v>
+      </c>
+      <c r="U226" t="n">
+        <v>7</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2</v>
+      </c>
+      <c r="W226" t="n">
+        <v>5</v>
+      </c>
+      <c r="X226" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AN226" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AQ226" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU226" t="inlineStr"/>
+      <c r="AV226" t="inlineStr"/>
+      <c r="AW226" t="n">
+        <v>535</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>278</v>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr"/>
+      <c r="BA226" t="inlineStr"/>
+      <c r="BB226" t="inlineStr"/>
+      <c r="BC226" t="n">
+        <v>451</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>197</v>
+      </c>
+      <c r="BE226" t="inlineStr"/>
+      <c r="BF226" t="inlineStr"/>
+      <c r="BG226" t="inlineStr"/>
+      <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>11</v>
+      </c>
+      <c r="BM226" t="inlineStr"/>
+      <c r="BN226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>b9aoAn8k</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>22 490</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>4</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M227" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N227" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>7</v>
+      </c>
+      <c r="R227" t="n">
+        <v>16</v>
+      </c>
+      <c r="S227" t="n">
+        <v>1</v>
+      </c>
+      <c r="T227" t="n">
+        <v>8</v>
+      </c>
+      <c r="U227" t="n">
+        <v>3</v>
+      </c>
+      <c r="V227" t="n">
+        <v>4</v>
+      </c>
+      <c r="W227" t="n">
+        <v>3</v>
+      </c>
+      <c r="X227" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AQ227" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT227" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU227" t="inlineStr"/>
+      <c r="AV227" t="inlineStr"/>
+      <c r="AW227" t="n">
+        <v>303</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>508</v>
+      </c>
+      <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr"/>
+      <c r="BA227" t="inlineStr"/>
+      <c r="BB227" t="inlineStr"/>
+      <c r="BC227" t="n">
+        <v>241</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>437</v>
+      </c>
+      <c r="BE227" t="inlineStr"/>
+      <c r="BF227" t="inlineStr"/>
+      <c r="BG227" t="inlineStr"/>
+      <c r="BH227" t="inlineStr"/>
+      <c r="BI227" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM227" t="inlineStr"/>
+      <c r="BN227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>19.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>47 590</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>4</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M228" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>18</v>
+      </c>
+      <c r="R228" t="n">
+        <v>16</v>
+      </c>
+      <c r="S228" t="n">
+        <v>10</v>
+      </c>
+      <c r="T228" t="n">
+        <v>8</v>
+      </c>
+      <c r="U228" t="n">
+        <v>5</v>
+      </c>
+      <c r="V228" t="n">
+        <v>1</v>
+      </c>
+      <c r="W228" t="n">
+        <v>3</v>
+      </c>
+      <c r="X228" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AN228" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AQ228" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT228" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU228" t="inlineStr"/>
+      <c r="AV228" t="inlineStr"/>
+      <c r="AW228" t="n">
+        <v>560</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>445</v>
+      </c>
+      <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr"/>
+      <c r="BA228" t="inlineStr"/>
+      <c r="BB228" t="inlineStr"/>
+      <c r="BC228" t="n">
+        <v>492</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>378</v>
+      </c>
+      <c r="BE228" t="inlineStr"/>
+      <c r="BF228" t="inlineStr"/>
+      <c r="BG228" t="inlineStr"/>
+      <c r="BH228" t="inlineStr"/>
+      <c r="BI228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM228" t="inlineStr"/>
+      <c r="BN228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>GWGWJzkK</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>19.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Stade du Moustoir
+ (Lorient)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>16 787</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>11 512</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>4</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>19</v>
+      </c>
+      <c r="R229" t="n">
+        <v>9</v>
+      </c>
+      <c r="S229" t="n">
+        <v>9</v>
+      </c>
+      <c r="T229" t="n">
+        <v>4</v>
+      </c>
+      <c r="U229" t="n">
+        <v>7</v>
+      </c>
+      <c r="V229" t="n">
+        <v>5</v>
+      </c>
+      <c r="W229" t="n">
+        <v>3</v>
+      </c>
+      <c r="X229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y229" t="inlineStr"/>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="inlineStr"/>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AQ229" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU229" t="inlineStr"/>
+      <c r="AV229" t="inlineStr"/>
+      <c r="AW229" t="n">
+        <v>629</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>361</v>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr"/>
+      <c r="BA229" t="inlineStr"/>
+      <c r="BB229" t="inlineStr"/>
+      <c r="BC229" t="n">
+        <v>499</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>249</v>
+      </c>
+      <c r="BE229" t="inlineStr"/>
+      <c r="BF229" t="inlineStr"/>
+      <c r="BG229" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>38</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM229" t="inlineStr"/>
+      <c r="BN229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>2g2J0IEs</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>21.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr"/>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr"/>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AN230" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AQ230" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU230" t="inlineStr"/>
+      <c r="AV230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr"/>
+      <c r="BA230" t="inlineStr"/>
+      <c r="BB230" t="inlineStr"/>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="BD230" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="BE230" t="inlineStr"/>
+      <c r="BF230" t="inlineStr"/>
+      <c r="BG230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BH230" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BI230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ230" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM230" t="inlineStr"/>
+      <c r="BN230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN230"/>
+  <dimension ref="A1:BN231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49688,15 +49688,11 @@
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>3</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -49730,99 +49726,63 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q230" t="n">
+        <v>11</v>
+      </c>
+      <c r="R230" t="n">
+        <v>11</v>
+      </c>
+      <c r="S230" t="n">
+        <v>3</v>
+      </c>
+      <c r="T230" t="n">
+        <v>6</v>
+      </c>
+      <c r="U230" t="n">
+        <v>7</v>
+      </c>
+      <c r="V230" t="n">
+        <v>3</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1</v>
+      </c>
+      <c r="X230" t="n">
+        <v>2</v>
       </c>
       <c r="Y230" t="inlineStr"/>
       <c r="Z230" t="inlineStr"/>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AA230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>4</v>
       </c>
       <c r="AE230" t="inlineStr"/>
       <c r="AF230" t="inlineStr"/>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL230" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>3</v>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
@@ -49860,64 +49820,308 @@
       </c>
       <c r="AU230" t="inlineStr"/>
       <c r="AV230" t="inlineStr"/>
-      <c r="AW230" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="AX230" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
+      <c r="AW230" t="n">
+        <v>411</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>697</v>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr"/>
       <c r="BA230" t="inlineStr"/>
       <c r="BB230" t="inlineStr"/>
-      <c r="BC230" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="BD230" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
+      <c r="BC230" t="n">
+        <v>347</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>604</v>
       </c>
       <c r="BE230" t="inlineStr"/>
       <c r="BF230" t="inlineStr"/>
-      <c r="BG230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BH230" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BI230" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ230" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK230" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>7</v>
       </c>
       <c r="BM230" t="inlineStr"/>
       <c r="BN230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>f5f1oGre</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>22.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Nouste Camp
+ (Pau)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>4 031</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>3 431</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr"/>
+      <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr"/>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AN231" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AQ231" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU231" t="inlineStr"/>
+      <c r="AV231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr"/>
+      <c r="BA231" t="inlineStr"/>
+      <c r="BB231" t="inlineStr"/>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="BD231" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BH231" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BI231" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BJ231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BL231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BM231" t="inlineStr"/>
+      <c r="BN231" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN231"/>
+  <dimension ref="A1:BN249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49892,15 +49892,11 @@
           <t>3 431</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -49934,99 +49930,63 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q231" t="n">
+        <v>8</v>
+      </c>
+      <c r="R231" t="n">
+        <v>10</v>
+      </c>
+      <c r="S231" t="n">
+        <v>4</v>
+      </c>
+      <c r="T231" t="n">
+        <v>4</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0</v>
+      </c>
+      <c r="V231" t="n">
+        <v>4</v>
+      </c>
+      <c r="W231" t="n">
+        <v>4</v>
+      </c>
+      <c r="X231" t="n">
+        <v>2</v>
       </c>
       <c r="Y231" t="inlineStr"/>
       <c r="Z231" t="inlineStr"/>
-      <c r="AA231" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA231" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
       </c>
       <c r="AE231" t="inlineStr"/>
       <c r="AF231" t="inlineStr"/>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>2</v>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
@@ -50064,64 +50024,4144 @@
       </c>
       <c r="AU231" t="inlineStr"/>
       <c r="AV231" t="inlineStr"/>
-      <c r="AW231" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="AX231" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="AW231" t="n">
+        <v>361</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>591</v>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr"/>
       <c r="BA231" t="inlineStr"/>
       <c r="BB231" t="inlineStr"/>
-      <c r="BC231" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="BD231" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
+      <c r="BC231" t="n">
+        <v>273</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>489</v>
       </c>
       <c r="BE231" t="inlineStr"/>
       <c r="BF231" t="inlineStr"/>
-      <c r="BG231" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BH231" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BI231" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BJ231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK231" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BL231" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BG231" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>5</v>
       </c>
       <c r="BM231" t="inlineStr"/>
       <c r="BN231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>26.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="M232" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N232" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>11</v>
+      </c>
+      <c r="R232" t="n">
+        <v>11</v>
+      </c>
+      <c r="S232" t="n">
+        <v>4</v>
+      </c>
+      <c r="T232" t="n">
+        <v>3</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2</v>
+      </c>
+      <c r="V232" t="n">
+        <v>1</v>
+      </c>
+      <c r="W232" t="n">
+        <v>5</v>
+      </c>
+      <c r="X232" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AN232" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AQ232" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU232" t="inlineStr"/>
+      <c r="AV232" t="inlineStr"/>
+      <c r="AW232" t="n">
+        <v>429</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>316</v>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr"/>
+      <c r="BA232" t="inlineStr"/>
+      <c r="BB232" t="inlineStr"/>
+      <c r="BC232" t="n">
+        <v>326</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>233</v>
+      </c>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM232" t="inlineStr"/>
+      <c r="BN232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>26.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="M233" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>11</v>
+      </c>
+      <c r="R233" t="n">
+        <v>13</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3</v>
+      </c>
+      <c r="T233" t="n">
+        <v>4</v>
+      </c>
+      <c r="U233" t="n">
+        <v>6</v>
+      </c>
+      <c r="V233" t="n">
+        <v>4</v>
+      </c>
+      <c r="W233" t="n">
+        <v>2</v>
+      </c>
+      <c r="X233" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AN233" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AQ233" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU233" t="inlineStr"/>
+      <c r="AV233" t="inlineStr"/>
+      <c r="AW233" t="n">
+        <v>412</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>377</v>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr"/>
+      <c r="BA233" t="inlineStr"/>
+      <c r="BB233" t="inlineStr"/>
+      <c r="BC233" t="n">
+        <v>348</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>297</v>
+      </c>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
+      <c r="BI233" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM233" t="inlineStr"/>
+      <c r="BN233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>26.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>13 796</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>4</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="M234" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>13</v>
+      </c>
+      <c r="R234" t="n">
+        <v>19</v>
+      </c>
+      <c r="S234" t="n">
+        <v>8</v>
+      </c>
+      <c r="T234" t="n">
+        <v>7</v>
+      </c>
+      <c r="U234" t="n">
+        <v>4</v>
+      </c>
+      <c r="V234" t="n">
+        <v>5</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1</v>
+      </c>
+      <c r="X234" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AN234" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AQ234" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU234" t="inlineStr"/>
+      <c r="AV234" t="inlineStr"/>
+      <c r="AW234" t="n">
+        <v>397</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>564</v>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr"/>
+      <c r="BA234" t="inlineStr"/>
+      <c r="BB234" t="inlineStr"/>
+      <c r="BC234" t="n">
+        <v>318</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>483</v>
+      </c>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
+      <c r="BI234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM234" t="inlineStr"/>
+      <c r="BN234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>27 130</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="M235" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>20</v>
+      </c>
+      <c r="R235" t="n">
+        <v>5</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1</v>
+      </c>
+      <c r="U235" t="n">
+        <v>8</v>
+      </c>
+      <c r="V235" t="n">
+        <v>2</v>
+      </c>
+      <c r="W235" t="n">
+        <v>8</v>
+      </c>
+      <c r="X235" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AN235" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AQ235" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>538</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>361</v>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr"/>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="n">
+        <v>465</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>287</v>
+      </c>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
+      <c r="BI235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM235" t="inlineStr"/>
+      <c r="BN235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Wplzx9A5</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>26.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>4</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0</v>
+      </c>
+      <c r="V236" t="n">
+        <v>2</v>
+      </c>
+      <c r="W236" t="n">
+        <v>0</v>
+      </c>
+      <c r="X236" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y236" t="inlineStr"/>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE236" t="inlineStr"/>
+      <c r="AF236" t="inlineStr"/>
+      <c r="AG236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AN236" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AQ236" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU236" t="inlineStr"/>
+      <c r="AV236" t="inlineStr"/>
+      <c r="AW236" t="n">
+        <v>153</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>146</v>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr"/>
+      <c r="BA236" t="inlineStr"/>
+      <c r="BB236" t="inlineStr"/>
+      <c r="BC236" t="n">
+        <v>111</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>99</v>
+      </c>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM236" t="inlineStr"/>
+      <c r="BN236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>dheSbdqf</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>26.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Petit A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>15 771</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>14</v>
+      </c>
+      <c r="R237" t="n">
+        <v>10</v>
+      </c>
+      <c r="S237" t="n">
+        <v>4</v>
+      </c>
+      <c r="T237" t="n">
+        <v>5</v>
+      </c>
+      <c r="U237" t="n">
+        <v>4</v>
+      </c>
+      <c r="V237" t="n">
+        <v>3</v>
+      </c>
+      <c r="W237" t="n">
+        <v>6</v>
+      </c>
+      <c r="X237" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y237" t="inlineStr"/>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="inlineStr"/>
+      <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AN237" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AQ237" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>614</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>337</v>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr"/>
+      <c r="BA237" t="inlineStr"/>
+      <c r="BB237" t="inlineStr"/>
+      <c r="BC237" t="n">
+        <v>518</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>238</v>
+      </c>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>34</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>11</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM237" t="inlineStr"/>
+      <c r="BN237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>25dJuiBt</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>26.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Stade Charlety
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>15 412</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>2</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>18</v>
+      </c>
+      <c r="R238" t="n">
+        <v>8</v>
+      </c>
+      <c r="S238" t="n">
+        <v>9</v>
+      </c>
+      <c r="T238" t="n">
+        <v>3</v>
+      </c>
+      <c r="U238" t="n">
+        <v>6</v>
+      </c>
+      <c r="V238" t="n">
+        <v>1</v>
+      </c>
+      <c r="W238" t="n">
+        <v>3</v>
+      </c>
+      <c r="X238" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y238" t="inlineStr"/>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE238" t="inlineStr"/>
+      <c r="AF238" t="inlineStr"/>
+      <c r="AG238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM238" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AN238" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AQ238" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU238" t="inlineStr"/>
+      <c r="AV238" t="inlineStr"/>
+      <c r="AW238" t="n">
+        <v>569</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>454</v>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr"/>
+      <c r="BA238" t="inlineStr"/>
+      <c r="BB238" t="inlineStr"/>
+      <c r="BC238" t="n">
+        <v>497</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>370</v>
+      </c>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI238" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ238" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK238" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM238" t="inlineStr"/>
+      <c r="BN238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>dW3GHvPj</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Parc des Sports
+ (Annecy)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>15 660</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>5 362</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>14</v>
+      </c>
+      <c r="R239" t="n">
+        <v>13</v>
+      </c>
+      <c r="S239" t="n">
+        <v>4</v>
+      </c>
+      <c r="T239" t="n">
+        <v>2</v>
+      </c>
+      <c r="U239" t="n">
+        <v>5</v>
+      </c>
+      <c r="V239" t="n">
+        <v>8</v>
+      </c>
+      <c r="W239" t="n">
+        <v>5</v>
+      </c>
+      <c r="X239" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y239" t="inlineStr"/>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE239" t="inlineStr"/>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AN239" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AQ239" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU239" t="inlineStr"/>
+      <c r="AV239" t="inlineStr"/>
+      <c r="AW239" t="n">
+        <v>394</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>383</v>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr"/>
+      <c r="BA239" t="inlineStr"/>
+      <c r="BB239" t="inlineStr"/>
+      <c r="BC239" t="n">
+        <v>256</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>235</v>
+      </c>
+      <c r="BE239" t="inlineStr"/>
+      <c r="BF239" t="inlineStr"/>
+      <c r="BG239" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>OvR8LmQO</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>5 004</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>10</v>
+      </c>
+      <c r="R240" t="n">
+        <v>10</v>
+      </c>
+      <c r="S240" t="n">
+        <v>2</v>
+      </c>
+      <c r="T240" t="n">
+        <v>4</v>
+      </c>
+      <c r="U240" t="n">
+        <v>4</v>
+      </c>
+      <c r="V240" t="n">
+        <v>4</v>
+      </c>
+      <c r="W240" t="n">
+        <v>4</v>
+      </c>
+      <c r="X240" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y240" t="inlineStr"/>
+      <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="inlineStr"/>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM240" t="inlineStr">
+        <is>
+          <t>4G9MhScS</t>
+        </is>
+      </c>
+      <c r="AN240" t="inlineStr">
+        <is>
+          <t>bichard sebastien</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AQ240" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU240" t="inlineStr"/>
+      <c r="AV240" t="inlineStr"/>
+      <c r="AW240" t="n">
+        <v>526</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>396</v>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr"/>
+      <c r="BA240" t="inlineStr"/>
+      <c r="BB240" t="inlineStr"/>
+      <c r="BC240" t="n">
+        <v>424</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>293</v>
+      </c>
+      <c r="BE240" t="inlineStr"/>
+      <c r="BF240" t="inlineStr"/>
+      <c r="BG240" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>17</v>
+      </c>
+      <c r="BM240" t="inlineStr"/>
+      <c r="BN240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>xrirzmuI</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>4 605</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>13</v>
+      </c>
+      <c r="R241" t="n">
+        <v>7</v>
+      </c>
+      <c r="S241" t="n">
+        <v>6</v>
+      </c>
+      <c r="T241" t="n">
+        <v>1</v>
+      </c>
+      <c r="U241" t="n">
+        <v>2</v>
+      </c>
+      <c r="V241" t="n">
+        <v>5</v>
+      </c>
+      <c r="W241" t="n">
+        <v>5</v>
+      </c>
+      <c r="X241" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y241" t="inlineStr"/>
+      <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="inlineStr"/>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AN241" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AQ241" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU241" t="inlineStr"/>
+      <c r="AV241" t="inlineStr"/>
+      <c r="AW241" t="n">
+        <v>429</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>466</v>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr"/>
+      <c r="BA241" t="inlineStr"/>
+      <c r="BB241" t="inlineStr"/>
+      <c r="BC241" t="n">
+        <v>352</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>379</v>
+      </c>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH241" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI241" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ241" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK241" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL241" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM241" t="inlineStr"/>
+      <c r="BN241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>8rypRidm</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Stade Saint-Symphorien
+ (Metz)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>28 786</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>19 290</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>14</v>
+      </c>
+      <c r="R242" t="n">
+        <v>10</v>
+      </c>
+      <c r="S242" t="n">
+        <v>7</v>
+      </c>
+      <c r="T242" t="n">
+        <v>3</v>
+      </c>
+      <c r="U242" t="n">
+        <v>4</v>
+      </c>
+      <c r="V242" t="n">
+        <v>4</v>
+      </c>
+      <c r="W242" t="n">
+        <v>3</v>
+      </c>
+      <c r="X242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y242" t="inlineStr"/>
+      <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="inlineStr"/>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK242" t="inlineStr"/>
+      <c r="AL242" t="inlineStr"/>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AQ242" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU242" t="inlineStr"/>
+      <c r="AV242" t="inlineStr"/>
+      <c r="AW242" t="n">
+        <v>546</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>479</v>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr"/>
+      <c r="BA242" t="inlineStr"/>
+      <c r="BB242" t="inlineStr"/>
+      <c r="BC242" t="n">
+        <v>465</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>388</v>
+      </c>
+      <c r="BE242" t="inlineStr"/>
+      <c r="BF242" t="inlineStr"/>
+      <c r="BG242" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>17</v>
+      </c>
+      <c r="BI242" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ242" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK242" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>18</v>
+      </c>
+      <c r="BM242" t="inlineStr"/>
+      <c r="BN242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>zJfRwVug</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Nouste Camp
+ (Pau)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>4 031</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>3 034</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>11</v>
+      </c>
+      <c r="R243" t="n">
+        <v>10</v>
+      </c>
+      <c r="S243" t="n">
+        <v>3</v>
+      </c>
+      <c r="T243" t="n">
+        <v>4</v>
+      </c>
+      <c r="U243" t="n">
+        <v>5</v>
+      </c>
+      <c r="V243" t="n">
+        <v>4</v>
+      </c>
+      <c r="W243" t="n">
+        <v>3</v>
+      </c>
+      <c r="X243" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y243" t="inlineStr"/>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE243" t="inlineStr"/>
+      <c r="AF243" t="inlineStr"/>
+      <c r="AG243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AN243" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AQ243" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU243" t="inlineStr"/>
+      <c r="AV243" t="inlineStr"/>
+      <c r="AW243" t="n">
+        <v>575</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>385</v>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr"/>
+      <c r="BA243" t="inlineStr"/>
+      <c r="BB243" t="inlineStr"/>
+      <c r="BC243" t="n">
+        <v>486</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>275</v>
+      </c>
+      <c r="BE243" t="inlineStr"/>
+      <c r="BF243" t="inlineStr"/>
+      <c r="BG243" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>45</v>
+      </c>
+      <c r="BI243" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ243" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK243" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM243" t="inlineStr"/>
+      <c r="BN243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>xOS0N9eC</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Stade Paul-Lignon
+ (Rodez)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>5 955</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>4 024</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>3</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>15</v>
+      </c>
+      <c r="R244" t="n">
+        <v>13</v>
+      </c>
+      <c r="S244" t="n">
+        <v>5</v>
+      </c>
+      <c r="T244" t="n">
+        <v>4</v>
+      </c>
+      <c r="U244" t="n">
+        <v>6</v>
+      </c>
+      <c r="V244" t="n">
+        <v>7</v>
+      </c>
+      <c r="W244" t="n">
+        <v>4</v>
+      </c>
+      <c r="X244" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y244" t="inlineStr"/>
+      <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="inlineStr"/>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AN244" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AQ244" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU244" t="inlineStr"/>
+      <c r="AV244" t="inlineStr"/>
+      <c r="AW244" t="n">
+        <v>397</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>530</v>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr"/>
+      <c r="BA244" t="inlineStr"/>
+      <c r="BB244" t="inlineStr"/>
+      <c r="BC244" t="n">
+        <v>308</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>435</v>
+      </c>
+      <c r="BE244" t="inlineStr"/>
+      <c r="BF244" t="inlineStr"/>
+      <c r="BG244" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI244" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ244" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK244" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM244" t="inlineStr"/>
+      <c r="BN244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>27.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>66 115</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AQ245" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr"/>
+      <c r="BA245" t="inlineStr"/>
+      <c r="BB245" t="inlineStr"/>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="BD245" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="BE245" t="inlineStr"/>
+      <c r="BF245" t="inlineStr"/>
+      <c r="BG245" t="inlineStr"/>
+      <c r="BH245" t="inlineStr"/>
+      <c r="BI245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK245" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL245" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BM245" t="inlineStr"/>
+      <c r="BN245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>14 111</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>gasset jean louis</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AQ246" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr"/>
+      <c r="BA246" t="inlineStr"/>
+      <c r="BB246" t="inlineStr"/>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="BD246" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="inlineStr"/>
+      <c r="BH246" t="inlineStr"/>
+      <c r="BI246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK246" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL246" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BM246" t="inlineStr"/>
+      <c r="BN246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>29 795</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AQ247" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr"/>
+      <c r="BA247" t="inlineStr"/>
+      <c r="BB247" t="inlineStr"/>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="BD247" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="inlineStr"/>
+      <c r="BH247" t="inlineStr"/>
+      <c r="BI247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK247" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BL247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>19 398</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AQ248" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU248" t="inlineStr"/>
+      <c r="AV248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr"/>
+      <c r="BA248" t="inlineStr"/>
+      <c r="BB248" t="inlineStr"/>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="BD248" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ248" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>54 868</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AQ249" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU249" t="inlineStr"/>
+      <c r="AV249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr"/>
+      <c r="BA249" t="inlineStr"/>
+      <c r="BB249" t="inlineStr"/>
+      <c r="BC249" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="BD249" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
+      <c r="BI249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ249" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK249" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL249" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BM249" t="inlineStr"/>
+      <c r="BN249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN249"/>
+  <dimension ref="A1:BN258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52772,15 +52772,11 @@
           <t>66 115</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -52802,15 +52798,11 @@
           <t>PSG</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
+      <c r="M245" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N245" t="n">
+        <v>2.98</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -52822,115 +52814,71 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q245" t="n">
+        <v>5</v>
+      </c>
+      <c r="R245" t="n">
+        <v>19</v>
+      </c>
+      <c r="S245" t="n">
+        <v>1</v>
+      </c>
+      <c r="T245" t="n">
+        <v>8</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2</v>
+      </c>
+      <c r="V245" t="n">
+        <v>9</v>
+      </c>
+      <c r="W245" t="n">
+        <v>2</v>
+      </c>
+      <c r="X245" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>0</v>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
@@ -52966,63 +52914,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW245" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="AX245" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
+      <c r="AU245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>309</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>918</v>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr"/>
       <c r="BA245" t="inlineStr"/>
       <c r="BB245" t="inlineStr"/>
-      <c r="BC245" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="BD245" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
+      <c r="BC245" t="n">
+        <v>241</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>863</v>
       </c>
       <c r="BE245" t="inlineStr"/>
       <c r="BF245" t="inlineStr"/>
       <c r="BG245" t="inlineStr"/>
       <c r="BH245" t="inlineStr"/>
-      <c r="BI245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BI245" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>9</v>
       </c>
       <c r="BM245" t="inlineStr"/>
       <c r="BN245" t="inlineStr"/>
@@ -53060,15 +52988,11 @@
           <t>14 111</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -53090,15 +53014,11 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
+      <c r="M246" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1.43</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -53110,115 +53030,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q246" t="n">
+        <v>9</v>
+      </c>
+      <c r="R246" t="n">
+        <v>15</v>
+      </c>
+      <c r="S246" t="n">
+        <v>2</v>
+      </c>
+      <c r="T246" t="n">
+        <v>6</v>
+      </c>
+      <c r="U246" t="n">
+        <v>5</v>
+      </c>
+      <c r="V246" t="n">
+        <v>5</v>
+      </c>
+      <c r="W246" t="n">
+        <v>2</v>
+      </c>
+      <c r="X246" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>2</v>
       </c>
       <c r="AM246" t="inlineStr">
         <is>
@@ -53254,63 +53130,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW246" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AX246" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
+      <c r="AU246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>487</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>465</v>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr"/>
       <c r="BA246" t="inlineStr"/>
       <c r="BB246" t="inlineStr"/>
-      <c r="BC246" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="BD246" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
+      <c r="BC246" t="n">
+        <v>416</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>403</v>
       </c>
       <c r="BE246" t="inlineStr"/>
       <c r="BF246" t="inlineStr"/>
       <c r="BG246" t="inlineStr"/>
       <c r="BH246" t="inlineStr"/>
-      <c r="BI246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK246" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL246" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BI246" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>10</v>
       </c>
       <c r="BM246" t="inlineStr"/>
       <c r="BN246" t="inlineStr"/>
@@ -53348,15 +53204,11 @@
           <t>29 795</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G247" t="n">
+        <v>2</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -53378,15 +53230,11 @@
           <t>Monaco</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+      <c r="M247" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0.4</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -53398,115 +53246,71 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q247" t="n">
+        <v>17</v>
+      </c>
+      <c r="R247" t="n">
+        <v>11</v>
+      </c>
+      <c r="S247" t="n">
+        <v>9</v>
+      </c>
+      <c r="T247" t="n">
+        <v>5</v>
+      </c>
+      <c r="U247" t="n">
+        <v>6</v>
+      </c>
+      <c r="V247" t="n">
+        <v>1</v>
+      </c>
+      <c r="W247" t="n">
+        <v>2</v>
+      </c>
+      <c r="X247" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>5</v>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
@@ -53542,63 +53346,43 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AW247" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="AX247" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
+      <c r="AU247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>313</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>477</v>
       </c>
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr"/>
       <c r="BA247" t="inlineStr"/>
       <c r="BB247" t="inlineStr"/>
-      <c r="BC247" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="BD247" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
+      <c r="BC247" t="n">
+        <v>246</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>396</v>
       </c>
       <c r="BE247" t="inlineStr"/>
       <c r="BF247" t="inlineStr"/>
       <c r="BG247" t="inlineStr"/>
       <c r="BH247" t="inlineStr"/>
-      <c r="BI247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK247" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BL247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BI247" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ247" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK247" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>7</v>
       </c>
       <c r="BM247" t="inlineStr"/>
       <c r="BN247" t="inlineStr"/>
@@ -53636,15 +53420,11 @@
           <t>19 398</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G248" t="n">
+        <v>3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -53666,15 +53446,11 @@
           <t>Nantes</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
+      <c r="M248" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0.74</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -53686,115 +53462,71 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q248" t="n">
+        <v>9</v>
+      </c>
+      <c r="R248" t="n">
+        <v>8</v>
+      </c>
+      <c r="S248" t="n">
+        <v>5</v>
+      </c>
+      <c r="T248" t="n">
+        <v>6</v>
+      </c>
+      <c r="U248" t="n">
+        <v>1</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1</v>
+      </c>
+      <c r="W248" t="n">
+        <v>3</v>
+      </c>
+      <c r="X248" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>3</v>
       </c>
       <c r="AM248" t="inlineStr">
         <is>
@@ -53832,53 +53564,37 @@
       </c>
       <c r="AU248" t="inlineStr"/>
       <c r="AV248" t="inlineStr"/>
-      <c r="AW248" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AX248" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
+      <c r="AW248" t="n">
+        <v>487</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>479</v>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr"/>
       <c r="BA248" t="inlineStr"/>
       <c r="BB248" t="inlineStr"/>
-      <c r="BC248" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="BD248" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
+      <c r="BC248" t="n">
+        <v>412</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>401</v>
       </c>
       <c r="BE248" t="inlineStr"/>
       <c r="BF248" t="inlineStr"/>
       <c r="BG248" t="inlineStr"/>
       <c r="BH248" t="inlineStr"/>
-      <c r="BI248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ248" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BK248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BI248" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ248" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK248" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL248" t="n">
+        <v>6</v>
       </c>
       <c r="BM248" t="inlineStr"/>
       <c r="BN248" t="inlineStr"/>
@@ -53916,15 +53632,11 @@
           <t>54 868</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -53946,15 +53658,11 @@
           <t>Auxerre</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="M249" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N249" t="n">
+        <v>1.3</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -53966,115 +53674,71 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q249" t="n">
+        <v>12</v>
+      </c>
+      <c r="R249" t="n">
+        <v>17</v>
+      </c>
+      <c r="S249" t="n">
+        <v>8</v>
+      </c>
+      <c r="T249" t="n">
+        <v>4</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2</v>
+      </c>
+      <c r="V249" t="n">
+        <v>7</v>
+      </c>
+      <c r="W249" t="n">
+        <v>2</v>
+      </c>
+      <c r="X249" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>4</v>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
@@ -54112,56 +53776,2432 @@
       </c>
       <c r="AU249" t="inlineStr"/>
       <c r="AV249" t="inlineStr"/>
-      <c r="AW249" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="AX249" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+      <c r="AW249" t="n">
+        <v>519</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>286</v>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr"/>
       <c r="BA249" t="inlineStr"/>
       <c r="BB249" t="inlineStr"/>
-      <c r="BC249" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="BD249" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+      <c r="BC249" t="n">
+        <v>442</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>219</v>
       </c>
       <c r="BE249" t="inlineStr"/>
       <c r="BF249" t="inlineStr"/>
       <c r="BG249" t="inlineStr"/>
       <c r="BH249" t="inlineStr"/>
-      <c r="BI249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ249" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BK249" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL249" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BI249" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK249" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>12</v>
       </c>
       <c r="BM249" t="inlineStr"/>
       <c r="BN249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>K4kBwMoA</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Landry R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Stade de la Licorne
+ (Amiens)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>12 097</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>8 171</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr"/>
+      <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AQ250" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU250" t="inlineStr"/>
+      <c r="AV250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr"/>
+      <c r="BA250" t="inlineStr"/>
+      <c r="BB250" t="inlineStr"/>
+      <c r="BC250" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="BD250" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BI250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK250" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL250" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BM250" t="inlineStr"/>
+      <c r="BN250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>hImJy0GM</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Buquet R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Stade Armand Cesari
+ (Bastia)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>16 048</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>9 809</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr"/>
+      <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr"/>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AN251" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AQ251" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU251" t="inlineStr"/>
+      <c r="AV251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr"/>
+      <c r="BA251" t="inlineStr"/>
+      <c r="BB251" t="inlineStr"/>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="BD251" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BH251" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BI251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BK251" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL251" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BM251" t="inlineStr"/>
+      <c r="BN251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>UD9kUH8d</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Abed K.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Stade des Alpes
+ (Grenoble)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>20 068</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>7 920</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr"/>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr"/>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AQ252" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr"/>
+      <c r="AV252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr"/>
+      <c r="BA252" t="inlineStr"/>
+      <c r="BB252" t="inlineStr"/>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="BD252" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BI252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK252" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BL252" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BM252" t="inlineStr"/>
+      <c r="BN252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Mm6sWwvp</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Valnet A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>7 187</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr"/>
+      <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr"/>
+      <c r="AF253" t="inlineStr"/>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AN253" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AQ253" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU253" t="inlineStr"/>
+      <c r="AV253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr"/>
+      <c r="BA253" t="inlineStr"/>
+      <c r="BB253" t="inlineStr"/>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="BD253" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="BE253" t="inlineStr"/>
+      <c r="BF253" t="inlineStr"/>
+      <c r="BG253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BH253" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BI253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK253" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL253" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BM253" t="inlineStr"/>
+      <c r="BN253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>CYrglw0S</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Stade Francis Le Basser
+ (Laval)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>11 017</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>6 799</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr"/>
+      <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr"/>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AN254" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>E3v5aJXp</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>gas emmanuel</t>
+        </is>
+      </c>
+      <c r="AQ254" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU254" t="inlineStr"/>
+      <c r="AV254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr"/>
+      <c r="BA254" t="inlineStr"/>
+      <c r="BB254" t="inlineStr"/>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="BD254" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="BE254" t="inlineStr"/>
+      <c r="BF254" t="inlineStr"/>
+      <c r="BG254" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BH254" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BI254" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ254" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BK254" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL254" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM254" t="inlineStr"/>
+      <c r="BN254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>A9nxhL03</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Gaillouste P.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Stade du Moustoir
+ (Lorient)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>16 787</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>12 036</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr"/>
+      <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr"/>
+      <c r="AF255" t="inlineStr"/>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AN255" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AQ255" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr"/>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="BD255" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
+      <c r="BG255" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BH255" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BI255" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BK255" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BL255" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BM255" t="inlineStr"/>
+      <c r="BN255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Oxd2urHc</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Rosier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Stade Francis Turcan
+ (Martigues)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr"/>
+      <c r="Z256" t="inlineStr"/>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr"/>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AN256" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AQ256" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr"/>
+      <c r="BA256" t="inlineStr"/>
+      <c r="BB256" t="inlineStr"/>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="BD256" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BH256" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BI256" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ256" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BK256" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BL256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM256" t="inlineStr"/>
+      <c r="BN256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>IZkpjaVF</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Chapapria R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Stade Bauer
+ (Paris - Saint-Ouen)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>4 643</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr"/>
+      <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr"/>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AN257" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AQ257" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU257" t="inlineStr"/>
+      <c r="AV257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr"/>
+      <c r="BA257" t="inlineStr"/>
+      <c r="BB257" t="inlineStr"/>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="BD257" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="BE257" t="inlineStr"/>
+      <c r="BF257" t="inlineStr"/>
+      <c r="BG257" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="BH257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BI257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ257" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BK257" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BL257" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>U5gzczE6</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Bouille T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>4 810</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr"/>
+      <c r="Z258" t="inlineStr"/>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr"/>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL258" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AN258" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AQ258" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU258" t="inlineStr"/>
+      <c r="AV258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr"/>
+      <c r="BA258" t="inlineStr"/>
+      <c r="BB258" t="inlineStr"/>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="BD258" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="BE258" t="inlineStr"/>
+      <c r="BF258" t="inlineStr"/>
+      <c r="BG258" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BH258" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK258" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL258" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM258" t="inlineStr"/>
+      <c r="BN258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN258"/>
+  <dimension ref="A1:BN276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53844,15 +53844,11 @@
           <t>8 171</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -53886,99 +53882,63 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q250" t="n">
+        <v>15</v>
+      </c>
+      <c r="R250" t="n">
+        <v>14</v>
+      </c>
+      <c r="S250" t="n">
+        <v>3</v>
+      </c>
+      <c r="T250" t="n">
+        <v>4</v>
+      </c>
+      <c r="U250" t="n">
+        <v>5</v>
+      </c>
+      <c r="V250" t="n">
+        <v>9</v>
+      </c>
+      <c r="W250" t="n">
+        <v>7</v>
+      </c>
+      <c r="X250" t="n">
+        <v>1</v>
       </c>
       <c r="Y250" t="inlineStr"/>
       <c r="Z250" t="inlineStr"/>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA250" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>2</v>
       </c>
       <c r="AE250" t="inlineStr"/>
       <c r="AF250" t="inlineStr"/>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>2</v>
       </c>
       <c r="AM250" t="inlineStr">
         <is>
@@ -54016,61 +53976,41 @@
       </c>
       <c r="AU250" t="inlineStr"/>
       <c r="AV250" t="inlineStr"/>
-      <c r="AW250" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="AX250" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
+      <c r="AW250" t="n">
+        <v>320</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>686</v>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr"/>
       <c r="BA250" t="inlineStr"/>
       <c r="BB250" t="inlineStr"/>
-      <c r="BC250" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="BD250" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
+      <c r="BC250" t="n">
+        <v>250</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>643</v>
       </c>
       <c r="BE250" t="inlineStr"/>
       <c r="BF250" t="inlineStr"/>
-      <c r="BG250" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BH250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BI250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK250" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL250" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BG250" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI250" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ250" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK250" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>11</v>
       </c>
       <c r="BM250" t="inlineStr"/>
       <c r="BN250" t="inlineStr"/>
@@ -54108,15 +54048,11 @@
           <t>9 809</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G251" t="n">
+        <v>2</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -54150,99 +54086,63 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q251" t="n">
+        <v>17</v>
+      </c>
+      <c r="R251" t="n">
+        <v>14</v>
+      </c>
+      <c r="S251" t="n">
+        <v>6</v>
+      </c>
+      <c r="T251" t="n">
+        <v>3</v>
+      </c>
+      <c r="U251" t="n">
+        <v>6</v>
+      </c>
+      <c r="V251" t="n">
+        <v>4</v>
+      </c>
+      <c r="W251" t="n">
+        <v>5</v>
+      </c>
+      <c r="X251" t="n">
+        <v>7</v>
       </c>
       <c r="Y251" t="inlineStr"/>
       <c r="Z251" t="inlineStr"/>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AA251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>2</v>
       </c>
       <c r="AE251" t="inlineStr"/>
       <c r="AF251" t="inlineStr"/>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>2</v>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
@@ -54280,61 +54180,41 @@
       </c>
       <c r="AU251" t="inlineStr"/>
       <c r="AV251" t="inlineStr"/>
-      <c r="AW251" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AX251" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="AW251" t="n">
+        <v>445</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>300</v>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr"/>
       <c r="BA251" t="inlineStr"/>
       <c r="BB251" t="inlineStr"/>
-      <c r="BC251" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="BD251" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="BC251" t="n">
+        <v>356</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>189</v>
       </c>
       <c r="BE251" t="inlineStr"/>
       <c r="BF251" t="inlineStr"/>
-      <c r="BG251" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BH251" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ251" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BK251" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL251" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BG251" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH251" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI251" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ251" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>13</v>
       </c>
       <c r="BM251" t="inlineStr"/>
       <c r="BN251" t="inlineStr"/>
@@ -54372,15 +54252,11 @@
           <t>7 920</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -54414,99 +54290,63 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q252" t="n">
+        <v>7</v>
+      </c>
+      <c r="R252" t="n">
+        <v>16</v>
+      </c>
+      <c r="S252" t="n">
+        <v>2</v>
+      </c>
+      <c r="T252" t="n">
+        <v>6</v>
+      </c>
+      <c r="U252" t="n">
+        <v>1</v>
+      </c>
+      <c r="V252" t="n">
+        <v>6</v>
+      </c>
+      <c r="W252" t="n">
+        <v>4</v>
+      </c>
+      <c r="X252" t="n">
+        <v>4</v>
       </c>
       <c r="Y252" t="inlineStr"/>
       <c r="Z252" t="inlineStr"/>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>0</v>
       </c>
       <c r="AE252" t="inlineStr"/>
       <c r="AF252" t="inlineStr"/>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG252" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>2</v>
       </c>
       <c r="AM252" t="inlineStr">
         <is>
@@ -54544,61 +54384,41 @@
       </c>
       <c r="AU252" t="inlineStr"/>
       <c r="AV252" t="inlineStr"/>
-      <c r="AW252" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="AX252" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
+      <c r="AW252" t="n">
+        <v>459</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>469</v>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr"/>
       <c r="BA252" t="inlineStr"/>
       <c r="BB252" t="inlineStr"/>
-      <c r="BC252" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="BD252" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
+      <c r="BC252" t="n">
+        <v>312</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>340</v>
       </c>
       <c r="BE252" t="inlineStr"/>
       <c r="BF252" t="inlineStr"/>
-      <c r="BG252" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="BH252" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BI252" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BJ252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK252" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BL252" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BG252" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH252" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI252" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ252" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>14</v>
       </c>
       <c r="BM252" t="inlineStr"/>
       <c r="BN252" t="inlineStr"/>
@@ -54636,15 +54456,11 @@
           <t>7 187</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -54678,99 +54494,63 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q253" t="n">
+        <v>11</v>
+      </c>
+      <c r="R253" t="n">
+        <v>6</v>
+      </c>
+      <c r="S253" t="n">
+        <v>5</v>
+      </c>
+      <c r="T253" t="n">
+        <v>4</v>
+      </c>
+      <c r="U253" t="n">
+        <v>4</v>
+      </c>
+      <c r="V253" t="n">
+        <v>1</v>
+      </c>
+      <c r="W253" t="n">
+        <v>2</v>
+      </c>
+      <c r="X253" t="n">
+        <v>1</v>
       </c>
       <c r="Y253" t="inlineStr"/>
       <c r="Z253" t="inlineStr"/>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>0</v>
       </c>
       <c r="AE253" t="inlineStr"/>
       <c r="AF253" t="inlineStr"/>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>1</v>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
@@ -54808,61 +54588,41 @@
       </c>
       <c r="AU253" t="inlineStr"/>
       <c r="AV253" t="inlineStr"/>
-      <c r="AW253" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="AX253" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
+      <c r="AW253" t="n">
+        <v>498</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>418</v>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr"/>
       <c r="BA253" t="inlineStr"/>
       <c r="BB253" t="inlineStr"/>
-      <c r="BC253" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="BD253" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="BC253" t="n">
+        <v>397</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>326</v>
       </c>
       <c r="BE253" t="inlineStr"/>
       <c r="BF253" t="inlineStr"/>
-      <c r="BG253" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BH253" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BI253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK253" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL253" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="BG253" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>24</v>
       </c>
       <c r="BM253" t="inlineStr"/>
       <c r="BN253" t="inlineStr"/>
@@ -54900,15 +54660,11 @@
           <t>6 799</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -54942,99 +54698,63 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q254" t="n">
+        <v>14</v>
+      </c>
+      <c r="R254" t="n">
+        <v>9</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4</v>
+      </c>
+      <c r="T254" t="n">
+        <v>4</v>
+      </c>
+      <c r="U254" t="n">
+        <v>6</v>
+      </c>
+      <c r="V254" t="n">
+        <v>2</v>
+      </c>
+      <c r="W254" t="n">
+        <v>4</v>
+      </c>
+      <c r="X254" t="n">
+        <v>3</v>
       </c>
       <c r="Y254" t="inlineStr"/>
       <c r="Z254" t="inlineStr"/>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>0</v>
       </c>
       <c r="AE254" t="inlineStr"/>
       <c r="AF254" t="inlineStr"/>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AG254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>2</v>
       </c>
       <c r="AM254" t="inlineStr">
         <is>
@@ -55072,61 +54792,41 @@
       </c>
       <c r="AU254" t="inlineStr"/>
       <c r="AV254" t="inlineStr"/>
-      <c r="AW254" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="AX254" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
+      <c r="AW254" t="n">
+        <v>449</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>547</v>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr"/>
       <c r="BA254" t="inlineStr"/>
       <c r="BB254" t="inlineStr"/>
-      <c r="BC254" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="BD254" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
+      <c r="BC254" t="n">
+        <v>360</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>471</v>
       </c>
       <c r="BE254" t="inlineStr"/>
       <c r="BF254" t="inlineStr"/>
-      <c r="BG254" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BH254" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="BI254" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ254" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BK254" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL254" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BG254" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK254" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL254" t="n">
+        <v>6</v>
       </c>
       <c r="BM254" t="inlineStr"/>
       <c r="BN254" t="inlineStr"/>
@@ -55164,15 +54864,11 @@
           <t>12 036</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G255" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -55206,99 +54902,63 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q255" t="n">
+        <v>11</v>
+      </c>
+      <c r="R255" t="n">
+        <v>9</v>
+      </c>
+      <c r="S255" t="n">
+        <v>5</v>
+      </c>
+      <c r="T255" t="n">
+        <v>4</v>
+      </c>
+      <c r="U255" t="n">
+        <v>1</v>
+      </c>
+      <c r="V255" t="n">
+        <v>2</v>
+      </c>
+      <c r="W255" t="n">
+        <v>5</v>
+      </c>
+      <c r="X255" t="n">
+        <v>3</v>
       </c>
       <c r="Y255" t="inlineStr"/>
       <c r="Z255" t="inlineStr"/>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>0</v>
       </c>
       <c r="AE255" t="inlineStr"/>
       <c r="AF255" t="inlineStr"/>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>3</v>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
@@ -55334,71 +54994,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AW255" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="AX255" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
+      <c r="AU255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>396</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>473</v>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr"/>
       <c r="BA255" t="inlineStr"/>
       <c r="BB255" t="inlineStr"/>
-      <c r="BC255" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="BD255" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
+      <c r="BC255" t="n">
+        <v>308</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>378</v>
       </c>
       <c r="BE255" t="inlineStr"/>
       <c r="BF255" t="inlineStr"/>
-      <c r="BG255" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BH255" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BI255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ255" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BK255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BL255" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BG255" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>14</v>
       </c>
       <c r="BM255" t="inlineStr"/>
       <c r="BN255" t="inlineStr"/>
@@ -55436,15 +55072,11 @@
           <t>580</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -55478,99 +55110,63 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q256" t="n">
+        <v>10</v>
+      </c>
+      <c r="R256" t="n">
+        <v>15</v>
+      </c>
+      <c r="S256" t="n">
+        <v>1</v>
+      </c>
+      <c r="T256" t="n">
+        <v>7</v>
+      </c>
+      <c r="U256" t="n">
+        <v>4</v>
+      </c>
+      <c r="V256" t="n">
+        <v>6</v>
+      </c>
+      <c r="W256" t="n">
+        <v>5</v>
+      </c>
+      <c r="X256" t="n">
+        <v>2</v>
       </c>
       <c r="Y256" t="inlineStr"/>
       <c r="Z256" t="inlineStr"/>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AA256" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>1</v>
       </c>
       <c r="AE256" t="inlineStr"/>
       <c r="AF256" t="inlineStr"/>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL256" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>3</v>
       </c>
       <c r="AM256" t="inlineStr">
         <is>
@@ -55606,71 +55202,47 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW256" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="AX256" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
+      <c r="AU256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>359</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>479</v>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr"/>
       <c r="BA256" t="inlineStr"/>
       <c r="BB256" t="inlineStr"/>
-      <c r="BC256" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="BD256" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
+      <c r="BC256" t="n">
+        <v>270</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>393</v>
       </c>
       <c r="BE256" t="inlineStr"/>
       <c r="BF256" t="inlineStr"/>
-      <c r="BG256" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BH256" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BI256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ256" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BK256" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BL256" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BG256" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI256" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ256" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK256" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>6</v>
       </c>
       <c r="BM256" t="inlineStr"/>
       <c r="BN256" t="inlineStr"/>
@@ -55708,15 +55280,11 @@
           <t>4 643</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -55750,99 +55318,63 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q257" t="n">
+        <v>6</v>
+      </c>
+      <c r="R257" t="n">
+        <v>16</v>
+      </c>
+      <c r="S257" t="n">
+        <v>2</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2</v>
+      </c>
+      <c r="V257" t="n">
+        <v>9</v>
+      </c>
+      <c r="W257" t="n">
+        <v>2</v>
+      </c>
+      <c r="X257" t="n">
+        <v>6</v>
       </c>
       <c r="Y257" t="inlineStr"/>
       <c r="Z257" t="inlineStr"/>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AA257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>3</v>
       </c>
       <c r="AE257" t="inlineStr"/>
       <c r="AF257" t="inlineStr"/>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AG257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>1</v>
       </c>
       <c r="AM257" t="inlineStr">
         <is>
@@ -55880,61 +55412,41 @@
       </c>
       <c r="AU257" t="inlineStr"/>
       <c r="AV257" t="inlineStr"/>
-      <c r="AW257" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="AX257" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
+      <c r="AW257" t="n">
+        <v>373</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>642</v>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr"/>
       <c r="BA257" t="inlineStr"/>
       <c r="BB257" t="inlineStr"/>
-      <c r="BC257" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="BD257" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
+      <c r="BC257" t="n">
+        <v>301</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>579</v>
       </c>
       <c r="BE257" t="inlineStr"/>
       <c r="BF257" t="inlineStr"/>
-      <c r="BG257" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="BH257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BI257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ257" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BK257" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BL257" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BG257" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI257" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ257" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK257" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL257" t="n">
+        <v>5</v>
       </c>
       <c r="BM257" t="inlineStr"/>
       <c r="BN257" t="inlineStr"/>
@@ -55972,15 +55484,11 @@
           <t>4 810</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G258" t="n">
+        <v>3</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -56014,99 +55522,63 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q258" t="n">
+        <v>18</v>
+      </c>
+      <c r="R258" t="n">
+        <v>9</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="n">
+        <v>2</v>
+      </c>
+      <c r="U258" t="n">
+        <v>7</v>
+      </c>
+      <c r="V258" t="n">
+        <v>4</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1</v>
+      </c>
+      <c r="X258" t="n">
+        <v>3</v>
       </c>
       <c r="Y258" t="inlineStr"/>
       <c r="Z258" t="inlineStr"/>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>0</v>
       </c>
       <c r="AE258" t="inlineStr"/>
       <c r="AF258" t="inlineStr"/>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL258" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AG258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>3</v>
       </c>
       <c r="AM258" t="inlineStr">
         <is>
@@ -56144,64 +55616,3852 @@
       </c>
       <c r="AU258" t="inlineStr"/>
       <c r="AV258" t="inlineStr"/>
-      <c r="AW258" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AX258" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
+      <c r="AW258" t="n">
+        <v>409</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>673</v>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr"/>
       <c r="BA258" t="inlineStr"/>
       <c r="BB258" t="inlineStr"/>
-      <c r="BC258" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="BD258" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
+      <c r="BC258" t="n">
+        <v>337</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>585</v>
       </c>
       <c r="BE258" t="inlineStr"/>
       <c r="BF258" t="inlineStr"/>
-      <c r="BG258" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="BH258" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BI258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK258" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL258" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG258" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI258" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ258" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK258" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>8</v>
       </c>
       <c r="BM258" t="inlineStr"/>
       <c r="BN258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>03.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N259" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>7</v>
+      </c>
+      <c r="R259" t="n">
+        <v>9</v>
+      </c>
+      <c r="S259" t="n">
+        <v>3</v>
+      </c>
+      <c r="T259" t="n">
+        <v>4</v>
+      </c>
+      <c r="U259" t="n">
+        <v>3</v>
+      </c>
+      <c r="V259" t="n">
+        <v>3</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1</v>
+      </c>
+      <c r="X259" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="AN259" t="inlineStr">
+        <is>
+          <t>kombouare antoine</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>de zerbi roberto</t>
+        </is>
+      </c>
+      <c r="AQ259" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU259" t="inlineStr"/>
+      <c r="AV259" t="inlineStr"/>
+      <c r="AW259" t="n">
+        <v>269</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>777</v>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr"/>
+      <c r="BA259" t="inlineStr"/>
+      <c r="BB259" t="inlineStr"/>
+      <c r="BC259" t="n">
+        <v>203</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>722</v>
+      </c>
+      <c r="BE259" t="inlineStr"/>
+      <c r="BF259" t="inlineStr"/>
+      <c r="BG259" t="inlineStr"/>
+      <c r="BH259" t="inlineStr"/>
+      <c r="BI259" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM259" t="inlineStr"/>
+      <c r="BN259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>16 366</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>16</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8</v>
+      </c>
+      <c r="T260" t="n">
+        <v>4</v>
+      </c>
+      <c r="U260" t="n">
+        <v>7</v>
+      </c>
+      <c r="V260" t="n">
+        <v>1</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1</v>
+      </c>
+      <c r="X260" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="AN260" t="inlineStr">
+        <is>
+          <t>pelissier christophe</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>stephan julien</t>
+        </is>
+      </c>
+      <c r="AQ260" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU260" t="inlineStr"/>
+      <c r="AV260" t="inlineStr"/>
+      <c r="AW260" t="n">
+        <v>326</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>510</v>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr"/>
+      <c r="BA260" t="inlineStr"/>
+      <c r="BB260" t="inlineStr"/>
+      <c r="BC260" t="n">
+        <v>258</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>440</v>
+      </c>
+      <c r="BE260" t="inlineStr"/>
+      <c r="BF260" t="inlineStr"/>
+      <c r="BG260" t="inlineStr"/>
+      <c r="BH260" t="inlineStr"/>
+      <c r="BI260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM260" t="inlineStr"/>
+      <c r="BN260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>12</v>
+      </c>
+      <c r="R261" t="n">
+        <v>15</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1</v>
+      </c>
+      <c r="U261" t="n">
+        <v>4</v>
+      </c>
+      <c r="V261" t="n">
+        <v>7</v>
+      </c>
+      <c r="W261" t="n">
+        <v>4</v>
+      </c>
+      <c r="X261" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="AN261" t="inlineStr">
+        <is>
+          <t>digard didier</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>gasset jean louis</t>
+        </is>
+      </c>
+      <c r="AQ261" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU261" t="inlineStr"/>
+      <c r="AV261" t="inlineStr"/>
+      <c r="AW261" t="n">
+        <v>433</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>462</v>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr"/>
+      <c r="BA261" t="inlineStr"/>
+      <c r="BB261" t="inlineStr"/>
+      <c r="BC261" t="n">
+        <v>358</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>383</v>
+      </c>
+      <c r="BE261" t="inlineStr"/>
+      <c r="BF261" t="inlineStr"/>
+      <c r="BG261" t="inlineStr"/>
+      <c r="BH261" t="inlineStr"/>
+      <c r="BI261" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM261" t="inlineStr"/>
+      <c r="BN261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>23 752</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>13</v>
+      </c>
+      <c r="R262" t="n">
+        <v>13</v>
+      </c>
+      <c r="S262" t="n">
+        <v>6</v>
+      </c>
+      <c r="T262" t="n">
+        <v>2</v>
+      </c>
+      <c r="U262" t="n">
+        <v>5</v>
+      </c>
+      <c r="V262" t="n">
+        <v>4</v>
+      </c>
+      <c r="W262" t="n">
+        <v>2</v>
+      </c>
+      <c r="X262" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="AN262" t="inlineStr">
+        <is>
+          <t>martinez carles</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>elsner luka</t>
+        </is>
+      </c>
+      <c r="AQ262" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU262" t="inlineStr"/>
+      <c r="AV262" t="inlineStr"/>
+      <c r="AW262" t="n">
+        <v>377</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>377</v>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr"/>
+      <c r="BA262" t="inlineStr"/>
+      <c r="BB262" t="inlineStr"/>
+      <c r="BC262" t="n">
+        <v>291</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>297</v>
+      </c>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+      <c r="BI262" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM262" t="inlineStr"/>
+      <c r="BN262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>02.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>33 043</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>2</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>13</v>
+      </c>
+      <c r="R263" t="n">
+        <v>9</v>
+      </c>
+      <c r="S263" t="n">
+        <v>3</v>
+      </c>
+      <c r="T263" t="n">
+        <v>3</v>
+      </c>
+      <c r="U263" t="n">
+        <v>8</v>
+      </c>
+      <c r="V263" t="n">
+        <v>4</v>
+      </c>
+      <c r="W263" t="n">
+        <v>2</v>
+      </c>
+      <c r="X263" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="AN263" t="inlineStr">
+        <is>
+          <t>dall oglio olivier</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>rosenior liam</t>
+        </is>
+      </c>
+      <c r="AQ263" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU263" t="inlineStr"/>
+      <c r="AV263" t="inlineStr"/>
+      <c r="AW263" t="n">
+        <v>388</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>729</v>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr"/>
+      <c r="BA263" t="inlineStr"/>
+      <c r="BB263" t="inlineStr"/>
+      <c r="BC263" t="n">
+        <v>322</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>670</v>
+      </c>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
+      <c r="BI263" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM263" t="inlineStr"/>
+      <c r="BN263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>02.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Turpin C.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>14 534</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N264" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>16</v>
+      </c>
+      <c r="R264" t="n">
+        <v>12</v>
+      </c>
+      <c r="S264" t="n">
+        <v>6</v>
+      </c>
+      <c r="T264" t="n">
+        <v>3</v>
+      </c>
+      <c r="U264" t="n">
+        <v>9</v>
+      </c>
+      <c r="V264" t="n">
+        <v>8</v>
+      </c>
+      <c r="W264" t="n">
+        <v>1</v>
+      </c>
+      <c r="X264" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="AN264" t="inlineStr">
+        <is>
+          <t>roy eric</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>haise franck</t>
+        </is>
+      </c>
+      <c r="AQ264" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU264" t="inlineStr"/>
+      <c r="AV264" t="inlineStr"/>
+      <c r="AW264" t="n">
+        <v>593</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>345</v>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr"/>
+      <c r="BA264" t="inlineStr"/>
+      <c r="BB264" t="inlineStr"/>
+      <c r="BC264" t="n">
+        <v>506</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>269</v>
+      </c>
+      <c r="BE264" t="inlineStr"/>
+      <c r="BF264" t="inlineStr"/>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
+      <c r="BI264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>11</v>
+      </c>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>02.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>47 926</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>18</v>
+      </c>
+      <c r="R265" t="n">
+        <v>13</v>
+      </c>
+      <c r="S265" t="n">
+        <v>8</v>
+      </c>
+      <c r="T265" t="n">
+        <v>2</v>
+      </c>
+      <c r="U265" t="n">
+        <v>5</v>
+      </c>
+      <c r="V265" t="n">
+        <v>6</v>
+      </c>
+      <c r="W265" t="n">
+        <v>5</v>
+      </c>
+      <c r="X265" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="AN265" t="inlineStr">
+        <is>
+          <t>luis enrique</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>still william</t>
+        </is>
+      </c>
+      <c r="AQ265" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>707</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>321</v>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr"/>
+      <c r="BA265" t="inlineStr"/>
+      <c r="BB265" t="inlineStr"/>
+      <c r="BC265" t="n">
+        <v>627</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>252</v>
+      </c>
+      <c r="BE265" t="inlineStr"/>
+      <c r="BF265" t="inlineStr"/>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
+      <c r="BI265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM265" t="inlineStr"/>
+      <c r="BN265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>01.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>45 084</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>14</v>
+      </c>
+      <c r="R266" t="n">
+        <v>14</v>
+      </c>
+      <c r="S266" t="n">
+        <v>2</v>
+      </c>
+      <c r="T266" t="n">
+        <v>3</v>
+      </c>
+      <c r="U266" t="n">
+        <v>8</v>
+      </c>
+      <c r="V266" t="n">
+        <v>6</v>
+      </c>
+      <c r="W266" t="n">
+        <v>4</v>
+      </c>
+      <c r="X266" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="AN266" t="inlineStr">
+        <is>
+          <t>genesio bruno</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>sage pierre</t>
+        </is>
+      </c>
+      <c r="AQ266" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU266" t="inlineStr"/>
+      <c r="AV266" t="inlineStr"/>
+      <c r="AW266" t="n">
+        <v>400</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>445</v>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr"/>
+      <c r="BA266" t="inlineStr"/>
+      <c r="BB266" t="inlineStr"/>
+      <c r="BC266" t="n">
+        <v>333</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>354</v>
+      </c>
+      <c r="BE266" t="inlineStr"/>
+      <c r="BF266" t="inlineStr"/>
+      <c r="BG266" t="inlineStr"/>
+      <c r="BH266" t="inlineStr"/>
+      <c r="BI266" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM266" t="inlineStr"/>
+      <c r="BN266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>01.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>10 540</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>11</v>
+      </c>
+      <c r="R267" t="n">
+        <v>10</v>
+      </c>
+      <c r="S267" t="n">
+        <v>3</v>
+      </c>
+      <c r="T267" t="n">
+        <v>3</v>
+      </c>
+      <c r="U267" t="n">
+        <v>4</v>
+      </c>
+      <c r="V267" t="n">
+        <v>3</v>
+      </c>
+      <c r="W267" t="n">
+        <v>4</v>
+      </c>
+      <c r="X267" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="AN267" t="inlineStr">
+        <is>
+          <t>hutter adi</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>dujeux alexandre</t>
+        </is>
+      </c>
+      <c r="AQ267" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>551</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU267" t="inlineStr"/>
+      <c r="AV267" t="inlineStr"/>
+      <c r="AW267" t="n">
+        <v>563</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>309</v>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr"/>
+      <c r="BA267" t="inlineStr"/>
+      <c r="BB267" t="inlineStr"/>
+      <c r="BC267" t="n">
+        <v>474</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>236</v>
+      </c>
+      <c r="BE267" t="inlineStr"/>
+      <c r="BF267" t="inlineStr"/>
+      <c r="BG267" t="inlineStr"/>
+      <c r="BH267" t="inlineStr"/>
+      <c r="BI267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>17</v>
+      </c>
+      <c r="BM267" t="inlineStr"/>
+      <c r="BN267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>W6sFgYy8</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>02.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Kubler G.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Stade de Roudourou
+ (Guingamp)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>19 060</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>6 733</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>3</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>QDfKl36E</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Guingamp</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>UgPj1p1N</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>18</v>
+      </c>
+      <c r="R268" t="n">
+        <v>16</v>
+      </c>
+      <c r="S268" t="n">
+        <v>8</v>
+      </c>
+      <c r="T268" t="n">
+        <v>5</v>
+      </c>
+      <c r="U268" t="n">
+        <v>6</v>
+      </c>
+      <c r="V268" t="n">
+        <v>8</v>
+      </c>
+      <c r="W268" t="n">
+        <v>4</v>
+      </c>
+      <c r="X268" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y268" t="inlineStr"/>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="inlineStr"/>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>QNSJnsB5</t>
+        </is>
+      </c>
+      <c r="AN268" t="inlineStr">
+        <is>
+          <t>ripoll sylvain</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>WrQARdPN</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>tanchot oswald</t>
+        </is>
+      </c>
+      <c r="AQ268" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU268" t="inlineStr"/>
+      <c r="AV268" t="inlineStr"/>
+      <c r="AW268" t="n">
+        <v>477</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>485</v>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr"/>
+      <c r="BA268" t="inlineStr"/>
+      <c r="BB268" t="inlineStr"/>
+      <c r="BC268" t="n">
+        <v>399</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>415</v>
+      </c>
+      <c r="BE268" t="inlineStr"/>
+      <c r="BF268" t="inlineStr"/>
+      <c r="BG268" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>18</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM268" t="inlineStr"/>
+      <c r="BN268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2RkbcGxq</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>02.11.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Taleb A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Stade Michel d'Ornano
+ (Caen)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>20 300</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>15 441</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>GjLn2QoH</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>AZwK8L6R</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>3</v>
+      </c>
+      <c r="R269" t="n">
+        <v>17</v>
+      </c>
+      <c r="S269" t="n">
+        <v>2</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
+      <c r="V269" t="n">
+        <v>9</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1</v>
+      </c>
+      <c r="X269" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y269" t="inlineStr"/>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE269" t="inlineStr"/>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>Q9EVqFe4</t>
+        </is>
+      </c>
+      <c r="AN269" t="inlineStr">
+        <is>
+          <t>seube nicolas</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>fo8nHfg4</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>tavenot benoit</t>
+        </is>
+      </c>
+      <c r="AQ269" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU269" t="inlineStr"/>
+      <c r="AV269" t="inlineStr"/>
+      <c r="AW269" t="n">
+        <v>430</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>500</v>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr"/>
+      <c r="BA269" t="inlineStr"/>
+      <c r="BB269" t="inlineStr"/>
+      <c r="BC269" t="n">
+        <v>330</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>397</v>
+      </c>
+      <c r="BE269" t="inlineStr"/>
+      <c r="BF269" t="inlineStr"/>
+      <c r="BG269" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>18</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM269" t="inlineStr"/>
+      <c r="BN269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>lrCa1peE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Parc des Sports
+ (Annecy)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>15 660</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>5 333</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>25dB6Eto</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>6NOhR4cm</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Pau FC</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>8</v>
+      </c>
+      <c r="R270" t="n">
+        <v>9</v>
+      </c>
+      <c r="S270" t="n">
+        <v>5</v>
+      </c>
+      <c r="T270" t="n">
+        <v>2</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" t="n">
+        <v>5</v>
+      </c>
+      <c r="W270" t="n">
+        <v>3</v>
+      </c>
+      <c r="X270" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE270" t="inlineStr"/>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>SIiBpBrs</t>
+        </is>
+      </c>
+      <c r="AN270" t="inlineStr">
+        <is>
+          <t>guyot laurent</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>fm0Qb28B</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>usai nicolas</t>
+        </is>
+      </c>
+      <c r="AQ270" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>228</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>457</v>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr"/>
+      <c r="BA270" t="inlineStr"/>
+      <c r="BB270" t="inlineStr"/>
+      <c r="BC270" t="n">
+        <v>127</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>336</v>
+      </c>
+      <c r="BE270" t="inlineStr"/>
+      <c r="BF270" t="inlineStr"/>
+      <c r="BG270" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM270" t="inlineStr"/>
+      <c r="BN270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>hh4S2xFL</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Lesage M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Stade Gabriel Montpied
+ (Clermont-Ferrand)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>10 800</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>2</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>IRuMRua1</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Clermont</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>jgNAYRGi</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>12</v>
+      </c>
+      <c r="R271" t="n">
+        <v>9</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4</v>
+      </c>
+      <c r="T271" t="n">
+        <v>2</v>
+      </c>
+      <c r="U271" t="n">
+        <v>4</v>
+      </c>
+      <c r="V271" t="n">
+        <v>4</v>
+      </c>
+      <c r="W271" t="n">
+        <v>4</v>
+      </c>
+      <c r="X271" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y271" t="inlineStr"/>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="inlineStr"/>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>YLrocixH</t>
+        </is>
+      </c>
+      <c r="AN271" t="inlineStr">
+        <is>
+          <t>batlles laurent</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>Cp0gM1r4</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>pantaloni olivier</t>
+        </is>
+      </c>
+      <c r="AQ271" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU271" t="inlineStr"/>
+      <c r="AV271" t="inlineStr"/>
+      <c r="AW271" t="n">
+        <v>453</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>569</v>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr"/>
+      <c r="BA271" t="inlineStr"/>
+      <c r="BB271" t="inlineStr"/>
+      <c r="BC271" t="n">
+        <v>361</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>485</v>
+      </c>
+      <c r="BE271" t="inlineStr"/>
+      <c r="BF271" t="inlineStr"/>
+      <c r="BG271" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM271" t="inlineStr"/>
+      <c r="BN271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>tjU6aOPQ</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Thual O.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Stade Marcel Tribut
+ (Dunkerque)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>4 933</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H272" t="n">
+        <v>1</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>tAAobNse</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Dunkerque</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>lKkBAsxF</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Amiens</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>15</v>
+      </c>
+      <c r="R272" t="n">
+        <v>12</v>
+      </c>
+      <c r="S272" t="n">
+        <v>8</v>
+      </c>
+      <c r="T272" t="n">
+        <v>6</v>
+      </c>
+      <c r="U272" t="n">
+        <v>1</v>
+      </c>
+      <c r="V272" t="n">
+        <v>4</v>
+      </c>
+      <c r="W272" t="n">
+        <v>6</v>
+      </c>
+      <c r="X272" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y272" t="inlineStr"/>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE272" t="inlineStr"/>
+      <c r="AF272" t="inlineStr"/>
+      <c r="AG272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+      <c r="AN272" t="inlineStr">
+        <is>
+          <t>castro luis</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>dS1CBple</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>daf omar</t>
+        </is>
+      </c>
+      <c r="AQ272" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU272" t="inlineStr"/>
+      <c r="AV272" t="inlineStr"/>
+      <c r="AW272" t="n">
+        <v>475</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>458</v>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr"/>
+      <c r="BA272" t="inlineStr"/>
+      <c r="BB272" t="inlineStr"/>
+      <c r="BC272" t="n">
+        <v>394</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>381</v>
+      </c>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI272" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM272" t="inlineStr"/>
+      <c r="BN272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>QN5wf2ml</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Petit A.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Stade Francis Turcan
+ (Martigues)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>ADl76OZP</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Martigues</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>2kM6ufaS</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>7</v>
+      </c>
+      <c r="R273" t="n">
+        <v>18</v>
+      </c>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
+        <v>6</v>
+      </c>
+      <c r="U273" t="n">
+        <v>4</v>
+      </c>
+      <c r="V273" t="n">
+        <v>10</v>
+      </c>
+      <c r="W273" t="n">
+        <v>3</v>
+      </c>
+      <c r="X273" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y273" t="inlineStr"/>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE273" t="inlineStr"/>
+      <c r="AF273" t="inlineStr"/>
+      <c r="AG273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>EwpPg8iH</t>
+        </is>
+      </c>
+      <c r="AN273" t="inlineStr">
+        <is>
+          <t>laurey thierry</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>SzfSpYcf</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>poirier gregory</t>
+        </is>
+      </c>
+      <c r="AQ273" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>305</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>600</v>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr"/>
+      <c r="BA273" t="inlineStr"/>
+      <c r="BB273" t="inlineStr"/>
+      <c r="BC273" t="n">
+        <v>220</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>524</v>
+      </c>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI273" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ273" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK273" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL273" t="n">
+        <v>17</v>
+      </c>
+      <c r="BM273" t="inlineStr"/>
+      <c r="BN273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>bgq7ef7e</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Benchabane F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Stade Charlety
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>12 377</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>0OEHEprs</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>0pOdQOCg</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Rodez</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>13</v>
+      </c>
+      <c r="R274" t="n">
+        <v>12</v>
+      </c>
+      <c r="S274" t="n">
+        <v>7</v>
+      </c>
+      <c r="T274" t="n">
+        <v>6</v>
+      </c>
+      <c r="U274" t="n">
+        <v>4</v>
+      </c>
+      <c r="V274" t="n">
+        <v>4</v>
+      </c>
+      <c r="W274" t="n">
+        <v>2</v>
+      </c>
+      <c r="X274" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y274" t="inlineStr"/>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE274" t="inlineStr"/>
+      <c r="AF274" t="inlineStr"/>
+      <c r="AG274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>zB2j3YvM</t>
+        </is>
+      </c>
+      <c r="AN274" t="inlineStr">
+        <is>
+          <t>gilli stephane</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>OQuqpG7i</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>santini didier</t>
+        </is>
+      </c>
+      <c r="AQ274" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU274" t="inlineStr"/>
+      <c r="AV274" t="inlineStr"/>
+      <c r="AW274" t="n">
+        <v>790</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>257</v>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr"/>
+      <c r="BA274" t="inlineStr"/>
+      <c r="BB274" t="inlineStr"/>
+      <c r="BC274" t="n">
+        <v>682</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE274" t="inlineStr"/>
+      <c r="BF274" t="inlineStr"/>
+      <c r="BG274" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM274" t="inlineStr"/>
+      <c r="BN274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>QXnqeErJ</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Leleu M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Stade de l'Aube
+ (Troyes)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>20 420</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>5 365</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>fsfAHubD</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Troyes</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>E1wDrLsJ</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>9</v>
+      </c>
+      <c r="R275" t="n">
+        <v>9</v>
+      </c>
+      <c r="S275" t="n">
+        <v>5</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1</v>
+      </c>
+      <c r="U275" t="n">
+        <v>3</v>
+      </c>
+      <c r="V275" t="n">
+        <v>2</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1</v>
+      </c>
+      <c r="X275" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y275" t="inlineStr"/>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE275" t="inlineStr"/>
+      <c r="AF275" t="inlineStr"/>
+      <c r="AG275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>4vG8dmrf</t>
+        </is>
+      </c>
+      <c r="AN275" t="inlineStr">
+        <is>
+          <t>dumont stephane</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>Ys1Pb7ws</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>frapolli olivier</t>
+        </is>
+      </c>
+      <c r="AQ275" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU275" t="inlineStr"/>
+      <c r="AV275" t="inlineStr"/>
+      <c r="AW275" t="n">
+        <v>590</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>396</v>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr"/>
+      <c r="BA275" t="inlineStr"/>
+      <c r="BB275" t="inlineStr"/>
+      <c r="BC275" t="n">
+        <v>502</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>315</v>
+      </c>
+      <c r="BE275" t="inlineStr"/>
+      <c r="BF275" t="inlineStr"/>
+      <c r="BG275" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM275" t="inlineStr"/>
+      <c r="BN275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>4WNXteh2</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>04.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Buquet R.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Michel Moretti Stadium
+ (Ajaccio)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>8 470</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2 757</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2aeoANM8</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>AC Ajaccio</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>4v0yqlWc</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr"/>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr"/>
+      <c r="AF276" t="inlineStr"/>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>8tmnzqxe</t>
+        </is>
+      </c>
+      <c r="AN276" t="inlineStr">
+        <is>
+          <t>chabert mathieu</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>le mignan stephane</t>
+        </is>
+      </c>
+      <c r="AQ276" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>555</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU276" t="inlineStr"/>
+      <c r="AV276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr"/>
+      <c r="BA276" t="inlineStr"/>
+      <c r="BB276" t="inlineStr"/>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="BD276" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="BE276" t="inlineStr"/>
+      <c r="BF276" t="inlineStr"/>
+      <c r="BG276" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BH276" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="BI276" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BL276" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BM276" t="inlineStr"/>
+      <c r="BN276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
